--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -57,7 +57,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -78,6 +78,12 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -355,7 +361,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z224"/>
+  <dimension ref="A1:Z70"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="11.63" customWidth="1" style="5" min="1" max="1"/>
@@ -386,17 +392,17 @@
           <t>Category</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="8" t="inlineStr">
         <is>
           <t>Detailed Explanation</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="8" t="inlineStr">
         <is>
           <t>Execution Steps</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="8" t="inlineStr">
         <is>
           <t>Pass Criteria</t>
         </is>
@@ -450,12 +456,12 @@
           <t>Tunneling / Stress</t>
         </is>
       </c>
-      <c r="D2" s="6" t="inlineStr">
+      <c r="D2" s="7" t="inlineStr">
         <is>
           <t>Simulates a burst of rapid TCP/UDP connection attempts (hundreds of concurrent connections) while the Netskope client tunnel is active. Tests whether the tunnel manager, WFP callout driver (stadrv), and FilterDevice rules can handle connection-table pressure without dropping legitimate traffic or crashing. Targets the packet interception layer's ability to classify and steer high volumes of new flows simultaneously.</t>
         </is>
       </c>
-      <c r="E2" s="6" t="inlineStr">
+      <c r="E2" s="7" t="inlineStr">
         <is>
           <t>1. Enroll Windows client with tunnel active and steering enabled
 2. Launch a connection storm tool (e.g., custom script opening 500+ concurrent HTTP/HTTPS connections to different destinations)
@@ -465,7 +471,7 @@
 6. Check Event Viewer for driver errors or pool exhaustion warnings</t>
         </is>
       </c>
-      <c r="F2" s="6" t="inlineStr">
+      <c r="F2" s="7" t="inlineStr">
         <is>
           <t>No BSOD. No service crash. Tunnel remains connected OR recovers within 60s. No permanent FilterDevice rule corruption.</t>
         </is>
@@ -519,12 +525,12 @@
           <t>Tunneling / Stress</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="7" t="inlineStr">
         <is>
           <t>Saturates the tunnel with maximum throughput traffic (large file downloads, streaming, bulk uploads simultaneously) to verify the tunnel can sustain high bandwidth without packet loss, memory growth, or degraded steering decisions. Tests the DTLS/TLS data path under sustained load — specifically whether the tunnel's send/receive buffers, SPDY framing, and kernel-to-usermode packet copy can keep up.</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="7" t="inlineStr">
         <is>
           <t>1. Establish tunnel (TLS and DTLS variants)
 2. Initiate sustained high-bandwidth traffic: 10 parallel large file downloads (1GB each) + streaming video + bulk upload
@@ -534,7 +540,7 @@
 6. Verify no tunnel disconnect during sustained load</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>Throughput sustains &gt;80% of baseline. Memory growth &lt;50MB over 30 min. No tunnel disconnects. Steering correctness maintained.</t>
         </is>
@@ -588,12 +594,12 @@
           <t>Tunneling / Stress</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>Rapidly connects and disconnects the tunnel (simulating unstable network — WiFi handoffs, VPN toggling, network adapter enable/disable). Tests the tunnel state machine's ability to handle rapid transitions between CONNECTED, DISCONNECTING, DISCONNECTED, and CONNECTING states without race conditions, leaked resources, or stuck states. Specifically targets the 22-state tunnel state machine and reconnect strategy logic.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>1. Establish tunnel connection
 2. Rapidly toggle network adapter (disable/enable) every 5-10 seconds for 50+ cycles
@@ -605,7 +611,7 @@
 8. Verify NPA tunnel also reconnects properly after each flap</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
         <is>
           <t>Tunnel recovers to CONNECTED state within 30s of network restore on every cycle. No stuck states. No crash. Resource counts stable.</t>
         </is>
@@ -659,12 +665,12 @@
           <t>Watchdog / Service Lifecycle</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="7" t="inlineStr">
         <is>
           <t>Kills the stAgentSvc service process unexpectedly (simulating crash, AV/EDR interference, or resource exhaustion) and verifies the Watchdog service (stAgentSvcWD) detects the abnormal stop and restarts it. Tests the watchdog's 60-second polling loop, its detection of non-zero exit codes, and its upgrade-bypass logic (should NOT restart during upgrades).</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="7" t="inlineStr">
         <is>
           <t>1. Verify stAgentSvc and stAgentSvcWD are both running
 2. taskkill /F /IM stAgentSvc.exe (force kill — simulates crash)
@@ -676,7 +682,7 @@
 8. Test edge case: kill stAgentSvc during upgrade (UpgradeInProgress=1 in registry) — watchdog should NOT restart</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>Watchdog restarts service within 60-90s. Tunnel recovers. No restart during upgrade. No permanent state corruption after crash+restart.</t>
         </is>
@@ -730,12 +736,12 @@
           <t>FailClose / Security</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>Verifies that FailClose correctly blocks all non-exempted traffic when the tunnel is unavailable (gateway unreachable, service crash, cert expiry). Tests the WFP FilterDevice rules that enforce blocking, captive portal detection for WiFi login exceptions, and the grace period mechanism. Critical: verifies FailClose does NOT get stuck in blocking state after tunnel recovery.</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>1. Enable FailClose in client configuration
 2. Establish tunnel — verify normal traffic flows
@@ -747,7 +753,7 @@
 8. Test edge case: FailClose + NPA-only tunnel (ENG-1012026 pattern) — verify cert-pinned apps are also blocked</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>Traffic blocked within 5s of tunnel drop. Traffic restored within 30s of tunnel recovery. No permanent block state. Captive portal detection works.</t>
         </is>
@@ -801,12 +807,12 @@
           <t>Steering / Config</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="7" t="inlineStr">
         <is>
           <t>Rapidly toggles traffic steering configuration between enabled and disabled states (via config push from management plane). Tests the client's ability to handle steering mode transitions (ALL→NONE→WEB→ALL) without dropping traffic, leaving stale FilterDevice rules, or entering an inconsistent state where some rules apply and others don't.</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="7" t="inlineStr">
         <is>
           <t>1. Start with steering mode = ALL (all traffic steered through tunnel)
 2. Push config change: steering = NONE
@@ -820,7 +826,7 @@
 10. Verify: ENG-591725 pattern — NONE→WEB transition actually reconnects tunnel</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>Steering transitions complete within 30s. No stale rules. No traffic leak during transition. NONE→WEB triggers reconnect.</t>
         </is>
@@ -874,12 +880,12 @@
           <t>Power Management / Tunneling</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="7" t="inlineStr">
         <is>
           <t>Tests NSClient behavior during Modern Standby (S0 low-power idle / Connected Standby / AOAC). Modern Standby is NOT traditional sleep — the CPU stays active at reduced power, and network adapters may stay connected. The client must handle: partial network availability during standby, timer coalescing, and the transition back to full-power where tunnel state must be valid. Tests specifically whether the tunnel state machine correctly handles AOAC power notifications.</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>1. Ensure test device supports Modern Standby (powercfg /a shows S0 Low Power Idle)
 2. Establish tunnel, verify traffic flowing
@@ -893,7 +899,7 @@
 10. Verify: memory consumption hasn't grown across cycles (no leak from repeated standby/wake)</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>Tunnel reconnects within 15s of wake. No manual intervention needed. No FailClose false-positive during wake. No memory growth across cycles.</t>
         </is>
@@ -947,12 +953,12 @@
           <t>Power Management / Service Lifecycle</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>Tests NSClient behavior across full hibernate (S4 — memory saved to disk, full power off) and resume. Unlike Modern Standby, S4 means ALL state is lost — network adapters reset, services see a cold-start-like event but with preserved process memory. Tests whether the service correctly re-detects network, re-establishes tunnel, and whether any in-memory state (tunnel state machine, config cache, GSLB selection) becomes stale or corrupt after resume.</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="7" t="inlineStr">
         <is>
           <t>1. Establish tunnel, verify traffic flowing
 2. Trigger hibernate (shutdown /h)
@@ -965,7 +971,7 @@
 9. Verify: FailClose handles the transition correctly (doesn't block during reconnect window)</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>Service survives hibernate. Tunnel reconnects within 30s of resume. Config re-validated. No stale GSLB state.</t>
         </is>
@@ -1019,12 +1025,12 @@
           <t>Power Management / Tunneling</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="7" t="inlineStr">
         <is>
           <t>Repeatedly cycles through S1 sleep and wake (traditional sleep, not Modern Standby) to stress-test the network change detection → tunnel reconnect path. Each sleep/wake is a full network adapter reset, meaning the tunnel MUST re-establish each time. Tests for resource leaks, stuck states, and degraded reconnect time across many cycles.</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>1. Establish tunnel, verify traffic flowing
 2. Script: trigger sleep (rundll32.exe powrprof.dll,SetSuspendState 0,1,0) → wait 30s → wake via scheduled task or WoL
@@ -1035,7 +1041,7 @@
 7. Verify: FailClose correctly blocks during the reconnect window of each cycle, unblocks after</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>Reconnect time consistent (&lt;30s) across all 50 cycles. No memory/handle growth. No permanent disconnect. FailClose correct on each cycle.</t>
         </is>
@@ -1089,12 +1095,12 @@
           <t>Power Management / Install-Upgrade</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="7" t="inlineStr">
         <is>
           <t>Rapidly reboots the machine (20+ cycles) to stress-test service startup, driver loading, config persistence, and enrollment state survival. Tests whether the client reliably starts after each boot, whether the stadrv driver loads correctly via SYSTEM_START, and whether config/certs survive the reboot cycle without corruption.</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="7" t="inlineStr">
         <is>
           <t>1. Verify client is enrolled, tunnel active
 2. Script: automated reboot loop (shutdown /r /t 5) with a scheduled task to verify client state on each boot
@@ -1105,7 +1111,7 @@
 7. Test variant: reboot during active upgrade (simulate power failure during MSI) — verify Legacy Monitor retries</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>All 20 reboots: service starts, driver loads, tunnel connects. No enrollment loss. No config corruption.</t>
         </is>
@@ -1159,12 +1165,12 @@
           <t>Soak / Resource Exhaustion</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>Runs the client under realistic production workload (browsing, streaming, file downloads, idle periods) for 72+ hours continuously. Monitors all process memory (stAgentSvc, stAgentUI, stadrv kernel pool) for unbounded growth. Tests for: handle leaks, thread leaks, cache growth without eviction, timer accumulation, connection pool growth, and FD exhaustion.</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>1. Enroll client, establish tunnel with steering = ALL
 2. Run automated workload: browser automation cycling through 100 websites, periodic large downloads, video streaming, idle periods
@@ -1176,7 +1182,7 @@
 8. Verify: tunnel remained connected throughout (check connection duration)</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>Memory growth &lt;200MB over 72h. No handle leak. No thread leak. No service crash. Tunnel uptime = test duration.</t>
         </is>
@@ -1230,12 +1236,12 @@
           <t>Driver / Kernel Integrity</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>Runs the stadrv kernel driver under Windows Driver Verifier with all checks enabled (pool tracking, IRQL checking, deadlock detection, I/O verification, DMA checking). Executes normal client operations while Driver Verifier monitors for: pool corruption, IRQL violations, deadlocks, use-after-free, double-free, buffer overruns. Any violation = BSOD with detailed crash dump identifying the exact code path.</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="7" t="inlineStr">
         <is>
           <t>1. Enable Driver Verifier for stadrv.sys: verifier /standard /driver stadrv.sys
 2. Reboot
@@ -1246,7 +1252,7 @@
 7. After test: disable Driver Verifier (verifier /reset), reboot</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>No BSOD for 4+ hours under full workload with Driver Verifier enabled. Zero pool violations detected.</t>
         </is>
@@ -1300,12 +1306,12 @@
           <t>Watchdog / Resilience</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>Tests watchdog resilience when the main service repeatedly crashes in rapid succession. Verifies the watchdog continues restarting without itself becoming unstable, and that the system eventually stabilizes. Also tests: what happens if the watchdog itself is killed? Is there a recovery mechanism?</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>1. Verify stAgentSvcWD and stAgentSvc both running
 2. Kill stAgentSvc immediately after watchdog restarts it — repeat 10 times in rapid succession
@@ -1316,7 +1322,7 @@
 7. Test: kill both stAgentSvc and stAgentSvcWD simultaneously — document recovery path</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>Watchdog survives 10 rapid restarts without itself crashing. Service eventually stabilizes. System returns to normal operation.</t>
         </is>
@@ -1370,12 +1376,12 @@
           <t>Config Download / Stress</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="7" t="inlineStr">
         <is>
           <t>Simulates rapid successive config pushes from management plane (admin making multiple quick changes, or automation scripts). Tests whether the client handles config updates that arrive faster than they can be processed — specifically whether ConfigMgr queues them correctly, whether partial config application occurs, and whether the final state matches the last pushed config.</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="7" t="inlineStr">
         <is>
           <t>1. Establish tunnel with known config state
 2. Push 20 config changes in rapid succession (2-second intervals) from management plane — each changing a different setting
@@ -1386,7 +1392,7 @@
 7. Monitor: memory during rapid config processing (no unbounded queue growth)</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>Final config state matches last push. No partial application. No crash. Reasonable tunnel disruption (not N reconnects for N config changes).</t>
         </is>
@@ -1440,12 +1446,12 @@
           <t>Install-Upgrade / FailClose</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="7" t="inlineStr">
         <is>
           <t>Tests the highest-risk NSClient scenario: auto-upgrade triggers while FailClose is active and blocking traffic. During upgrade, the service restarts — which means FailClose rules in the WFP driver must persist even while the usermode service is down. Tests whether FilterDevice rules survive the upgrade gap and whether traffic remains blocked (not leaked) during the upgrade window.</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="7" t="inlineStr">
         <is>
           <t>1. Enable FailClose, disconnect from gateway (FailClose actively blocking traffic)
 2. Trigger auto-upgrade to a new version
@@ -1455,7 +1461,7 @@
 6. Test: upgrade fails/rolls back while FailClose is active — verify recovery</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>Zero traffic leak during upgrade window. FailClose rules persist in stadrv even during service restart. Clean recovery after upgrade completes or fails.</t>
         </is>
@@ -1509,12 +1515,12 @@
           <t>Install-Upgrade / Watchdog</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="7" t="inlineStr">
         <is>
           <t>Tests the Legacy Monitor's ability to retry an aborted MSI installation. Simulates power failure / BSOD during upgrade by force-killing the MSI process mid-installation. Verifies the Legacy Monitor (stAgentSvcMon) detects the incomplete upgrade on next boot and retries, eventually reaching a consistent state.</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="7" t="inlineStr">
         <is>
           <t>1. Trigger auto-upgrade
 2. While MSI is running (before completion): force power off (or taskkill msiexec.exe)
@@ -1526,7 +1532,7 @@
 8. Verify: client is functional after recovery (enrolled, tunnel active)</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>Legacy Monitor retries successfully. Client reaches consistent state (either upgraded or rolled back). No stuck half-installed state.</t>
         </is>
@@ -1580,12 +1586,12 @@
           <t>Tunneling / Network Change</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>Rapidly adds and removes virtual network adapters (VPN connect/disconnect, USB tethering plug/unplug, VM network adapter add/remove). Each adapter change triggers a network change event that the tunnel state machine must process. Tests for race conditions when multiple network change events arrive faster than the reconnect cycle can complete.</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>1. Establish tunnel on primary adapter
 2. Rapidly enable/disable a secondary adapter (VPN, USB ethernet) every 3 seconds for 30 cycles
@@ -1595,7 +1601,7 @@
 6. Test: remove ALL adapters (airplane mode) → re-add primary → verify tunnel reconnects</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>Tunnel survives secondary adapter changes. Correct reconnect on primary adapter loss/restore. No race conditions.</t>
         </is>
@@ -1649,12 +1655,12 @@
           <t>Tunneling / Proxy</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="7" t="inlineStr">
         <is>
           <t>Tests tunnel reconnection through an authenticated proxy after various disconnect events (reboot, sleep/wake, network change). The proxy detection path is one of the highest-risk areas in tunnel establishment — ENG-593814 shows proxy fails after reboot, ENG-463329 shows proxy lost after upgrade. Tests whether proxy credentials survive state transitions.</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="7" t="inlineStr">
         <is>
           <t>1. Configure client behind an authenticated proxy (NTLM or Kerberos)
 2. Verify tunnel connects through proxy successfully
@@ -1667,7 +1673,7 @@
 9. Test: proxy returns 407 during reconnect — verify client handles gracefully (no infinite auth loop)</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>Tunnel reconnects through proxy after every state transition. No credential loss. No infinite auth loop on 407.</t>
         </is>
@@ -1721,12 +1727,12 @@
           <t>FailClose / Network</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="7" t="inlineStr">
         <is>
           <t>Tests captive portal detection — the mechanism that temporarily allows traffic when FailClose would otherwise block a user trying to authenticate to hotel/airport WiFi. Verifies detection works for various portal types: HTTP redirects, meta refresh tags, JavaScript-based redirects, and HTTPS-intercepting portals. This is the #1 source of FailClose escalation bugs.</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="7" t="inlineStr">
         <is>
           <t>1. Enable FailClose on client
 2. Connect to a WiFi network with a captive portal (or simulate one)
@@ -1737,7 +1743,7 @@
 7. Test: grace period expires before user completes login — verify FailClose re-blocks AND allows retry</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>Captive portal detected. Grace period opens. User can authenticate. FailClose resumes after auth. Works for all portal types.</t>
         </is>
@@ -1791,12 +1797,12 @@
           <t>FailClose / VDI</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>Tests FailClose behavior when multiple users share a VDI machine. The master image may have FailClose enabled, but individual user sessions have different enrollment states. Tests: does FailClose apply per-user or per-machine? What happens when one user is enrolled and another isn't? What if the enrolled user logs off — does FailClose trap the next user?</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="7" t="inlineStr">
         <is>
           <t>1. Configure VDI machine with FailClose enabled and peruserconfig mode
 2. User A logs in and enrolls — verify tunnel connects, traffic flows
@@ -1806,7 +1812,7 @@
 6. Verify: FailClose doesn't permanently lock out non-enrolled users on shared machines</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>Non-enrolled users can still reach enrollment portal. FailClose doesn't trap users in unrecoverable state on shared machines. Per-user isolation works correctly.</t>
         </is>
@@ -1860,12 +1866,12 @@
           <t>Service Lifecycle / IPC</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="7" t="inlineStr">
         <is>
           <t>Tests NSCom2/NSMsg2 IPC communication between stAgentSvc (service) and nsClient UI process when the service restarts (crash, upgrade, watchdog-triggered restart). Verifies the UI correctly detects service loss, reconnects IPC channel on restart, and displays accurate status — not stale state from pre-restart.</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="7" t="inlineStr">
         <is>
           <t>1. Verify stAgentSvc running, UI connected via IPC (tray icon shows connected)
 2. Kill stAgentSvc (simulate crash)
@@ -1876,7 +1882,7 @@
 7. Test: rapid service restarts (3 in 60s) — verify UI doesn't crash from rapid IPC reconnect attempts</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>UI accurately reflects service state through crash and restart. No stale status. No UI crash during rapid service restarts.</t>
         </is>
@@ -1930,12 +1936,12 @@
           <t>Steering / Traffic Interception</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="7" t="inlineStr">
         <is>
           <t>Tests what happens to active TCP connections when steering rules change (e.g., a domain moves from 'bypass' to 'steer' via config push). Existing connections established before the rule change should either be: gracefully terminated and re-established through tunnel, OR allowed to complete and new connections follow new rules. Tests for connection drops, RST storms, or silent policy bypass on existing connections.</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="7" t="inlineStr">
         <is>
           <t>1. Establish tunnel with steering enabled
 2. Start a long-lived TCP connection to a domain that is currently bypassed (e.g., large download)
@@ -1946,7 +1952,7 @@
 7. Test: 100 active connections across 50 domains, change steering for all 50 simultaneously</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="7" t="inlineStr">
         <is>
           <t>New connections follow new rules. Existing connections handled gracefully (no user-visible breakage). No permanent policy bypass on stale connections.</t>
         </is>
@@ -2000,12 +2006,12 @@
           <t>Certificate Management / Tunneling</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>Tests client behavior when the device certificate expires while the tunnel is active. The tunnel authenticated using this cert — what happens when it expires mid-session? Tests: does the tunnel drop? Does it gracefully re-download a new cert? What happens with FailClose during the re-authentication window?</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>1. Enroll client with a device cert that expires in 2 hours (or manipulate system clock)
 2. Establish tunnel — verify traffic flows
@@ -2017,7 +2023,7 @@
 8. Test: MP is unreachable when cert expires — what happens? Permanent disconnect?</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>Cert renewal automatic. Tunnel re-authenticates without user intervention. Minimal (&lt;30s) disruption. FailClose handles gracefully.</t>
         </is>
@@ -2071,7 +2077,7 @@
           <t>FailClose / Steering</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="7" t="inlineStr">
         <is>
           <t>DNS traffic not steered after FailClose recovery; FailClose + Flexible Dynamic Steering race. FailClose + Dynamic Steering combination causes 5 S1 bugs. DNS not steered after FC recovery. Distinct from generic FC enforcement test.</t>
         </is>
@@ -2087,7 +2093,7 @@
 7. Repeat 1~6 for 20 times</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="7" t="inlineStr">
         <is>
           <t>DNS traffic steered correctly after FailClose recovery; steering mode change during FailClose does not leave inconsistent state; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2141,7 +2147,7 @@
           <t>Soak / Client Status</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="7" t="inlineStr">
         <is>
           <t>Burst of client status updates overwhelms backend causing config download failures for all tenants. 4 Critical/High IMFs from same pattern — client status storms from AD sync or enable/disable cycles overwhelming provisioner-clientservices.</t>
         </is>
@@ -2156,7 +2162,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="F26" s="7" t="inlineStr">
         <is>
           <t>Client throttles status updates to &lt;1 per 60s; config downloads succeed within 30s during storm; no cascading failure; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2210,7 +2216,7 @@
           <t>Power Management / AOAC</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="7" t="inlineStr">
         <is>
           <t>AOAC devices lose enrollment or disconnect after wake due to cached status race. 12 AOAC escalations — highest feature count after Steering. Repeated pattern: AOAC wake triggers stale cached status causing disable/disconnect.</t>
         </is>
@@ -2225,7 +2231,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="F27" s="7" t="inlineStr">
         <is>
           <t>Client remains enabled with correct status after AOAC wake; upgrade completes without enrollment loss on AOAC device; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2279,7 +2285,7 @@
           <t>FailClose / Network</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="7" t="inlineStr">
         <is>
           <t>FailClose rules not applied on cold boot when NSGW is unreachable at startup. S1 bug class — traffic bypasses FailClose post-reboot. Distinct from existing FC-01 (captive portal) and STRESS-07 (runtime enforcement).</t>
         </is>
@@ -2294,7 +2300,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="F28" s="7" t="inlineStr">
         <is>
           <t>All non-exempt traffic blocked immediately after boot even when gateway is unreachable; tunnel recovers when gateway accessible again; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2348,7 +2354,7 @@
           <t>Self-Protection / Tamper</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="7" t="inlineStr">
         <is>
           <t>Anti-tampering bypassed by CCleaner-style tools or driver IOCTL manipulation. PSIRT-class vulnerabilities. 3rd-party tools can remove client without tamperproof password; IOCTL bypass disables client.</t>
         </is>
@@ -2364,7 +2370,7 @@
 7. Repeat 1~6 for 20 times</t>
         </is>
       </c>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="F29" s="7" t="inlineStr">
         <is>
           <t>All third-party uninstall attempts blocked; unauthorized IOCTL commands rejected; client remains enabled and protected; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2418,7 +2424,7 @@
           <t>Steering / DNS Security</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="7" t="inlineStr">
         <is>
           <t>Large DNS TCP packets dropped or cause BSOD; DNS security causes perf degradation under load. DNS TCP fix caused BSOD (S1 in review). Large TCP segmented packets dropped in loopback. DNS security causes perf issues on VDI/Citrix.</t>
         </is>
@@ -2433,7 +2439,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="F30" s="7" t="inlineStr">
         <is>
           <t>No packet drops for large DNS TCP; no BSOD; DNS latency &lt;100ms under 50-session load on VDI; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2487,7 +2493,7 @@
           <t>Steering / DNS Security / VDI</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="7" t="inlineStr">
         <is>
           <t>Large DNS TCP packets dropped or cause BSOD; DNS security causes perf degradation under load. DNS TCP fix caused BSOD (S1 in review). Large TCP segmented packets dropped in loopback. DNS security causes perf issues on VDI/Citrix.</t>
         </is>
@@ -2503,7 +2509,7 @@
 7. Repeat 1~6 for 20 times</t>
         </is>
       </c>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="F31" s="7" t="inlineStr">
         <is>
           <t>No packet drops for large DNS TCP; no BSOD; DNS latency &lt;100ms under 50-session load on VDI; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2557,7 +2563,7 @@
           <t>Watchdog / Install-Upgrade</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="7" t="inlineStr">
         <is>
           <t>SetUpgradeProgressInReg sets value=1 but UnsetUpgradeInProgressInReg only runs in stopInstallationMonitorService(exit_upgrade=true) path; if MSI fails abnormally registry persists. PR-7878 refactored UpgradeInProgress management; if upgrade crashes between Set and Unset, watchdog skips monitoring (sees isClientUpgradeInProgress=true) indefinitely</t>
         </is>
@@ -2572,7 +2578,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="F32" s="7" t="inlineStr">
         <is>
           <t>After reboot, UpgradeMonitorThread detects aborted upgrade, retries MSI, and clears UpgradeInProgress within 3 hours; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2626,7 +2632,7 @@
           <t>Steering / Config</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="7" t="inlineStr">
         <is>
           <t>Client connects to wrong POP or fails DTLS-to-TLS failover causing performance degradation. 7 GSLB escalations. Repeated pattern: client picks suboptimal DP or DTLS failover to TLS fails, causing outage.</t>
         </is>
@@ -2641,7 +2647,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="F33" s="7" t="inlineStr">
         <is>
           <t>Client selects optimal DP via GSLB; DTLS-to-TLS failover completes within 30s; client returns to DTLS when available; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2695,7 +2701,7 @@
           <t>Config Download / Corruption</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="7" t="inlineStr">
         <is>
           <t>Corrupted nsconfig.json or encrypted config file causes client disable or crash. Config corruption causes silent client disable. Multiple escalations show nsconfig.json corruption and cert deletion crash during re-enrollment.</t>
         </is>
@@ -2710,7 +2716,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="F34" s="7" t="inlineStr">
         <is>
           <t>Client recovers from corrupted config via backup mechanism; cert deletion does not crash service; client re-enrolls automatically; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2764,7 +2770,7 @@
           <t>Install-Upgrade / Schedule</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="7" t="inlineStr">
         <is>
           <t>Scheduled upgrade fails on specific day patterns or interrupted upgrade leaves client removed. 11 Install/Upgrade escalations. Schedule timing (3rd Wed monthly) fails. Interrupted upgrades leave client silently removed.</t>
         </is>
@@ -2780,7 +2786,7 @@
 7. Repeat 1~6 for 5 times</t>
         </is>
       </c>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="F35" s="7" t="inlineStr">
         <is>
           <t>Upgrade triggers on scheduled day; interrupted upgrade recovered by Legacy Monitor; client never left in removed state; consistent results across all 5 repetitions with no degradation</t>
         </is>
@@ -2834,7 +2840,7 @@
           <t>Service Lifecycle / Multi-User</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="7" t="inlineStr">
         <is>
           <t>Simultaneous VDI logons cause tunnel ownership conflict or traffic disruption for existing users. Distinct from FC-02 (FailClose+VDI). These bugs are about tunnel ownership conflicts when users login simultaneously on shared VDI.</t>
         </is>
@@ -2850,7 +2856,7 @@
 7. Repeat 1~6 for 20 times</t>
         </is>
       </c>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="F36" s="7" t="inlineStr">
         <is>
           <t>No traffic disruption for existing sessions during concurrent logon; each user gets correct steering; logout does not break other sessions; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2904,7 +2910,7 @@
           <t>Steering / Secure Enrollment</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="7" t="inlineStr">
         <is>
           <t>IDP enrollment fails on Citrix machines or Autopilot provisioning due to timing/session issues. 5 Secure Enrollment escalations. Citrix+IDP and Autopilot are repeated failure patterns. Concurrent webview2 init causes blank enrollment window.</t>
         </is>
@@ -2920,7 +2926,7 @@
 7. Repeat 1~6 for 20 times</t>
         </is>
       </c>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="F37" s="7" t="inlineStr">
         <is>
           <t>IDP enrollment succeeds on Citrix first login; Autopilot enrollment completes; no blank webview2 windows; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -2974,7 +2980,7 @@
           <t>Steering / CertPinned</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="7" t="inlineStr">
         <is>
           <t>Cert-pinned exception incorrectly causes ALL traffic to bypass instead of only the pinned app. Repeated pattern: cert-pinned exception broadens to bypass all traffic. 4 escalations including regressions from fixes.</t>
         </is>
@@ -2989,7 +2995,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="F38" s="7" t="inlineStr">
         <is>
           <t>Only cert-pinned app traffic bypasses; all other traffic remains steered; config change does not broaden exception scope; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3043,7 +3049,7 @@
           <t>Service Lifecycle / Crash</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="7" t="inlineStr">
         <is>
           <t>Multiple synchronization issues (nsssl::s_sslConns, CTunnelMgr::m_tunnels, async DeviceIoControl) cause crash during service stop or tunnel disconnect. 20+ duplicate/related tickets. Five distinct race conditions in tunnel disconnect path. Affects sleep/wake, network change, multi-user, NPA+SWG combos.</t>
         </is>
@@ -3057,7 +3063,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="F39" s="7" t="inlineStr">
         <is>
           <t>No stAgentSvc crash dumps generated across 50 service stop/start cycles with concurrent network events; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3111,7 +3117,7 @@
           <t>Tunneling / On-Prem Detection</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="7" t="inlineStr">
         <is>
           <t>On-prem detection using egress IP fails or client does not reconnect tunnel after on-prem to off-prem transition. On-prem detection regression (ENG-918451 Missing in Regression). Client fails to reconnect tunnel after egress IP change.</t>
         </is>
@@ -3127,7 +3133,7 @@
 7. Repeat 1~6 for 20 times</t>
         </is>
       </c>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="F40" s="7" t="inlineStr">
         <is>
           <t>On-prem correctly detected via egress IP; off-prem transition triggers tunnel reconnect within 30s; steering resumes; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3181,7 +3187,7 @@
           <t>Install-Upgrade / Silent Removal</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="7" t="inlineStr">
         <is>
           <t>Incorrect upgrade monitor binary path + missing restart logic causes NSClient to be fully uninstalled after reboot during upgrade. stAgentSvcMon cannot start.. Blocker-priority bug affecting 8+ machines at Genpact. Silent removal leaves endpoint completely unprotected.</t>
         </is>
@@ -3195,7 +3201,7 @@
 5. Repeat 1~4 for 5 times</t>
         </is>
       </c>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="F41" s="7" t="inlineStr">
         <is>
           <t>After reboot, installation monitor service detects incomplete upgrade and retries. Client is present and functional; consistent results across all 5 repetitions with no degradation</t>
         </is>
@@ -3249,7 +3255,7 @@
           <t>Driver / AOAC Thread Sync</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="7" t="inlineStr">
         <is>
           <t>Write packet thread starts before driver global settings are initialized after AOAC wake. Null pointer dereference crashes stAgentSvc. No recovery without reboot.. Multiple Blocker bugs for same customer. Day-1 code with missing synchronization. AOAC standby is extremely common on modern laptops.</t>
         </is>
@@ -3264,7 +3270,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="F42" s="7" t="inlineStr">
         <is>
           <t>Service never crashes on wake. Write-packet thread waits for driver initialization. No null pointer access; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3318,7 +3324,7 @@
           <t>Watchdog / Service Lifecycle</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="7" t="inlineStr">
         <is>
           <t>downloadAdminSettings switches FF OFF but RemoveWatchdogMonitorService fails leaving stWatchdog registered and auto-start. PR-7878 adds FF toggle logic in downloadAdminSettings that calls RemoveWatchdogMonitorService; if service is busy it fails silently leaving orphan auto-start entry</t>
         </is>
@@ -3332,7 +3338,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="F43" s="7" t="inlineStr">
         <is>
           <t>stWatchdog service no longer appears in services.msc; UpgradeInProgress registry absent; no orphan stAgentSvcMon.exe on disk; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3386,7 +3392,7 @@
           <t>Watchdog / Service Lifecycle</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>Watchdog sees stAgentSvc in START_PENDING, skips action (PR-7930 fix), but service hangs in PENDING forever with no recovery. PR-7930 added skip for PENDING states; if service permanently stuck in START_PENDING the watchdog will never intervene — infinite no-service state</t>
         </is>
@@ -3400,7 +3406,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="F44" s="7" t="inlineStr">
         <is>
           <t>Watchdog eventually force-kills and restarts the hung service, or escalates via log error after N cycles; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3454,7 +3460,7 @@
           <t>Tunneling / Stress</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="7" t="inlineStr">
         <is>
           <t>NSClient steering creates excessive connections to DC causing CPU exhaustion. SMB connection handling under steering causes DC CPU exhaustion. Distinct from generic connection storm (STRESS-01 tests tunnel, not DC impact).</t>
         </is>
@@ -3469,7 +3475,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="F45" s="7" t="inlineStr">
         <is>
           <t>DC CPU stays below 80% during SMB operations with NSClient; no connection amplification; no client crash; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3523,7 +3529,7 @@
           <t>FailClose / Multi-User VDI</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="7" t="inlineStr">
         <is>
           <t>On multi-user VDI, new user session cannot read nsuser.conf, triggering FailClose for all sessions including working ones. Blocker affecting 1500 users at one customer. FailClose activated due to missing per-user config file on Citrix/AVD shared machines during user logon.</t>
         </is>
@@ -3537,7 +3543,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="F46" s="7" t="inlineStr">
         <is>
           <t>New user session failure to read nsuser.conf does not trigger FailClose for existing active sessions; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3591,7 +3597,7 @@
           <t>Enrollment / IDP Multi-User</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="7" t="inlineStr">
         <is>
           <t>Second user on AVD/VDI gets silently enrolled via UPN before IDP authentication can trigger, bypassing required identity verification. Blocker Tier-1 customer. Security gap: users enrolled without authentication. UPN wins race against IDP on multi-user machines.</t>
         </is>
@@ -3605,7 +3611,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="F47" s="7" t="inlineStr">
         <is>
           <t>Second and subsequent users must complete IDP authentication before enrollment; no silent UPN bypass; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3659,7 +3665,7 @@
           <t>Install-Upgrade / Interrupted Upgrade</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="7" t="inlineStr">
         <is>
           <t>Power failure or reboot during MSI causes nsBinaries Feature to be advertised instead of Local. Subsequent upgrades register success but old binary keeps running.. Critical: 100+ devices at SUN Pharma stuck running old binary while registry shows upgraded version. Silent security gap.</t>
         </is>
@@ -3674,7 +3680,7 @@
 6. Repeat 1~5 for 5 times</t>
         </is>
       </c>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="F48" s="7" t="inlineStr">
         <is>
           <t>After recovery, stAgentSvc runs the new version. No version mismatch between appinfo.log and running binary; consistent results across all 5 repetitions with no degradation</t>
         </is>
@@ -3728,7 +3734,7 @@
           <t>VDI / Multi-Session Race</t>
         </is>
       </c>
-      <c r="D49" s="6" t="inlineStr">
+      <c r="D49" s="7" t="inlineStr">
         <is>
           <t>When multiple users log in before first tunnel connects, nsFilterDevice config reload is skipped. Web traffic routes through outer tunnel instead of inner, bypassing security.. Critical RED-labeled bug at Citizen Bank. All VDI users affected when race occurs. Requires VDI reboot to fix.</t>
         </is>
@@ -3743,7 +3749,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F49" s="6" t="inlineStr">
+      <c r="F49" s="7" t="inlineStr">
         <is>
           <t>nsFilterDevice config reloads correctly regardless of multi-user logon timing. All traffic steered through inner tunnel; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3797,7 +3803,7 @@
           <t>Tunneling / IPv6 Bypass</t>
         </is>
       </c>
-      <c r="D50" s="6" t="inlineStr">
+      <c r="D50" s="7" t="inlineStr">
         <is>
           <t>IPv6 connections without hostname bypass fail-close/steering after network change. m_forceTearDown flag not reset after admin disable/enable cycle.. Blocker: security breach allowing access to blocked websites. Two separate bugs: IPv6 bypass + tearDown flag not reset.</t>
         </is>
@@ -3812,7 +3818,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F50" s="6" t="inlineStr">
+      <c r="F50" s="7" t="inlineStr">
         <is>
           <t>IPv6 traffic without hostname is blocked (not bypassed). m_forceTearDown resets correctly after admin enable; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3866,7 +3872,7 @@
           <t>Service Lifecycle / DeviceIoControl Crash</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
+      <c r="D51" s="7" t="inlineStr">
         <is>
           <t>Synchronous DeviceIoControl() call blocks indefinitely during network switch under fail-close. Service crashes with no recovery. Dead for 5 days until reboot.. Critical RED-labeled bug at JLL (Tier 1). Service crash with 5-day undetected outage. Only reproducible under extended stress.</t>
         </is>
@@ -3880,7 +3886,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F51" s="6" t="inlineStr">
+      <c r="F51" s="7" t="inlineStr">
         <is>
           <t>No service crash during extended network switching. Overlapped IO prevents indefinite DeviceIoControl blocking; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -3934,7 +3940,7 @@
           <t>64-bit Migration / Enrollment</t>
         </is>
       </c>
-      <c r="D52" s="6" t="inlineStr">
+      <c r="D52" s="7" t="inlineStr">
         <is>
           <t>StoreProductVersionsForUpgrade only backs up tokens when is64bitProcess is true; 32-to-64 upgrade path loses tokens. PR-8105 guards backup with 'if(is64bitProcess)' — a 32-bit client upgrading to 64-bit will not backup tokens before RemoveExistingProducts wipes registry</t>
         </is>
@@ -3947,7 +3953,7 @@
 4. Repeat 1~3 for 5 times</t>
         </is>
       </c>
-      <c r="F52" s="6" t="inlineStr">
+      <c r="F52" s="7" t="inlineStr">
         <is>
           <t>AuthenticationToken and EncryptionToken data values exist and match pre-upgrade values; device does not require re-enrollment; consistent results across all 5 repetitions with no degradation</t>
         </is>
@@ -4001,7 +4007,7 @@
           <t>Steering / IPv6</t>
         </is>
       </c>
-      <c r="D53" s="6" t="inlineStr">
+      <c r="D53" s="7" t="inlineStr">
         <is>
           <t>IPv6 traffic not steered or local-link IPv6 exceptions not honored. IPv6 steering gaps on macOS and iOS. Performance degradation with IPv6. Local link exceptions not enforced.</t>
         </is>
@@ -4016,7 +4022,7 @@
 6. Repeat 1~5 for 20 times</t>
         </is>
       </c>
-      <c r="F53" s="6" t="inlineStr">
+      <c r="F53" s="7" t="inlineStr">
         <is>
           <t>IPv6 traffic correctly steered; local-link exceptions honored; IPv6 throughput within 20% of IPv4 baseline; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -4070,7 +4076,7 @@
           <t>Install-Upgrade / AOAC</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
+      <c r="D54" s="7" t="inlineStr">
         <is>
           <t>AOAC power-up event handling blocks SCM callback for 24s, causing service stop token to expire (10s threshold). Upgrade aborts with error 1603 and rolls back.. Blocker-priority bug at Tata Motors, 50-60 machines affected. AOAC+self-protection+upgrade is a common real-world combo.</t>
         </is>
@@ -4084,7 +4090,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F54" s="6" t="inlineStr">
+      <c r="F54" s="7" t="inlineStr">
         <is>
           <t>Upgrade completes within SCM timeout. Service stop token is accepted. No MSI rollback occurs; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -4138,7 +4144,7 @@
           <t>Driver / AOAC Quota Exhaustion</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
+      <c r="D55" s="7" t="inlineStr">
         <is>
           <t>System quota exhaustion (error 1453) causes packet sink thread to exit. Tunnel disconnects with DRIVER_INIT_ERROR, client enters permanent fail-close requiring reboot.. Multiple customers hit this pattern on AOAC devices. Fix adds driver restart on quota error, needs validation under stress.</t>
         </is>
@@ -4152,7 +4158,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F55" s="6" t="inlineStr">
+      <c r="F55" s="7" t="inlineStr">
         <is>
           <t>On quota error, stadrv restarts automatically. Tunnel reconnects without manual intervention. No persistent fail-close state; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -4206,7 +4212,7 @@
           <t>Config Download / Steering Mode Change</t>
         </is>
       </c>
-      <c r="D56" s="6" t="inlineStr">
+      <c r="D56" s="7" t="inlineStr">
         <is>
           <t>Steering mode change (cloud-&gt;web) disconnects tunnel, causing in-flight config downloads (exception.json) to fail. Client enforces new mode without exception list, tunneling bypassed domains.. Critical RED-labeled bug at Concentrix (Tier 1). Multiple users lost access to bypassed domains. Day-1 design gap.</t>
         </is>
@@ -4220,7 +4226,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F56" s="6" t="inlineStr">
+      <c r="F56" s="7" t="inlineStr">
         <is>
           <t>All mandatory config downloads complete before tunnel teardown. No traffic mode enforcement without valid exception list; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -4274,7 +4280,7 @@
           <t>Watchdog / Config</t>
         </is>
       </c>
-      <c r="D57" s="6" t="inlineStr">
+      <c r="D57" s="7" t="inlineStr">
         <is>
           <t>readConfigFile cannot read encrypted nsconfig.json.enc before decryption keys are available; m_WatchdogMonitorEnabled stays false. PR-7957 moved watchdog start from main.cpp into readConfigFile; if encrypted config path fails early the FF never gets set and watchdog never launches</t>
         </is>
@@ -4288,7 +4294,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F57" s="6" t="inlineStr">
+      <c r="F57" s="7" t="inlineStr">
         <is>
           <t>stWatchdog service state is SERVICE_RUNNING; nswatchdog_log shows successful startup entry; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -4342,7 +4348,7 @@
           <t>Driver / DNS Security</t>
         </is>
       </c>
-      <c r="D58" s="6" t="inlineStr">
+      <c r="D58" s="7" t="inlineStr">
         <is>
           <t>Missing synchronization on DNS ports data structure causes kernel crash under multi-session VDI load. Blocker BSOD on Citrix production servers. Race in driver DNS code path. Unique failure shape not covered by DRV-01 (generic driver verifier).</t>
         </is>
@@ -4354,7 +4360,7 @@
 3. Monitor for BSOD/bugcheck events over 4+ hours</t>
         </is>
       </c>
-      <c r="F58" s="6" t="inlineStr">
+      <c r="F58" s="7" t="inlineStr">
         <is>
           <t>No BSOD or kernel crash events after 4 hours of sustained multi-session DNS load</t>
         </is>
@@ -4408,7 +4414,7 @@
           <t>Tunneling / DNS Health Check</t>
         </is>
       </c>
-      <c r="D59" s="6" t="inlineStr">
+      <c r="D59" s="7" t="inlineStr">
         <is>
           <t>Periodic DNS health check resolves deprecated sfchecker host, fails repeatedly, tears down tunnel in a loop. Critical bug blocking production rollout. Tunnel torn down every 3 minutes due to hardcoded health check target being retired.</t>
         </is>
@@ -4420,7 +4426,7 @@
 3. Verify tunnel stability and that DNS health check succeeds against current endpoint (addon host)</t>
         </is>
       </c>
-      <c r="F59" s="6" t="inlineStr">
+      <c r="F59" s="7" t="inlineStr">
         <is>
           <t>Tunnel remains connected without disconnection from DNS health check failures over 2-hour period</t>
         </is>
@@ -4474,7 +4480,7 @@
           <t>Install-Upgrade / Scheduled Upgrade</t>
         </is>
       </c>
-      <c r="D60" s="6" t="inlineStr">
+      <c r="D60" s="7" t="inlineStr">
         <is>
           <t>CScheduledClientUpgradeMgr::isScheduleTimeElapsed() enters infinite loop for certain schedule configurations, hanging the main thread. Blocker: client shows Disabled with no error. Day-1 logic bug in schedule time calculation. 50+ devices affected at one customer.</t>
         </is>
@@ -4487,7 +4493,7 @@
 4. Repeat 1~3 for 5 times</t>
         </is>
       </c>
-      <c r="F60" s="6" t="inlineStr">
+      <c r="F60" s="7" t="inlineStr">
         <is>
           <t>Client remains enabled and functional; scheduled upgrade triggers correctly without hanging; consistent results across all 5 repetitions with no degradation</t>
         </is>
@@ -4541,7 +4547,7 @@
           <t>FailClose / Pre-Login</t>
         </is>
       </c>
-      <c r="D61" s="6" t="inlineStr">
+      <c r="D61" s="7" t="inlineStr">
         <is>
           <t>System account (WsiAccount) triggers FailClose before actual user enrolls; passwordreset.microsoftonline.com blocked at Windows login screen. Blocker: users cannot reset Windows password. FailClose activates for non-enrolled system accounts that log in before real user.</t>
         </is>
@@ -4555,7 +4561,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F61" s="6" t="inlineStr">
+      <c r="F61" s="7" t="inlineStr">
         <is>
           <t>SSPR workflow completes at Windows login screen despite FailClose being configured; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -4609,7 +4615,7 @@
           <t>Config / Secure Validation Race</t>
         </is>
       </c>
-      <c r="D62" s="6" t="inlineStr">
+      <c r="D62" s="7" t="inlineStr">
         <is>
           <t>delete_redis_prioritykey() runs before setting.set() completes, causing 405 validation error on subsequent config downloads. Blocker: steering config cannot download, client has no domain list. Race condition in backend feature flag update sequence.</t>
         </is>
@@ -4623,7 +4629,7 @@
 5. Repeat 1~4 for 20 times</t>
         </is>
       </c>
-      <c r="F62" s="6" t="inlineStr">
+      <c r="F62" s="7" t="inlineStr">
         <is>
           <t>Steering config downloads successfully after feature flag changes; no 405 errors in client logs; consistent results across all 20 repetitions with no degradation</t>
         </is>
@@ -4677,7 +4683,7 @@
           <t>Install-Upgrade / Auto-Upgrade</t>
         </is>
       </c>
-      <c r="D63" s="6" t="inlineStr">
+      <c r="D63" s="7" t="inlineStr">
         <is>
           <t>msiexec upgrade command requires Logs folder under %appdata%\Netskope\stagent but stAgentUI sometimes fails to create it, silently blocking upgrade. Multiple customers stuck on old versions. Silent failure with no error logging. Affects any upgrade path where UI process didn't initialize AppData.</t>
         </is>
@@ -4691,7 +4697,7 @@
 5. Repeat 1~4 for 5 times</t>
         </is>
       </c>
-      <c r="F63" s="6" t="inlineStr">
+      <c r="F63" s="7" t="inlineStr">
         <is>
           <t>Upgrade completes successfully; installer creates missing Logs folder before launching msiexec; consistent results across all 5 repetitions with no degradation</t>
         </is>
@@ -4745,7 +4751,7 @@
           <t>DEM / Crash</t>
         </is>
       </c>
-      <c r="D64" s="6" t="inlineStr">
+      <c r="D64" s="7" t="inlineStr">
         <is>
           <t>Race condition in DeviceStats network event handler causes crash when DEM device health generates frequent events. Crash linked to multiple customer tickets (Lojas Renner, CME Group). Synchronization bug in m_events access. Also triggers FailClose unexpectedly.</t>
         </is>
@@ -4758,7 +4764,7 @@
 4. Verify no unexpected FailClose activations</t>
         </is>
       </c>
-      <c r="F64" s="6" t="inlineStr">
+      <c r="F64" s="7" t="inlineStr">
         <is>
           <t>No crashes and no unexpected FailClose events after 4 hours with DEM device health active under frequent network events</t>
         </is>
@@ -4797,4485 +4803,469 @@
       <c r="Z64" s="6" t="n"/>
     </row>
     <row r="65" ht="15.75" customHeight="1" s="5">
-      <c r="A65" s="6" t="n"/>
-      <c r="B65" s="6" t="n"/>
-      <c r="C65" s="6" t="n"/>
-      <c r="D65" s="6" t="n"/>
-      <c r="E65" s="6" t="n"/>
-      <c r="F65" s="6" t="n"/>
-      <c r="G65" s="6" t="n"/>
-      <c r="H65" s="6" t="n"/>
-      <c r="I65" s="6" t="n"/>
-      <c r="J65" s="6" t="n"/>
-      <c r="K65" s="6" t="n"/>
-      <c r="L65" s="6" t="n"/>
-      <c r="M65" s="6" t="n"/>
-      <c r="N65" s="6" t="n"/>
-      <c r="O65" s="6" t="n"/>
-      <c r="P65" s="6" t="n"/>
-      <c r="Q65" s="6" t="n"/>
-      <c r="R65" s="6" t="n"/>
-      <c r="S65" s="6" t="n"/>
-      <c r="T65" s="6" t="n"/>
-      <c r="U65" s="6" t="n"/>
-      <c r="V65" s="6" t="n"/>
-      <c r="W65" s="6" t="n"/>
-      <c r="X65" s="6" t="n"/>
-      <c r="Y65" s="6" t="n"/>
-      <c r="Z65" s="6" t="n"/>
+      <c r="A65" s="0" t="inlineStr">
+        <is>
+          <t>WD-03</t>
+        </is>
+      </c>
+      <c r="B65" s="0" t="inlineStr">
+        <is>
+          <t>Watchdog Crash &amp; Self-Recovery</t>
+        </is>
+      </c>
+      <c r="C65" s="0" t="inlineStr">
+        <is>
+          <t>Watchdog / Resilience</t>
+        </is>
+      </c>
+      <c r="D65" s="9" t="inlineStr">
+        <is>
+          <t>Crash the watchdog process and verify it self-recovers (or the service notices and signals).</t>
+        </is>
+      </c>
+      <c r="E65" s="9" t="inlineStr">
+        <is>
+          <t>1. Watchdog and main service both running
+2. SIGKILL the watchdog process
+3. Wait 60s
+4. Verify watchdog auto-restarts (via Windows service recovery / systemd Restart=)
+5. Re-test STRESS-05 service kill — watchdog must still restart service</t>
+        </is>
+      </c>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Watchdog restarts ≤30s. Subsequent service-kill recovery still works.</t>
+        </is>
+      </c>
+      <c r="G65" s="0" t="inlineStr">
+        <is>
+          <t>Watchdog down + service crash = endpoint dead, no auto-recovery.</t>
+        </is>
+      </c>
+      <c r="H65" s="0" t="inlineStr">
+        <is>
+          <t>Watchdog escalation bugs.</t>
+        </is>
+      </c>
+      <c r="I65" s="0" t="inlineStr">
+        <is>
+          <t>ch21_watchdog.md</t>
+        </is>
+      </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" s="5">
-      <c r="A66" s="6" t="n"/>
-      <c r="B66" s="6" t="n"/>
-      <c r="C66" s="6" t="n"/>
-      <c r="D66" s="6" t="n"/>
-      <c r="E66" s="6" t="n"/>
-      <c r="F66" s="6" t="n"/>
-      <c r="G66" s="6" t="n"/>
-      <c r="H66" s="6" t="n"/>
-      <c r="I66" s="6" t="n"/>
-      <c r="J66" s="6" t="n"/>
-      <c r="K66" s="6" t="n"/>
-      <c r="L66" s="6" t="n"/>
-      <c r="M66" s="6" t="n"/>
-      <c r="N66" s="6" t="n"/>
-      <c r="O66" s="6" t="n"/>
-      <c r="P66" s="6" t="n"/>
-      <c r="Q66" s="6" t="n"/>
-      <c r="R66" s="6" t="n"/>
-      <c r="S66" s="6" t="n"/>
-      <c r="T66" s="6" t="n"/>
-      <c r="U66" s="6" t="n"/>
-      <c r="V66" s="6" t="n"/>
-      <c r="W66" s="6" t="n"/>
-      <c r="X66" s="6" t="n"/>
-      <c r="Y66" s="6" t="n"/>
-      <c r="Z66" s="6" t="n"/>
+      <c r="A66" s="0" t="inlineStr">
+        <is>
+          <t>NPA-01</t>
+        </is>
+      </c>
+      <c r="B66" s="0" t="inlineStr">
+        <is>
+          <t>NPA Tunnel Loss + Re-establish</t>
+        </is>
+      </c>
+      <c r="C66" s="0" t="inlineStr">
+        <is>
+          <t>Tunneling / NPA</t>
+        </is>
+      </c>
+      <c r="D66" s="9" t="inlineStr">
+        <is>
+          <t>Drop the NPA tunnel mid-traffic and verify private-app connectivity recovers.</t>
+        </is>
+      </c>
+      <c r="E66" s="9" t="inlineStr">
+        <is>
+          <t>1. NPA tunnel up, accessing private app
+2. Block NPA broker IP via firewall
+3. Verify private-app traffic blocked (not silently routed elsewhere)
+4. Unblock — verify NPA reconnects ≤60s and traffic resumes</t>
+        </is>
+      </c>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Private-app traffic stops on NPA loss. Reconnect ≤60s. No leak to public path during outage.</t>
+        </is>
+      </c>
+      <c r="G66" s="0" t="inlineStr">
+        <is>
+          <t>Private-app traffic leaks during outage (security gap) OR never recovers (productivity loss).</t>
+        </is>
+      </c>
+      <c r="H66" s="0" t="inlineStr">
+        <is>
+          <t>IMF-1043 (NPA tunnel).</t>
+        </is>
+      </c>
+      <c r="I66" s="0" t="inlineStr">
+        <is>
+          <t>ch15_npa_integration.md, ch07_tunnel_management.md</t>
+        </is>
+      </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" s="5">
-      <c r="A67" s="6" t="n"/>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-      <c r="E67" s="6" t="n"/>
-      <c r="F67" s="6" t="n"/>
-      <c r="G67" s="6" t="n"/>
-      <c r="H67" s="6" t="n"/>
-      <c r="I67" s="6" t="n"/>
-      <c r="J67" s="6" t="n"/>
-      <c r="K67" s="6" t="n"/>
-      <c r="L67" s="6" t="n"/>
-      <c r="M67" s="6" t="n"/>
-      <c r="N67" s="6" t="n"/>
-      <c r="O67" s="6" t="n"/>
-      <c r="P67" s="6" t="n"/>
-      <c r="Q67" s="6" t="n"/>
-      <c r="R67" s="6" t="n"/>
-      <c r="S67" s="6" t="n"/>
-      <c r="T67" s="6" t="n"/>
-      <c r="U67" s="6" t="n"/>
-      <c r="V67" s="6" t="n"/>
-      <c r="W67" s="6" t="n"/>
-      <c r="X67" s="6" t="n"/>
-      <c r="Y67" s="6" t="n"/>
-      <c r="Z67" s="6" t="n"/>
+      <c r="A67" s="0" t="inlineStr">
+        <is>
+          <t>DC-01</t>
+        </is>
+      </c>
+      <c r="B67" s="0" t="inlineStr">
+        <is>
+          <t>Device Classification Vault Deletion</t>
+        </is>
+      </c>
+      <c r="C67" s="0" t="inlineStr">
+        <is>
+          <t>Driver / Kernel Integrity</t>
+        </is>
+      </c>
+      <c r="D67" s="9" t="inlineStr">
+        <is>
+          <t>Delete DC vault keys and verify graceful failure mode (not silent classification bypass).</t>
+        </is>
+      </c>
+      <c r="E67" s="9" t="inlineStr">
+        <is>
+          <t>1. Healthy DC posture, device classified
+2. Service stopped
+3. Delete vault keys from disk
+4. Start service
+5. Verify classification falls back to 'unknown' (not 'trusted')
+6. Verify user prompted or policy enforced for unknown posture</t>
+        </is>
+      </c>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Posture = unknown after vault deletion. No trusted bypass. Policy enforces unknown-device rule.</t>
+        </is>
+      </c>
+      <c r="G67" s="0" t="inlineStr">
+        <is>
+          <t>Posture wrongly retained → trusted bypass on tampered device.</t>
+        </is>
+      </c>
+      <c r="H67" s="0" t="inlineStr">
+        <is>
+          <t>IMF-925 (vault/DB deletion breaks DC).</t>
+        </is>
+      </c>
+      <c r="I67" s="0" t="inlineStr">
+        <is>
+          <t>ch12_device_classification.md</t>
+        </is>
+      </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" s="5">
-      <c r="A68" s="6" t="n"/>
-      <c r="B68" s="6" t="n"/>
-      <c r="C68" s="6" t="n"/>
-      <c r="D68" s="6" t="n"/>
-      <c r="E68" s="6" t="n"/>
-      <c r="F68" s="6" t="n"/>
-      <c r="G68" s="6" t="n"/>
-      <c r="H68" s="6" t="n"/>
-      <c r="I68" s="6" t="n"/>
-      <c r="J68" s="6" t="n"/>
-      <c r="K68" s="6" t="n"/>
-      <c r="L68" s="6" t="n"/>
-      <c r="M68" s="6" t="n"/>
-      <c r="N68" s="6" t="n"/>
-      <c r="O68" s="6" t="n"/>
-      <c r="P68" s="6" t="n"/>
-      <c r="Q68" s="6" t="n"/>
-      <c r="R68" s="6" t="n"/>
-      <c r="S68" s="6" t="n"/>
-      <c r="T68" s="6" t="n"/>
-      <c r="U68" s="6" t="n"/>
-      <c r="V68" s="6" t="n"/>
-      <c r="W68" s="6" t="n"/>
-      <c r="X68" s="6" t="n"/>
-      <c r="Y68" s="6" t="n"/>
-      <c r="Z68" s="6" t="n"/>
+      <c r="A68" s="0" t="inlineStr">
+        <is>
+          <t>INTEROP-01</t>
+        </is>
+      </c>
+      <c r="B68" s="0" t="inlineStr">
+        <is>
+          <t>Cisco AnyConnect Coexistence — FailClose Swap</t>
+        </is>
+      </c>
+      <c r="C68" s="0" t="inlineStr">
+        <is>
+          <t>FailClose / Network</t>
+        </is>
+      </c>
+      <c r="D68" s="9" t="inlineStr">
+        <is>
+          <t>Run AnyConnect alongside Netskope and toggle AnyConnect VPN up/down. Verify FailClose handles the swap correctly.</t>
+        </is>
+      </c>
+      <c r="E68" s="9" t="inlineStr">
+        <is>
+          <t>1. Both clients installed, Netskope tunnel up, AnyConnect down
+2. Connect AnyConnect (full or split tunnel)
+3. Verify Netskope adapts (split: continues; full: graceful tunnel handoff or FailClose engage per policy)
+4. Disconnect AnyConnect — verify Netskope resumes ≤60s</t>
+        </is>
+      </c>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>No BSOD. FailClose state matches policy. Netskope resumes ≤60s post-AnyConnect-disconnect.</t>
+        </is>
+      </c>
+      <c r="G68" s="0" t="inlineStr">
+        <is>
+          <t>Conflict between WFP layers → BSOD or permanent traffic blackout. False FailClose on swap.</t>
+        </is>
+      </c>
+      <c r="H68" s="0" t="inlineStr">
+        <is>
+          <t>ENG-991833 (FailClose + IPSec/VPN swap, enableFCOnNetworkDisconnect flag).</t>
+        </is>
+      </c>
+      <c r="I68" s="0" t="inlineStr">
+        <is>
+          <t>plan-9002-interop-test.md, ch11_failclose.md</t>
+        </is>
+      </c>
     </row>
     <row r="69" ht="15.75" customHeight="1" s="5">
-      <c r="A69" s="6" t="n"/>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-      <c r="E69" s="6" t="n"/>
-      <c r="F69" s="6" t="n"/>
-      <c r="G69" s="6" t="n"/>
-      <c r="H69" s="6" t="n"/>
-      <c r="I69" s="6" t="n"/>
-      <c r="J69" s="6" t="n"/>
-      <c r="K69" s="6" t="n"/>
-      <c r="L69" s="6" t="n"/>
-      <c r="M69" s="6" t="n"/>
-      <c r="N69" s="6" t="n"/>
-      <c r="O69" s="6" t="n"/>
-      <c r="P69" s="6" t="n"/>
-      <c r="Q69" s="6" t="n"/>
-      <c r="R69" s="6" t="n"/>
-      <c r="S69" s="6" t="n"/>
-      <c r="T69" s="6" t="n"/>
-      <c r="U69" s="6" t="n"/>
-      <c r="V69" s="6" t="n"/>
-      <c r="W69" s="6" t="n"/>
-      <c r="X69" s="6" t="n"/>
-      <c r="Y69" s="6" t="n"/>
-      <c r="Z69" s="6" t="n"/>
+      <c r="A69" s="0" t="inlineStr">
+        <is>
+          <t>INTEROP-02</t>
+        </is>
+      </c>
+      <c r="B69" s="0" t="inlineStr">
+        <is>
+          <t>CrowdStrike Kernel Sensor Coexistence</t>
+        </is>
+      </c>
+      <c r="C69" s="0" t="inlineStr">
+        <is>
+          <t>Driver / Kernel Integrity</t>
+        </is>
+      </c>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>Stress driver path with CrowdStrike falcon-sensor active. Verify no WFP/kernel-callback collisions.</t>
+        </is>
+      </c>
+      <c r="E69" s="9" t="inlineStr">
+        <is>
+          <t>1. Install CrowdStrike sensor + Netskope client
+2. Run STRESS-01 (connection storm) with both kernel modules active
+3. Monitor for BSOD, dropped packets, sensor blocking driver load
+4. Verify both products report healthy</t>
+        </is>
+      </c>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>No BSOD. Both products healthy. Connection storm completes per STRESS-01 PC.</t>
+        </is>
+      </c>
+      <c r="G69" s="0" t="inlineStr">
+        <is>
+          <t>BSOD at scale — fleet-wide outage.</t>
+        </is>
+      </c>
+      <c r="H69" s="0" t="inlineStr">
+        <is>
+          <t>Kernel-sensor coexistence escalation bugs.</t>
+        </is>
+      </c>
+      <c r="I69" s="0" t="inlineStr">
+        <is>
+          <t>plan-9002-interop-test.md, ch18_security.md</t>
+        </is>
+      </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" s="5">
-      <c r="A70" s="6" t="n"/>
-      <c r="B70" s="6" t="n"/>
-      <c r="C70" s="6" t="n"/>
-      <c r="D70" s="6" t="n"/>
-      <c r="E70" s="6" t="n"/>
-      <c r="F70" s="6" t="n"/>
-      <c r="G70" s="6" t="n"/>
-      <c r="H70" s="6" t="n"/>
-      <c r="I70" s="6" t="n"/>
-      <c r="J70" s="6" t="n"/>
-      <c r="K70" s="6" t="n"/>
-      <c r="L70" s="6" t="n"/>
-      <c r="M70" s="6" t="n"/>
-      <c r="N70" s="6" t="n"/>
-      <c r="O70" s="6" t="n"/>
-      <c r="P70" s="6" t="n"/>
-      <c r="Q70" s="6" t="n"/>
-      <c r="R70" s="6" t="n"/>
-      <c r="S70" s="6" t="n"/>
-      <c r="T70" s="6" t="n"/>
-      <c r="U70" s="6" t="n"/>
-      <c r="V70" s="6" t="n"/>
-      <c r="W70" s="6" t="n"/>
-      <c r="X70" s="6" t="n"/>
-      <c r="Y70" s="6" t="n"/>
-      <c r="Z70" s="6" t="n"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" s="5">
-      <c r="A71" s="6" t="n"/>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-      <c r="E71" s="6" t="n"/>
-      <c r="F71" s="6" t="n"/>
-      <c r="G71" s="6" t="n"/>
-      <c r="H71" s="6" t="n"/>
-      <c r="I71" s="6" t="n"/>
-      <c r="J71" s="6" t="n"/>
-      <c r="K71" s="6" t="n"/>
-      <c r="L71" s="6" t="n"/>
-      <c r="M71" s="6" t="n"/>
-      <c r="N71" s="6" t="n"/>
-      <c r="O71" s="6" t="n"/>
-      <c r="P71" s="6" t="n"/>
-      <c r="Q71" s="6" t="n"/>
-      <c r="R71" s="6" t="n"/>
-      <c r="S71" s="6" t="n"/>
-      <c r="T71" s="6" t="n"/>
-      <c r="U71" s="6" t="n"/>
-      <c r="V71" s="6" t="n"/>
-      <c r="W71" s="6" t="n"/>
-      <c r="X71" s="6" t="n"/>
-      <c r="Y71" s="6" t="n"/>
-      <c r="Z71" s="6" t="n"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" s="5">
-      <c r="A72" s="6" t="n"/>
-      <c r="B72" s="6" t="n"/>
-      <c r="C72" s="6" t="n"/>
-      <c r="D72" s="6" t="n"/>
-      <c r="E72" s="6" t="n"/>
-      <c r="F72" s="6" t="n"/>
-      <c r="G72" s="6" t="n"/>
-      <c r="H72" s="6" t="n"/>
-      <c r="I72" s="6" t="n"/>
-      <c r="J72" s="6" t="n"/>
-      <c r="K72" s="6" t="n"/>
-      <c r="L72" s="6" t="n"/>
-      <c r="M72" s="6" t="n"/>
-      <c r="N72" s="6" t="n"/>
-      <c r="O72" s="6" t="n"/>
-      <c r="P72" s="6" t="n"/>
-      <c r="Q72" s="6" t="n"/>
-      <c r="R72" s="6" t="n"/>
-      <c r="S72" s="6" t="n"/>
-      <c r="T72" s="6" t="n"/>
-      <c r="U72" s="6" t="n"/>
-      <c r="V72" s="6" t="n"/>
-      <c r="W72" s="6" t="n"/>
-      <c r="X72" s="6" t="n"/>
-      <c r="Y72" s="6" t="n"/>
-      <c r="Z72" s="6" t="n"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" s="5">
-      <c r="A73" s="6" t="n"/>
-      <c r="B73" s="6" t="n"/>
-      <c r="C73" s="6" t="n"/>
-      <c r="D73" s="6" t="n"/>
-      <c r="E73" s="6" t="n"/>
-      <c r="F73" s="6" t="n"/>
-      <c r="G73" s="6" t="n"/>
-      <c r="H73" s="6" t="n"/>
-      <c r="I73" s="6" t="n"/>
-      <c r="J73" s="6" t="n"/>
-      <c r="K73" s="6" t="n"/>
-      <c r="L73" s="6" t="n"/>
-      <c r="M73" s="6" t="n"/>
-      <c r="N73" s="6" t="n"/>
-      <c r="O73" s="6" t="n"/>
-      <c r="P73" s="6" t="n"/>
-      <c r="Q73" s="6" t="n"/>
-      <c r="R73" s="6" t="n"/>
-      <c r="S73" s="6" t="n"/>
-      <c r="T73" s="6" t="n"/>
-      <c r="U73" s="6" t="n"/>
-      <c r="V73" s="6" t="n"/>
-      <c r="W73" s="6" t="n"/>
-      <c r="X73" s="6" t="n"/>
-      <c r="Y73" s="6" t="n"/>
-      <c r="Z73" s="6" t="n"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1" s="5">
-      <c r="A74" s="6" t="n"/>
-      <c r="B74" s="6" t="n"/>
-      <c r="C74" s="6" t="n"/>
-      <c r="D74" s="6" t="n"/>
-      <c r="E74" s="6" t="n"/>
-      <c r="F74" s="6" t="n"/>
-      <c r="G74" s="6" t="n"/>
-      <c r="H74" s="6" t="n"/>
-      <c r="I74" s="6" t="n"/>
-      <c r="J74" s="6" t="n"/>
-      <c r="K74" s="6" t="n"/>
-      <c r="L74" s="6" t="n"/>
-      <c r="M74" s="6" t="n"/>
-      <c r="N74" s="6" t="n"/>
-      <c r="O74" s="6" t="n"/>
-      <c r="P74" s="6" t="n"/>
-      <c r="Q74" s="6" t="n"/>
-      <c r="R74" s="6" t="n"/>
-      <c r="S74" s="6" t="n"/>
-      <c r="T74" s="6" t="n"/>
-      <c r="U74" s="6" t="n"/>
-      <c r="V74" s="6" t="n"/>
-      <c r="W74" s="6" t="n"/>
-      <c r="X74" s="6" t="n"/>
-      <c r="Y74" s="6" t="n"/>
-      <c r="Z74" s="6" t="n"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" s="5">
-      <c r="A75" s="6" t="n"/>
-      <c r="B75" s="6" t="n"/>
-      <c r="C75" s="6" t="n"/>
-      <c r="D75" s="6" t="n"/>
-      <c r="E75" s="6" t="n"/>
-      <c r="F75" s="6" t="n"/>
-      <c r="G75" s="6" t="n"/>
-      <c r="H75" s="6" t="n"/>
-      <c r="I75" s="6" t="n"/>
-      <c r="J75" s="6" t="n"/>
-      <c r="K75" s="6" t="n"/>
-      <c r="L75" s="6" t="n"/>
-      <c r="M75" s="6" t="n"/>
-      <c r="N75" s="6" t="n"/>
-      <c r="O75" s="6" t="n"/>
-      <c r="P75" s="6" t="n"/>
-      <c r="Q75" s="6" t="n"/>
-      <c r="R75" s="6" t="n"/>
-      <c r="S75" s="6" t="n"/>
-      <c r="T75" s="6" t="n"/>
-      <c r="U75" s="6" t="n"/>
-      <c r="V75" s="6" t="n"/>
-      <c r="W75" s="6" t="n"/>
-      <c r="X75" s="6" t="n"/>
-      <c r="Y75" s="6" t="n"/>
-      <c r="Z75" s="6" t="n"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1" s="5">
-      <c r="A76" s="6" t="n"/>
-      <c r="B76" s="6" t="n"/>
-      <c r="C76" s="6" t="n"/>
-      <c r="D76" s="6" t="n"/>
-      <c r="E76" s="6" t="n"/>
-      <c r="F76" s="6" t="n"/>
-      <c r="G76" s="6" t="n"/>
-      <c r="H76" s="6" t="n"/>
-      <c r="I76" s="6" t="n"/>
-      <c r="J76" s="6" t="n"/>
-      <c r="K76" s="6" t="n"/>
-      <c r="L76" s="6" t="n"/>
-      <c r="M76" s="6" t="n"/>
-      <c r="N76" s="6" t="n"/>
-      <c r="O76" s="6" t="n"/>
-      <c r="P76" s="6" t="n"/>
-      <c r="Q76" s="6" t="n"/>
-      <c r="R76" s="6" t="n"/>
-      <c r="S76" s="6" t="n"/>
-      <c r="T76" s="6" t="n"/>
-      <c r="U76" s="6" t="n"/>
-      <c r="V76" s="6" t="n"/>
-      <c r="W76" s="6" t="n"/>
-      <c r="X76" s="6" t="n"/>
-      <c r="Y76" s="6" t="n"/>
-      <c r="Z76" s="6" t="n"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" s="5">
-      <c r="A77" s="6" t="n"/>
-      <c r="B77" s="6" t="n"/>
-      <c r="C77" s="6" t="n"/>
-      <c r="D77" s="6" t="n"/>
-      <c r="E77" s="6" t="n"/>
-      <c r="F77" s="6" t="n"/>
-      <c r="G77" s="6" t="n"/>
-      <c r="H77" s="6" t="n"/>
-      <c r="I77" s="6" t="n"/>
-      <c r="J77" s="6" t="n"/>
-      <c r="K77" s="6" t="n"/>
-      <c r="L77" s="6" t="n"/>
-      <c r="M77" s="6" t="n"/>
-      <c r="N77" s="6" t="n"/>
-      <c r="O77" s="6" t="n"/>
-      <c r="P77" s="6" t="n"/>
-      <c r="Q77" s="6" t="n"/>
-      <c r="R77" s="6" t="n"/>
-      <c r="S77" s="6" t="n"/>
-      <c r="T77" s="6" t="n"/>
-      <c r="U77" s="6" t="n"/>
-      <c r="V77" s="6" t="n"/>
-      <c r="W77" s="6" t="n"/>
-      <c r="X77" s="6" t="n"/>
-      <c r="Y77" s="6" t="n"/>
-      <c r="Z77" s="6" t="n"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1" s="5">
-      <c r="A78" s="6" t="n"/>
-      <c r="B78" s="6" t="n"/>
-      <c r="C78" s="6" t="n"/>
-      <c r="D78" s="6" t="n"/>
-      <c r="E78" s="6" t="n"/>
-      <c r="F78" s="6" t="n"/>
-      <c r="G78" s="6" t="n"/>
-      <c r="H78" s="6" t="n"/>
-      <c r="I78" s="6" t="n"/>
-      <c r="J78" s="6" t="n"/>
-      <c r="K78" s="6" t="n"/>
-      <c r="L78" s="6" t="n"/>
-      <c r="M78" s="6" t="n"/>
-      <c r="N78" s="6" t="n"/>
-      <c r="O78" s="6" t="n"/>
-      <c r="P78" s="6" t="n"/>
-      <c r="Q78" s="6" t="n"/>
-      <c r="R78" s="6" t="n"/>
-      <c r="S78" s="6" t="n"/>
-      <c r="T78" s="6" t="n"/>
-      <c r="U78" s="6" t="n"/>
-      <c r="V78" s="6" t="n"/>
-      <c r="W78" s="6" t="n"/>
-      <c r="X78" s="6" t="n"/>
-      <c r="Y78" s="6" t="n"/>
-      <c r="Z78" s="6" t="n"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" s="5">
-      <c r="A79" s="6" t="n"/>
-      <c r="B79" s="6" t="n"/>
-      <c r="C79" s="6" t="n"/>
-      <c r="D79" s="6" t="n"/>
-      <c r="E79" s="6" t="n"/>
-      <c r="F79" s="6" t="n"/>
-      <c r="G79" s="6" t="n"/>
-      <c r="H79" s="6" t="n"/>
-      <c r="I79" s="6" t="n"/>
-      <c r="J79" s="6" t="n"/>
-      <c r="K79" s="6" t="n"/>
-      <c r="L79" s="6" t="n"/>
-      <c r="M79" s="6" t="n"/>
-      <c r="N79" s="6" t="n"/>
-      <c r="O79" s="6" t="n"/>
-      <c r="P79" s="6" t="n"/>
-      <c r="Q79" s="6" t="n"/>
-      <c r="R79" s="6" t="n"/>
-      <c r="S79" s="6" t="n"/>
-      <c r="T79" s="6" t="n"/>
-      <c r="U79" s="6" t="n"/>
-      <c r="V79" s="6" t="n"/>
-      <c r="W79" s="6" t="n"/>
-      <c r="X79" s="6" t="n"/>
-      <c r="Y79" s="6" t="n"/>
-      <c r="Z79" s="6" t="n"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" s="5">
-      <c r="A80" s="6" t="n"/>
-      <c r="B80" s="6" t="n"/>
-      <c r="C80" s="6" t="n"/>
-      <c r="D80" s="6" t="n"/>
-      <c r="E80" s="6" t="n"/>
-      <c r="F80" s="6" t="n"/>
-      <c r="G80" s="6" t="n"/>
-      <c r="H80" s="6" t="n"/>
-      <c r="I80" s="6" t="n"/>
-      <c r="J80" s="6" t="n"/>
-      <c r="K80" s="6" t="n"/>
-      <c r="L80" s="6" t="n"/>
-      <c r="M80" s="6" t="n"/>
-      <c r="N80" s="6" t="n"/>
-      <c r="O80" s="6" t="n"/>
-      <c r="P80" s="6" t="n"/>
-      <c r="Q80" s="6" t="n"/>
-      <c r="R80" s="6" t="n"/>
-      <c r="S80" s="6" t="n"/>
-      <c r="T80" s="6" t="n"/>
-      <c r="U80" s="6" t="n"/>
-      <c r="V80" s="6" t="n"/>
-      <c r="W80" s="6" t="n"/>
-      <c r="X80" s="6" t="n"/>
-      <c r="Y80" s="6" t="n"/>
-      <c r="Z80" s="6" t="n"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" s="5">
-      <c r="A81" s="6" t="n"/>
-      <c r="B81" s="6" t="n"/>
-      <c r="C81" s="6" t="n"/>
-      <c r="D81" s="6" t="n"/>
-      <c r="E81" s="6" t="n"/>
-      <c r="F81" s="6" t="n"/>
-      <c r="G81" s="6" t="n"/>
-      <c r="H81" s="6" t="n"/>
-      <c r="I81" s="6" t="n"/>
-      <c r="J81" s="6" t="n"/>
-      <c r="K81" s="6" t="n"/>
-      <c r="L81" s="6" t="n"/>
-      <c r="M81" s="6" t="n"/>
-      <c r="N81" s="6" t="n"/>
-      <c r="O81" s="6" t="n"/>
-      <c r="P81" s="6" t="n"/>
-      <c r="Q81" s="6" t="n"/>
-      <c r="R81" s="6" t="n"/>
-      <c r="S81" s="6" t="n"/>
-      <c r="T81" s="6" t="n"/>
-      <c r="U81" s="6" t="n"/>
-      <c r="V81" s="6" t="n"/>
-      <c r="W81" s="6" t="n"/>
-      <c r="X81" s="6" t="n"/>
-      <c r="Y81" s="6" t="n"/>
-      <c r="Z81" s="6" t="n"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1" s="5">
-      <c r="A82" s="6" t="n"/>
-      <c r="B82" s="6" t="n"/>
-      <c r="C82" s="6" t="n"/>
-      <c r="D82" s="6" t="n"/>
-      <c r="E82" s="6" t="n"/>
-      <c r="F82" s="6" t="n"/>
-      <c r="G82" s="6" t="n"/>
-      <c r="H82" s="6" t="n"/>
-      <c r="I82" s="6" t="n"/>
-      <c r="J82" s="6" t="n"/>
-      <c r="K82" s="6" t="n"/>
-      <c r="L82" s="6" t="n"/>
-      <c r="M82" s="6" t="n"/>
-      <c r="N82" s="6" t="n"/>
-      <c r="O82" s="6" t="n"/>
-      <c r="P82" s="6" t="n"/>
-      <c r="Q82" s="6" t="n"/>
-      <c r="R82" s="6" t="n"/>
-      <c r="S82" s="6" t="n"/>
-      <c r="T82" s="6" t="n"/>
-      <c r="U82" s="6" t="n"/>
-      <c r="V82" s="6" t="n"/>
-      <c r="W82" s="6" t="n"/>
-      <c r="X82" s="6" t="n"/>
-      <c r="Y82" s="6" t="n"/>
-      <c r="Z82" s="6" t="n"/>
-    </row>
-    <row r="83" ht="15.75" customHeight="1" s="5">
-      <c r="A83" s="6" t="n"/>
-      <c r="B83" s="6" t="n"/>
-      <c r="C83" s="6" t="n"/>
-      <c r="D83" s="6" t="n"/>
-      <c r="E83" s="6" t="n"/>
-      <c r="F83" s="6" t="n"/>
-      <c r="G83" s="6" t="n"/>
-      <c r="H83" s="6" t="n"/>
-      <c r="I83" s="6" t="n"/>
-      <c r="J83" s="6" t="n"/>
-      <c r="K83" s="6" t="n"/>
-      <c r="L83" s="6" t="n"/>
-      <c r="M83" s="6" t="n"/>
-      <c r="N83" s="6" t="n"/>
-      <c r="O83" s="6" t="n"/>
-      <c r="P83" s="6" t="n"/>
-      <c r="Q83" s="6" t="n"/>
-      <c r="R83" s="6" t="n"/>
-      <c r="S83" s="6" t="n"/>
-      <c r="T83" s="6" t="n"/>
-      <c r="U83" s="6" t="n"/>
-      <c r="V83" s="6" t="n"/>
-      <c r="W83" s="6" t="n"/>
-      <c r="X83" s="6" t="n"/>
-      <c r="Y83" s="6" t="n"/>
-      <c r="Z83" s="6" t="n"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1" s="5">
-      <c r="A84" s="6" t="n"/>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6" t="n"/>
-      <c r="E84" s="6" t="n"/>
-      <c r="F84" s="6" t="n"/>
-      <c r="G84" s="6" t="n"/>
-      <c r="H84" s="6" t="n"/>
-      <c r="I84" s="6" t="n"/>
-      <c r="J84" s="6" t="n"/>
-      <c r="K84" s="6" t="n"/>
-      <c r="L84" s="6" t="n"/>
-      <c r="M84" s="6" t="n"/>
-      <c r="N84" s="6" t="n"/>
-      <c r="O84" s="6" t="n"/>
-      <c r="P84" s="6" t="n"/>
-      <c r="Q84" s="6" t="n"/>
-      <c r="R84" s="6" t="n"/>
-      <c r="S84" s="6" t="n"/>
-      <c r="T84" s="6" t="n"/>
-      <c r="U84" s="6" t="n"/>
-      <c r="V84" s="6" t="n"/>
-      <c r="W84" s="6" t="n"/>
-      <c r="X84" s="6" t="n"/>
-      <c r="Y84" s="6" t="n"/>
-      <c r="Z84" s="6" t="n"/>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" s="5">
-      <c r="A85" s="6" t="n"/>
-      <c r="B85" s="6" t="n"/>
-      <c r="C85" s="6" t="n"/>
-      <c r="D85" s="6" t="n"/>
-      <c r="E85" s="6" t="n"/>
-      <c r="F85" s="6" t="n"/>
-      <c r="G85" s="6" t="n"/>
-      <c r="H85" s="6" t="n"/>
-      <c r="I85" s="6" t="n"/>
-      <c r="J85" s="6" t="n"/>
-      <c r="K85" s="6" t="n"/>
-      <c r="L85" s="6" t="n"/>
-      <c r="M85" s="6" t="n"/>
-      <c r="N85" s="6" t="n"/>
-      <c r="O85" s="6" t="n"/>
-      <c r="P85" s="6" t="n"/>
-      <c r="Q85" s="6" t="n"/>
-      <c r="R85" s="6" t="n"/>
-      <c r="S85" s="6" t="n"/>
-      <c r="T85" s="6" t="n"/>
-      <c r="U85" s="6" t="n"/>
-      <c r="V85" s="6" t="n"/>
-      <c r="W85" s="6" t="n"/>
-      <c r="X85" s="6" t="n"/>
-      <c r="Y85" s="6" t="n"/>
-      <c r="Z85" s="6" t="n"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" s="5">
-      <c r="A86" s="6" t="n"/>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-      <c r="E86" s="6" t="n"/>
-      <c r="F86" s="6" t="n"/>
-      <c r="G86" s="6" t="n"/>
-      <c r="H86" s="6" t="n"/>
-      <c r="I86" s="6" t="n"/>
-      <c r="J86" s="6" t="n"/>
-      <c r="K86" s="6" t="n"/>
-      <c r="L86" s="6" t="n"/>
-      <c r="M86" s="6" t="n"/>
-      <c r="N86" s="6" t="n"/>
-      <c r="O86" s="6" t="n"/>
-      <c r="P86" s="6" t="n"/>
-      <c r="Q86" s="6" t="n"/>
-      <c r="R86" s="6" t="n"/>
-      <c r="S86" s="6" t="n"/>
-      <c r="T86" s="6" t="n"/>
-      <c r="U86" s="6" t="n"/>
-      <c r="V86" s="6" t="n"/>
-      <c r="W86" s="6" t="n"/>
-      <c r="X86" s="6" t="n"/>
-      <c r="Y86" s="6" t="n"/>
-      <c r="Z86" s="6" t="n"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" s="5">
-      <c r="A87" s="6" t="n"/>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="F87" s="6" t="n"/>
-      <c r="G87" s="6" t="n"/>
-      <c r="H87" s="6" t="n"/>
-      <c r="I87" s="6" t="n"/>
-      <c r="J87" s="6" t="n"/>
-      <c r="K87" s="6" t="n"/>
-      <c r="L87" s="6" t="n"/>
-      <c r="M87" s="6" t="n"/>
-      <c r="N87" s="6" t="n"/>
-      <c r="O87" s="6" t="n"/>
-      <c r="P87" s="6" t="n"/>
-      <c r="Q87" s="6" t="n"/>
-      <c r="R87" s="6" t="n"/>
-      <c r="S87" s="6" t="n"/>
-      <c r="T87" s="6" t="n"/>
-      <c r="U87" s="6" t="n"/>
-      <c r="V87" s="6" t="n"/>
-      <c r="W87" s="6" t="n"/>
-      <c r="X87" s="6" t="n"/>
-      <c r="Y87" s="6" t="n"/>
-      <c r="Z87" s="6" t="n"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1" s="5">
-      <c r="A88" s="6" t="n"/>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="6" t="n"/>
-      <c r="D88" s="6" t="n"/>
-      <c r="E88" s="6" t="n"/>
-      <c r="F88" s="6" t="n"/>
-      <c r="G88" s="6" t="n"/>
-      <c r="H88" s="6" t="n"/>
-      <c r="I88" s="6" t="n"/>
-      <c r="J88" s="6" t="n"/>
-      <c r="K88" s="6" t="n"/>
-      <c r="L88" s="6" t="n"/>
-      <c r="M88" s="6" t="n"/>
-      <c r="N88" s="6" t="n"/>
-      <c r="O88" s="6" t="n"/>
-      <c r="P88" s="6" t="n"/>
-      <c r="Q88" s="6" t="n"/>
-      <c r="R88" s="6" t="n"/>
-      <c r="S88" s="6" t="n"/>
-      <c r="T88" s="6" t="n"/>
-      <c r="U88" s="6" t="n"/>
-      <c r="V88" s="6" t="n"/>
-      <c r="W88" s="6" t="n"/>
-      <c r="X88" s="6" t="n"/>
-      <c r="Y88" s="6" t="n"/>
-      <c r="Z88" s="6" t="n"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1" s="5">
-      <c r="A89" s="6" t="n"/>
-      <c r="B89" s="6" t="n"/>
-      <c r="C89" s="6" t="n"/>
-      <c r="D89" s="6" t="n"/>
-      <c r="E89" s="6" t="n"/>
-      <c r="F89" s="6" t="n"/>
-      <c r="G89" s="6" t="n"/>
-      <c r="H89" s="6" t="n"/>
-      <c r="I89" s="6" t="n"/>
-      <c r="J89" s="6" t="n"/>
-      <c r="K89" s="6" t="n"/>
-      <c r="L89" s="6" t="n"/>
-      <c r="M89" s="6" t="n"/>
-      <c r="N89" s="6" t="n"/>
-      <c r="O89" s="6" t="n"/>
-      <c r="P89" s="6" t="n"/>
-      <c r="Q89" s="6" t="n"/>
-      <c r="R89" s="6" t="n"/>
-      <c r="S89" s="6" t="n"/>
-      <c r="T89" s="6" t="n"/>
-      <c r="U89" s="6" t="n"/>
-      <c r="V89" s="6" t="n"/>
-      <c r="W89" s="6" t="n"/>
-      <c r="X89" s="6" t="n"/>
-      <c r="Y89" s="6" t="n"/>
-      <c r="Z89" s="6" t="n"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1" s="5">
-      <c r="A90" s="6" t="n"/>
-      <c r="B90" s="6" t="n"/>
-      <c r="C90" s="6" t="n"/>
-      <c r="D90" s="6" t="n"/>
-      <c r="E90" s="6" t="n"/>
-      <c r="F90" s="6" t="n"/>
-      <c r="G90" s="6" t="n"/>
-      <c r="H90" s="6" t="n"/>
-      <c r="I90" s="6" t="n"/>
-      <c r="J90" s="6" t="n"/>
-      <c r="K90" s="6" t="n"/>
-      <c r="L90" s="6" t="n"/>
-      <c r="M90" s="6" t="n"/>
-      <c r="N90" s="6" t="n"/>
-      <c r="O90" s="6" t="n"/>
-      <c r="P90" s="6" t="n"/>
-      <c r="Q90" s="6" t="n"/>
-      <c r="R90" s="6" t="n"/>
-      <c r="S90" s="6" t="n"/>
-      <c r="T90" s="6" t="n"/>
-      <c r="U90" s="6" t="n"/>
-      <c r="V90" s="6" t="n"/>
-      <c r="W90" s="6" t="n"/>
-      <c r="X90" s="6" t="n"/>
-      <c r="Y90" s="6" t="n"/>
-      <c r="Z90" s="6" t="n"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1" s="5">
-      <c r="A91" s="6" t="n"/>
-      <c r="B91" s="6" t="n"/>
-      <c r="C91" s="6" t="n"/>
-      <c r="D91" s="6" t="n"/>
-      <c r="E91" s="6" t="n"/>
-      <c r="F91" s="6" t="n"/>
-      <c r="G91" s="6" t="n"/>
-      <c r="H91" s="6" t="n"/>
-      <c r="I91" s="6" t="n"/>
-      <c r="J91" s="6" t="n"/>
-      <c r="K91" s="6" t="n"/>
-      <c r="L91" s="6" t="n"/>
-      <c r="M91" s="6" t="n"/>
-      <c r="N91" s="6" t="n"/>
-      <c r="O91" s="6" t="n"/>
-      <c r="P91" s="6" t="n"/>
-      <c r="Q91" s="6" t="n"/>
-      <c r="R91" s="6" t="n"/>
-      <c r="S91" s="6" t="n"/>
-      <c r="T91" s="6" t="n"/>
-      <c r="U91" s="6" t="n"/>
-      <c r="V91" s="6" t="n"/>
-      <c r="W91" s="6" t="n"/>
-      <c r="X91" s="6" t="n"/>
-      <c r="Y91" s="6" t="n"/>
-      <c r="Z91" s="6" t="n"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1" s="5">
-      <c r="A92" s="6" t="n"/>
-      <c r="B92" s="6" t="n"/>
-      <c r="C92" s="6" t="n"/>
-      <c r="D92" s="6" t="n"/>
-      <c r="E92" s="6" t="n"/>
-      <c r="F92" s="6" t="n"/>
-      <c r="G92" s="6" t="n"/>
-      <c r="H92" s="6" t="n"/>
-      <c r="I92" s="6" t="n"/>
-      <c r="J92" s="6" t="n"/>
-      <c r="K92" s="6" t="n"/>
-      <c r="L92" s="6" t="n"/>
-      <c r="M92" s="6" t="n"/>
-      <c r="N92" s="6" t="n"/>
-      <c r="O92" s="6" t="n"/>
-      <c r="P92" s="6" t="n"/>
-      <c r="Q92" s="6" t="n"/>
-      <c r="R92" s="6" t="n"/>
-      <c r="S92" s="6" t="n"/>
-      <c r="T92" s="6" t="n"/>
-      <c r="U92" s="6" t="n"/>
-      <c r="V92" s="6" t="n"/>
-      <c r="W92" s="6" t="n"/>
-      <c r="X92" s="6" t="n"/>
-      <c r="Y92" s="6" t="n"/>
-      <c r="Z92" s="6" t="n"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1" s="5">
-      <c r="A93" s="6" t="n"/>
-      <c r="B93" s="6" t="n"/>
-      <c r="C93" s="6" t="n"/>
-      <c r="D93" s="6" t="n"/>
-      <c r="E93" s="6" t="n"/>
-      <c r="F93" s="6" t="n"/>
-      <c r="G93" s="6" t="n"/>
-      <c r="H93" s="6" t="n"/>
-      <c r="I93" s="6" t="n"/>
-      <c r="J93" s="6" t="n"/>
-      <c r="K93" s="6" t="n"/>
-      <c r="L93" s="6" t="n"/>
-      <c r="M93" s="6" t="n"/>
-      <c r="N93" s="6" t="n"/>
-      <c r="O93" s="6" t="n"/>
-      <c r="P93" s="6" t="n"/>
-      <c r="Q93" s="6" t="n"/>
-      <c r="R93" s="6" t="n"/>
-      <c r="S93" s="6" t="n"/>
-      <c r="T93" s="6" t="n"/>
-      <c r="U93" s="6" t="n"/>
-      <c r="V93" s="6" t="n"/>
-      <c r="W93" s="6" t="n"/>
-      <c r="X93" s="6" t="n"/>
-      <c r="Y93" s="6" t="n"/>
-      <c r="Z93" s="6" t="n"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1" s="5">
-      <c r="A94" s="6" t="n"/>
-      <c r="B94" s="6" t="n"/>
-      <c r="C94" s="6" t="n"/>
-      <c r="D94" s="6" t="n"/>
-      <c r="E94" s="6" t="n"/>
-      <c r="F94" s="6" t="n"/>
-      <c r="G94" s="6" t="n"/>
-      <c r="H94" s="6" t="n"/>
-      <c r="I94" s="6" t="n"/>
-      <c r="J94" s="6" t="n"/>
-      <c r="K94" s="6" t="n"/>
-      <c r="L94" s="6" t="n"/>
-      <c r="M94" s="6" t="n"/>
-      <c r="N94" s="6" t="n"/>
-      <c r="O94" s="6" t="n"/>
-      <c r="P94" s="6" t="n"/>
-      <c r="Q94" s="6" t="n"/>
-      <c r="R94" s="6" t="n"/>
-      <c r="S94" s="6" t="n"/>
-      <c r="T94" s="6" t="n"/>
-      <c r="U94" s="6" t="n"/>
-      <c r="V94" s="6" t="n"/>
-      <c r="W94" s="6" t="n"/>
-      <c r="X94" s="6" t="n"/>
-      <c r="Y94" s="6" t="n"/>
-      <c r="Z94" s="6" t="n"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1" s="5">
-      <c r="A95" s="6" t="n"/>
-      <c r="B95" s="6" t="n"/>
-      <c r="C95" s="6" t="n"/>
-      <c r="D95" s="6" t="n"/>
-      <c r="E95" s="6" t="n"/>
-      <c r="F95" s="6" t="n"/>
-      <c r="G95" s="6" t="n"/>
-      <c r="H95" s="6" t="n"/>
-      <c r="I95" s="6" t="n"/>
-      <c r="J95" s="6" t="n"/>
-      <c r="K95" s="6" t="n"/>
-      <c r="L95" s="6" t="n"/>
-      <c r="M95" s="6" t="n"/>
-      <c r="N95" s="6" t="n"/>
-      <c r="O95" s="6" t="n"/>
-      <c r="P95" s="6" t="n"/>
-      <c r="Q95" s="6" t="n"/>
-      <c r="R95" s="6" t="n"/>
-      <c r="S95" s="6" t="n"/>
-      <c r="T95" s="6" t="n"/>
-      <c r="U95" s="6" t="n"/>
-      <c r="V95" s="6" t="n"/>
-      <c r="W95" s="6" t="n"/>
-      <c r="X95" s="6" t="n"/>
-      <c r="Y95" s="6" t="n"/>
-      <c r="Z95" s="6" t="n"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1" s="5">
-      <c r="A96" s="6" t="n"/>
-      <c r="B96" s="6" t="n"/>
-      <c r="C96" s="6" t="n"/>
-      <c r="D96" s="6" t="n"/>
-      <c r="E96" s="6" t="n"/>
-      <c r="F96" s="6" t="n"/>
-      <c r="G96" s="6" t="n"/>
-      <c r="H96" s="6" t="n"/>
-      <c r="I96" s="6" t="n"/>
-      <c r="J96" s="6" t="n"/>
-      <c r="K96" s="6" t="n"/>
-      <c r="L96" s="6" t="n"/>
-      <c r="M96" s="6" t="n"/>
-      <c r="N96" s="6" t="n"/>
-      <c r="O96" s="6" t="n"/>
-      <c r="P96" s="6" t="n"/>
-      <c r="Q96" s="6" t="n"/>
-      <c r="R96" s="6" t="n"/>
-      <c r="S96" s="6" t="n"/>
-      <c r="T96" s="6" t="n"/>
-      <c r="U96" s="6" t="n"/>
-      <c r="V96" s="6" t="n"/>
-      <c r="W96" s="6" t="n"/>
-      <c r="X96" s="6" t="n"/>
-      <c r="Y96" s="6" t="n"/>
-      <c r="Z96" s="6" t="n"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1" s="5">
-      <c r="A97" s="6" t="n"/>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-      <c r="E97" s="6" t="n"/>
-      <c r="F97" s="6" t="n"/>
-      <c r="G97" s="6" t="n"/>
-      <c r="H97" s="6" t="n"/>
-      <c r="I97" s="6" t="n"/>
-      <c r="J97" s="6" t="n"/>
-      <c r="K97" s="6" t="n"/>
-      <c r="L97" s="6" t="n"/>
-      <c r="M97" s="6" t="n"/>
-      <c r="N97" s="6" t="n"/>
-      <c r="O97" s="6" t="n"/>
-      <c r="P97" s="6" t="n"/>
-      <c r="Q97" s="6" t="n"/>
-      <c r="R97" s="6" t="n"/>
-      <c r="S97" s="6" t="n"/>
-      <c r="T97" s="6" t="n"/>
-      <c r="U97" s="6" t="n"/>
-      <c r="V97" s="6" t="n"/>
-      <c r="W97" s="6" t="n"/>
-      <c r="X97" s="6" t="n"/>
-      <c r="Y97" s="6" t="n"/>
-      <c r="Z97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="15.75" customHeight="1" s="5">
-      <c r="A98" s="6" t="n"/>
-      <c r="B98" s="6" t="n"/>
-      <c r="C98" s="6" t="n"/>
-      <c r="D98" s="6" t="n"/>
-      <c r="E98" s="6" t="n"/>
-      <c r="F98" s="6" t="n"/>
-      <c r="G98" s="6" t="n"/>
-      <c r="H98" s="6" t="n"/>
-      <c r="I98" s="6" t="n"/>
-      <c r="J98" s="6" t="n"/>
-      <c r="K98" s="6" t="n"/>
-      <c r="L98" s="6" t="n"/>
-      <c r="M98" s="6" t="n"/>
-      <c r="N98" s="6" t="n"/>
-      <c r="O98" s="6" t="n"/>
-      <c r="P98" s="6" t="n"/>
-      <c r="Q98" s="6" t="n"/>
-      <c r="R98" s="6" t="n"/>
-      <c r="S98" s="6" t="n"/>
-      <c r="T98" s="6" t="n"/>
-      <c r="U98" s="6" t="n"/>
-      <c r="V98" s="6" t="n"/>
-      <c r="W98" s="6" t="n"/>
-      <c r="X98" s="6" t="n"/>
-      <c r="Y98" s="6" t="n"/>
-      <c r="Z98" s="6" t="n"/>
-    </row>
-    <row r="99" ht="15.75" customHeight="1" s="5">
-      <c r="A99" s="6" t="n"/>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-      <c r="E99" s="6" t="n"/>
-      <c r="F99" s="6" t="n"/>
-      <c r="G99" s="6" t="n"/>
-      <c r="H99" s="6" t="n"/>
-      <c r="I99" s="6" t="n"/>
-      <c r="J99" s="6" t="n"/>
-      <c r="K99" s="6" t="n"/>
-      <c r="L99" s="6" t="n"/>
-      <c r="M99" s="6" t="n"/>
-      <c r="N99" s="6" t="n"/>
-      <c r="O99" s="6" t="n"/>
-      <c r="P99" s="6" t="n"/>
-      <c r="Q99" s="6" t="n"/>
-      <c r="R99" s="6" t="n"/>
-      <c r="S99" s="6" t="n"/>
-      <c r="T99" s="6" t="n"/>
-      <c r="U99" s="6" t="n"/>
-      <c r="V99" s="6" t="n"/>
-      <c r="W99" s="6" t="n"/>
-      <c r="X99" s="6" t="n"/>
-      <c r="Y99" s="6" t="n"/>
-      <c r="Z99" s="6" t="n"/>
-    </row>
-    <row r="100" ht="15.75" customHeight="1" s="5">
-      <c r="A100" s="6" t="n"/>
-      <c r="B100" s="6" t="n"/>
-      <c r="C100" s="6" t="n"/>
-      <c r="D100" s="6" t="n"/>
-      <c r="E100" s="6" t="n"/>
-      <c r="F100" s="6" t="n"/>
-      <c r="G100" s="6" t="n"/>
-      <c r="H100" s="6" t="n"/>
-      <c r="I100" s="6" t="n"/>
-      <c r="J100" s="6" t="n"/>
-      <c r="K100" s="6" t="n"/>
-      <c r="L100" s="6" t="n"/>
-      <c r="M100" s="6" t="n"/>
-      <c r="N100" s="6" t="n"/>
-      <c r="O100" s="6" t="n"/>
-      <c r="P100" s="6" t="n"/>
-      <c r="Q100" s="6" t="n"/>
-      <c r="R100" s="6" t="n"/>
-      <c r="S100" s="6" t="n"/>
-      <c r="T100" s="6" t="n"/>
-      <c r="U100" s="6" t="n"/>
-      <c r="V100" s="6" t="n"/>
-      <c r="W100" s="6" t="n"/>
-      <c r="X100" s="6" t="n"/>
-      <c r="Y100" s="6" t="n"/>
-      <c r="Z100" s="6" t="n"/>
-    </row>
-    <row r="101" ht="15.75" customHeight="1" s="5">
-      <c r="A101" s="6" t="n"/>
-      <c r="B101" s="6" t="n"/>
-      <c r="C101" s="6" t="n"/>
-      <c r="D101" s="6" t="n"/>
-      <c r="E101" s="6" t="n"/>
-      <c r="F101" s="6" t="n"/>
-      <c r="G101" s="6" t="n"/>
-      <c r="H101" s="6" t="n"/>
-      <c r="I101" s="6" t="n"/>
-      <c r="J101" s="6" t="n"/>
-      <c r="K101" s="6" t="n"/>
-      <c r="L101" s="6" t="n"/>
-      <c r="M101" s="6" t="n"/>
-      <c r="N101" s="6" t="n"/>
-      <c r="O101" s="6" t="n"/>
-      <c r="P101" s="6" t="n"/>
-      <c r="Q101" s="6" t="n"/>
-      <c r="R101" s="6" t="n"/>
-      <c r="S101" s="6" t="n"/>
-      <c r="T101" s="6" t="n"/>
-      <c r="U101" s="6" t="n"/>
-      <c r="V101" s="6" t="n"/>
-      <c r="W101" s="6" t="n"/>
-      <c r="X101" s="6" t="n"/>
-      <c r="Y101" s="6" t="n"/>
-      <c r="Z101" s="6" t="n"/>
-    </row>
-    <row r="102" ht="15.75" customHeight="1" s="5">
-      <c r="A102" s="6" t="n"/>
-      <c r="B102" s="6" t="n"/>
-      <c r="C102" s="6" t="n"/>
-      <c r="D102" s="6" t="n"/>
-      <c r="E102" s="6" t="n"/>
-      <c r="F102" s="6" t="n"/>
-      <c r="G102" s="6" t="n"/>
-      <c r="H102" s="6" t="n"/>
-      <c r="I102" s="6" t="n"/>
-      <c r="J102" s="6" t="n"/>
-      <c r="K102" s="6" t="n"/>
-      <c r="L102" s="6" t="n"/>
-      <c r="M102" s="6" t="n"/>
-      <c r="N102" s="6" t="n"/>
-      <c r="O102" s="6" t="n"/>
-      <c r="P102" s="6" t="n"/>
-      <c r="Q102" s="6" t="n"/>
-      <c r="R102" s="6" t="n"/>
-      <c r="S102" s="6" t="n"/>
-      <c r="T102" s="6" t="n"/>
-      <c r="U102" s="6" t="n"/>
-      <c r="V102" s="6" t="n"/>
-      <c r="W102" s="6" t="n"/>
-      <c r="X102" s="6" t="n"/>
-      <c r="Y102" s="6" t="n"/>
-      <c r="Z102" s="6" t="n"/>
-    </row>
-    <row r="103" ht="15.75" customHeight="1" s="5">
-      <c r="A103" s="6" t="n"/>
-      <c r="B103" s="6" t="n"/>
-      <c r="C103" s="6" t="n"/>
-      <c r="D103" s="6" t="n"/>
-      <c r="E103" s="6" t="n"/>
-      <c r="F103" s="6" t="n"/>
-      <c r="G103" s="6" t="n"/>
-      <c r="H103" s="6" t="n"/>
-      <c r="I103" s="6" t="n"/>
-      <c r="J103" s="6" t="n"/>
-      <c r="K103" s="6" t="n"/>
-      <c r="L103" s="6" t="n"/>
-      <c r="M103" s="6" t="n"/>
-      <c r="N103" s="6" t="n"/>
-      <c r="O103" s="6" t="n"/>
-      <c r="P103" s="6" t="n"/>
-      <c r="Q103" s="6" t="n"/>
-      <c r="R103" s="6" t="n"/>
-      <c r="S103" s="6" t="n"/>
-      <c r="T103" s="6" t="n"/>
-      <c r="U103" s="6" t="n"/>
-      <c r="V103" s="6" t="n"/>
-      <c r="W103" s="6" t="n"/>
-      <c r="X103" s="6" t="n"/>
-      <c r="Y103" s="6" t="n"/>
-      <c r="Z103" s="6" t="n"/>
-    </row>
-    <row r="104" ht="15.75" customHeight="1" s="5">
-      <c r="A104" s="6" t="n"/>
-      <c r="B104" s="6" t="n"/>
-      <c r="C104" s="6" t="n"/>
-      <c r="D104" s="6" t="n"/>
-      <c r="E104" s="6" t="n"/>
-      <c r="F104" s="6" t="n"/>
-      <c r="G104" s="6" t="n"/>
-      <c r="H104" s="6" t="n"/>
-      <c r="I104" s="6" t="n"/>
-      <c r="J104" s="6" t="n"/>
-      <c r="K104" s="6" t="n"/>
-      <c r="L104" s="6" t="n"/>
-      <c r="M104" s="6" t="n"/>
-      <c r="N104" s="6" t="n"/>
-      <c r="O104" s="6" t="n"/>
-      <c r="P104" s="6" t="n"/>
-      <c r="Q104" s="6" t="n"/>
-      <c r="R104" s="6" t="n"/>
-      <c r="S104" s="6" t="n"/>
-      <c r="T104" s="6" t="n"/>
-      <c r="U104" s="6" t="n"/>
-      <c r="V104" s="6" t="n"/>
-      <c r="W104" s="6" t="n"/>
-      <c r="X104" s="6" t="n"/>
-      <c r="Y104" s="6" t="n"/>
-      <c r="Z104" s="6" t="n"/>
-    </row>
-    <row r="105" ht="15.75" customHeight="1" s="5">
-      <c r="A105" s="6" t="n"/>
-      <c r="B105" s="6" t="n"/>
-      <c r="C105" s="6" t="n"/>
-      <c r="D105" s="6" t="n"/>
-      <c r="E105" s="6" t="n"/>
-      <c r="F105" s="6" t="n"/>
-      <c r="G105" s="6" t="n"/>
-      <c r="H105" s="6" t="n"/>
-      <c r="I105" s="6" t="n"/>
-      <c r="J105" s="6" t="n"/>
-      <c r="K105" s="6" t="n"/>
-      <c r="L105" s="6" t="n"/>
-      <c r="M105" s="6" t="n"/>
-      <c r="N105" s="6" t="n"/>
-      <c r="O105" s="6" t="n"/>
-      <c r="P105" s="6" t="n"/>
-      <c r="Q105" s="6" t="n"/>
-      <c r="R105" s="6" t="n"/>
-      <c r="S105" s="6" t="n"/>
-      <c r="T105" s="6" t="n"/>
-      <c r="U105" s="6" t="n"/>
-      <c r="V105" s="6" t="n"/>
-      <c r="W105" s="6" t="n"/>
-      <c r="X105" s="6" t="n"/>
-      <c r="Y105" s="6" t="n"/>
-      <c r="Z105" s="6" t="n"/>
-    </row>
-    <row r="106" ht="15.75" customHeight="1" s="5">
-      <c r="A106" s="6" t="n"/>
-      <c r="B106" s="6" t="n"/>
-      <c r="C106" s="6" t="n"/>
-      <c r="D106" s="6" t="n"/>
-      <c r="E106" s="6" t="n"/>
-      <c r="F106" s="6" t="n"/>
-      <c r="G106" s="6" t="n"/>
-      <c r="H106" s="6" t="n"/>
-      <c r="I106" s="6" t="n"/>
-      <c r="J106" s="6" t="n"/>
-      <c r="K106" s="6" t="n"/>
-      <c r="L106" s="6" t="n"/>
-      <c r="M106" s="6" t="n"/>
-      <c r="N106" s="6" t="n"/>
-      <c r="O106" s="6" t="n"/>
-      <c r="P106" s="6" t="n"/>
-      <c r="Q106" s="6" t="n"/>
-      <c r="R106" s="6" t="n"/>
-      <c r="S106" s="6" t="n"/>
-      <c r="T106" s="6" t="n"/>
-      <c r="U106" s="6" t="n"/>
-      <c r="V106" s="6" t="n"/>
-      <c r="W106" s="6" t="n"/>
-      <c r="X106" s="6" t="n"/>
-      <c r="Y106" s="6" t="n"/>
-      <c r="Z106" s="6" t="n"/>
-    </row>
-    <row r="107" ht="15.75" customHeight="1" s="5">
-      <c r="A107" s="6" t="n"/>
-      <c r="B107" s="6" t="n"/>
-      <c r="C107" s="6" t="n"/>
-      <c r="D107" s="6" t="n"/>
-      <c r="E107" s="6" t="n"/>
-      <c r="F107" s="6" t="n"/>
-      <c r="G107" s="6" t="n"/>
-      <c r="H107" s="6" t="n"/>
-      <c r="I107" s="6" t="n"/>
-      <c r="J107" s="6" t="n"/>
-      <c r="K107" s="6" t="n"/>
-      <c r="L107" s="6" t="n"/>
-      <c r="M107" s="6" t="n"/>
-      <c r="N107" s="6" t="n"/>
-      <c r="O107" s="6" t="n"/>
-      <c r="P107" s="6" t="n"/>
-      <c r="Q107" s="6" t="n"/>
-      <c r="R107" s="6" t="n"/>
-      <c r="S107" s="6" t="n"/>
-      <c r="T107" s="6" t="n"/>
-      <c r="U107" s="6" t="n"/>
-      <c r="V107" s="6" t="n"/>
-      <c r="W107" s="6" t="n"/>
-      <c r="X107" s="6" t="n"/>
-      <c r="Y107" s="6" t="n"/>
-      <c r="Z107" s="6" t="n"/>
-    </row>
-    <row r="108" ht="15.75" customHeight="1" s="5">
-      <c r="A108" s="6" t="n"/>
-      <c r="B108" s="6" t="n"/>
-      <c r="C108" s="6" t="n"/>
-      <c r="D108" s="6" t="n"/>
-      <c r="E108" s="6" t="n"/>
-      <c r="F108" s="6" t="n"/>
-      <c r="G108" s="6" t="n"/>
-      <c r="H108" s="6" t="n"/>
-      <c r="I108" s="6" t="n"/>
-      <c r="J108" s="6" t="n"/>
-      <c r="K108" s="6" t="n"/>
-      <c r="L108" s="6" t="n"/>
-      <c r="M108" s="6" t="n"/>
-      <c r="N108" s="6" t="n"/>
-      <c r="O108" s="6" t="n"/>
-      <c r="P108" s="6" t="n"/>
-      <c r="Q108" s="6" t="n"/>
-      <c r="R108" s="6" t="n"/>
-      <c r="S108" s="6" t="n"/>
-      <c r="T108" s="6" t="n"/>
-      <c r="U108" s="6" t="n"/>
-      <c r="V108" s="6" t="n"/>
-      <c r="W108" s="6" t="n"/>
-      <c r="X108" s="6" t="n"/>
-      <c r="Y108" s="6" t="n"/>
-      <c r="Z108" s="6" t="n"/>
-    </row>
-    <row r="109" ht="15.75" customHeight="1" s="5">
-      <c r="A109" s="6" t="n"/>
-      <c r="B109" s="6" t="n"/>
-      <c r="C109" s="6" t="n"/>
-      <c r="D109" s="6" t="n"/>
-      <c r="E109" s="6" t="n"/>
-      <c r="F109" s="6" t="n"/>
-      <c r="G109" s="6" t="n"/>
-      <c r="H109" s="6" t="n"/>
-      <c r="I109" s="6" t="n"/>
-      <c r="J109" s="6" t="n"/>
-      <c r="K109" s="6" t="n"/>
-      <c r="L109" s="6" t="n"/>
-      <c r="M109" s="6" t="n"/>
-      <c r="N109" s="6" t="n"/>
-      <c r="O109" s="6" t="n"/>
-      <c r="P109" s="6" t="n"/>
-      <c r="Q109" s="6" t="n"/>
-      <c r="R109" s="6" t="n"/>
-      <c r="S109" s="6" t="n"/>
-      <c r="T109" s="6" t="n"/>
-      <c r="U109" s="6" t="n"/>
-      <c r="V109" s="6" t="n"/>
-      <c r="W109" s="6" t="n"/>
-      <c r="X109" s="6" t="n"/>
-      <c r="Y109" s="6" t="n"/>
-      <c r="Z109" s="6" t="n"/>
-    </row>
-    <row r="110" ht="15.75" customHeight="1" s="5">
-      <c r="A110" s="6" t="n"/>
-      <c r="B110" s="6" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6" t="n"/>
-      <c r="E110" s="6" t="n"/>
-      <c r="F110" s="6" t="n"/>
-      <c r="G110" s="6" t="n"/>
-      <c r="H110" s="6" t="n"/>
-      <c r="I110" s="6" t="n"/>
-      <c r="J110" s="6" t="n"/>
-      <c r="K110" s="6" t="n"/>
-      <c r="L110" s="6" t="n"/>
-      <c r="M110" s="6" t="n"/>
-      <c r="N110" s="6" t="n"/>
-      <c r="O110" s="6" t="n"/>
-      <c r="P110" s="6" t="n"/>
-      <c r="Q110" s="6" t="n"/>
-      <c r="R110" s="6" t="n"/>
-      <c r="S110" s="6" t="n"/>
-      <c r="T110" s="6" t="n"/>
-      <c r="U110" s="6" t="n"/>
-      <c r="V110" s="6" t="n"/>
-      <c r="W110" s="6" t="n"/>
-      <c r="X110" s="6" t="n"/>
-      <c r="Y110" s="6" t="n"/>
-      <c r="Z110" s="6" t="n"/>
-    </row>
-    <row r="111" ht="15.75" customHeight="1" s="5">
-      <c r="A111" s="6" t="n"/>
-      <c r="B111" s="6" t="n"/>
-      <c r="C111" s="6" t="n"/>
-      <c r="D111" s="6" t="n"/>
-      <c r="E111" s="6" t="n"/>
-      <c r="F111" s="6" t="n"/>
-      <c r="G111" s="6" t="n"/>
-      <c r="H111" s="6" t="n"/>
-      <c r="I111" s="6" t="n"/>
-      <c r="J111" s="6" t="n"/>
-      <c r="K111" s="6" t="n"/>
-      <c r="L111" s="6" t="n"/>
-      <c r="M111" s="6" t="n"/>
-      <c r="N111" s="6" t="n"/>
-      <c r="O111" s="6" t="n"/>
-      <c r="P111" s="6" t="n"/>
-      <c r="Q111" s="6" t="n"/>
-      <c r="R111" s="6" t="n"/>
-      <c r="S111" s="6" t="n"/>
-      <c r="T111" s="6" t="n"/>
-      <c r="U111" s="6" t="n"/>
-      <c r="V111" s="6" t="n"/>
-      <c r="W111" s="6" t="n"/>
-      <c r="X111" s="6" t="n"/>
-      <c r="Y111" s="6" t="n"/>
-      <c r="Z111" s="6" t="n"/>
-    </row>
-    <row r="112" ht="15.75" customHeight="1" s="5">
-      <c r="A112" s="6" t="n"/>
-      <c r="B112" s="6" t="n"/>
-      <c r="C112" s="6" t="n"/>
-      <c r="D112" s="6" t="n"/>
-      <c r="E112" s="6" t="n"/>
-      <c r="F112" s="6" t="n"/>
-      <c r="G112" s="6" t="n"/>
-      <c r="H112" s="6" t="n"/>
-      <c r="I112" s="6" t="n"/>
-      <c r="J112" s="6" t="n"/>
-      <c r="K112" s="6" t="n"/>
-      <c r="L112" s="6" t="n"/>
-      <c r="M112" s="6" t="n"/>
-      <c r="N112" s="6" t="n"/>
-      <c r="O112" s="6" t="n"/>
-      <c r="P112" s="6" t="n"/>
-      <c r="Q112" s="6" t="n"/>
-      <c r="R112" s="6" t="n"/>
-      <c r="S112" s="6" t="n"/>
-      <c r="T112" s="6" t="n"/>
-      <c r="U112" s="6" t="n"/>
-      <c r="V112" s="6" t="n"/>
-      <c r="W112" s="6" t="n"/>
-      <c r="X112" s="6" t="n"/>
-      <c r="Y112" s="6" t="n"/>
-      <c r="Z112" s="6" t="n"/>
-    </row>
-    <row r="113" ht="15.75" customHeight="1" s="5">
-      <c r="A113" s="6" t="n"/>
-      <c r="B113" s="6" t="n"/>
-      <c r="C113" s="6" t="n"/>
-      <c r="D113" s="6" t="n"/>
-      <c r="E113" s="6" t="n"/>
-      <c r="F113" s="6" t="n"/>
-      <c r="G113" s="6" t="n"/>
-      <c r="H113" s="6" t="n"/>
-      <c r="I113" s="6" t="n"/>
-      <c r="J113" s="6" t="n"/>
-      <c r="K113" s="6" t="n"/>
-      <c r="L113" s="6" t="n"/>
-      <c r="M113" s="6" t="n"/>
-      <c r="N113" s="6" t="n"/>
-      <c r="O113" s="6" t="n"/>
-      <c r="P113" s="6" t="n"/>
-      <c r="Q113" s="6" t="n"/>
-      <c r="R113" s="6" t="n"/>
-      <c r="S113" s="6" t="n"/>
-      <c r="T113" s="6" t="n"/>
-      <c r="U113" s="6" t="n"/>
-      <c r="V113" s="6" t="n"/>
-      <c r="W113" s="6" t="n"/>
-      <c r="X113" s="6" t="n"/>
-      <c r="Y113" s="6" t="n"/>
-      <c r="Z113" s="6" t="n"/>
-    </row>
-    <row r="114" ht="15.75" customHeight="1" s="5">
-      <c r="A114" s="6" t="n"/>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-      <c r="E114" s="6" t="n"/>
-      <c r="F114" s="6" t="n"/>
-      <c r="G114" s="6" t="n"/>
-      <c r="H114" s="6" t="n"/>
-      <c r="I114" s="6" t="n"/>
-      <c r="J114" s="6" t="n"/>
-      <c r="K114" s="6" t="n"/>
-      <c r="L114" s="6" t="n"/>
-      <c r="M114" s="6" t="n"/>
-      <c r="N114" s="6" t="n"/>
-      <c r="O114" s="6" t="n"/>
-      <c r="P114" s="6" t="n"/>
-      <c r="Q114" s="6" t="n"/>
-      <c r="R114" s="6" t="n"/>
-      <c r="S114" s="6" t="n"/>
-      <c r="T114" s="6" t="n"/>
-      <c r="U114" s="6" t="n"/>
-      <c r="V114" s="6" t="n"/>
-      <c r="W114" s="6" t="n"/>
-      <c r="X114" s="6" t="n"/>
-      <c r="Y114" s="6" t="n"/>
-      <c r="Z114" s="6" t="n"/>
-    </row>
-    <row r="115" ht="15.75" customHeight="1" s="5">
-      <c r="A115" s="6" t="n"/>
-      <c r="B115" s="6" t="n"/>
-      <c r="C115" s="6" t="n"/>
-      <c r="D115" s="6" t="n"/>
-      <c r="E115" s="6" t="n"/>
-      <c r="F115" s="6" t="n"/>
-      <c r="G115" s="6" t="n"/>
-      <c r="H115" s="6" t="n"/>
-      <c r="I115" s="6" t="n"/>
-      <c r="J115" s="6" t="n"/>
-      <c r="K115" s="6" t="n"/>
-      <c r="L115" s="6" t="n"/>
-      <c r="M115" s="6" t="n"/>
-      <c r="N115" s="6" t="n"/>
-      <c r="O115" s="6" t="n"/>
-      <c r="P115" s="6" t="n"/>
-      <c r="Q115" s="6" t="n"/>
-      <c r="R115" s="6" t="n"/>
-      <c r="S115" s="6" t="n"/>
-      <c r="T115" s="6" t="n"/>
-      <c r="U115" s="6" t="n"/>
-      <c r="V115" s="6" t="n"/>
-      <c r="W115" s="6" t="n"/>
-      <c r="X115" s="6" t="n"/>
-      <c r="Y115" s="6" t="n"/>
-      <c r="Z115" s="6" t="n"/>
-    </row>
-    <row r="116" ht="15.75" customHeight="1" s="5">
-      <c r="A116" s="6" t="n"/>
-      <c r="B116" s="6" t="n"/>
-      <c r="C116" s="6" t="n"/>
-      <c r="D116" s="6" t="n"/>
-      <c r="E116" s="6" t="n"/>
-      <c r="F116" s="6" t="n"/>
-      <c r="G116" s="6" t="n"/>
-      <c r="H116" s="6" t="n"/>
-      <c r="I116" s="6" t="n"/>
-      <c r="J116" s="6" t="n"/>
-      <c r="K116" s="6" t="n"/>
-      <c r="L116" s="6" t="n"/>
-      <c r="M116" s="6" t="n"/>
-      <c r="N116" s="6" t="n"/>
-      <c r="O116" s="6" t="n"/>
-      <c r="P116" s="6" t="n"/>
-      <c r="Q116" s="6" t="n"/>
-      <c r="R116" s="6" t="n"/>
-      <c r="S116" s="6" t="n"/>
-      <c r="T116" s="6" t="n"/>
-      <c r="U116" s="6" t="n"/>
-      <c r="V116" s="6" t="n"/>
-      <c r="W116" s="6" t="n"/>
-      <c r="X116" s="6" t="n"/>
-      <c r="Y116" s="6" t="n"/>
-      <c r="Z116" s="6" t="n"/>
-    </row>
-    <row r="117" ht="15.75" customHeight="1" s="5">
-      <c r="A117" s="6" t="n"/>
-      <c r="B117" s="6" t="n"/>
-      <c r="C117" s="6" t="n"/>
-      <c r="D117" s="6" t="n"/>
-      <c r="E117" s="6" t="n"/>
-      <c r="F117" s="6" t="n"/>
-      <c r="G117" s="6" t="n"/>
-      <c r="H117" s="6" t="n"/>
-      <c r="I117" s="6" t="n"/>
-      <c r="J117" s="6" t="n"/>
-      <c r="K117" s="6" t="n"/>
-      <c r="L117" s="6" t="n"/>
-      <c r="M117" s="6" t="n"/>
-      <c r="N117" s="6" t="n"/>
-      <c r="O117" s="6" t="n"/>
-      <c r="P117" s="6" t="n"/>
-      <c r="Q117" s="6" t="n"/>
-      <c r="R117" s="6" t="n"/>
-      <c r="S117" s="6" t="n"/>
-      <c r="T117" s="6" t="n"/>
-      <c r="U117" s="6" t="n"/>
-      <c r="V117" s="6" t="n"/>
-      <c r="W117" s="6" t="n"/>
-      <c r="X117" s="6" t="n"/>
-      <c r="Y117" s="6" t="n"/>
-      <c r="Z117" s="6" t="n"/>
-    </row>
-    <row r="118" ht="15.75" customHeight="1" s="5">
-      <c r="A118" s="6" t="n"/>
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="6" t="n"/>
-      <c r="D118" s="6" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
-      <c r="G118" s="6" t="n"/>
-      <c r="H118" s="6" t="n"/>
-      <c r="I118" s="6" t="n"/>
-      <c r="J118" s="6" t="n"/>
-      <c r="K118" s="6" t="n"/>
-      <c r="L118" s="6" t="n"/>
-      <c r="M118" s="6" t="n"/>
-      <c r="N118" s="6" t="n"/>
-      <c r="O118" s="6" t="n"/>
-      <c r="P118" s="6" t="n"/>
-      <c r="Q118" s="6" t="n"/>
-      <c r="R118" s="6" t="n"/>
-      <c r="S118" s="6" t="n"/>
-      <c r="T118" s="6" t="n"/>
-      <c r="U118" s="6" t="n"/>
-      <c r="V118" s="6" t="n"/>
-      <c r="W118" s="6" t="n"/>
-      <c r="X118" s="6" t="n"/>
-      <c r="Y118" s="6" t="n"/>
-      <c r="Z118" s="6" t="n"/>
-    </row>
-    <row r="119" ht="15.75" customHeight="1" s="5">
-      <c r="A119" s="6" t="n"/>
-      <c r="B119" s="6" t="n"/>
-      <c r="C119" s="6" t="n"/>
-      <c r="D119" s="6" t="n"/>
-      <c r="E119" s="6" t="n"/>
-      <c r="F119" s="6" t="n"/>
-      <c r="G119" s="6" t="n"/>
-      <c r="H119" s="6" t="n"/>
-      <c r="I119" s="6" t="n"/>
-      <c r="J119" s="6" t="n"/>
-      <c r="K119" s="6" t="n"/>
-      <c r="L119" s="6" t="n"/>
-      <c r="M119" s="6" t="n"/>
-      <c r="N119" s="6" t="n"/>
-      <c r="O119" s="6" t="n"/>
-      <c r="P119" s="6" t="n"/>
-      <c r="Q119" s="6" t="n"/>
-      <c r="R119" s="6" t="n"/>
-      <c r="S119" s="6" t="n"/>
-      <c r="T119" s="6" t="n"/>
-      <c r="U119" s="6" t="n"/>
-      <c r="V119" s="6" t="n"/>
-      <c r="W119" s="6" t="n"/>
-      <c r="X119" s="6" t="n"/>
-      <c r="Y119" s="6" t="n"/>
-      <c r="Z119" s="6" t="n"/>
-    </row>
-    <row r="120" ht="15.75" customHeight="1" s="5">
-      <c r="A120" s="6" t="n"/>
-      <c r="B120" s="6" t="n"/>
-      <c r="C120" s="6" t="n"/>
-      <c r="D120" s="6" t="n"/>
-      <c r="E120" s="6" t="n"/>
-      <c r="F120" s="6" t="n"/>
-      <c r="G120" s="6" t="n"/>
-      <c r="H120" s="6" t="n"/>
-      <c r="I120" s="6" t="n"/>
-      <c r="J120" s="6" t="n"/>
-      <c r="K120" s="6" t="n"/>
-      <c r="L120" s="6" t="n"/>
-      <c r="M120" s="6" t="n"/>
-      <c r="N120" s="6" t="n"/>
-      <c r="O120" s="6" t="n"/>
-      <c r="P120" s="6" t="n"/>
-      <c r="Q120" s="6" t="n"/>
-      <c r="R120" s="6" t="n"/>
-      <c r="S120" s="6" t="n"/>
-      <c r="T120" s="6" t="n"/>
-      <c r="U120" s="6" t="n"/>
-      <c r="V120" s="6" t="n"/>
-      <c r="W120" s="6" t="n"/>
-      <c r="X120" s="6" t="n"/>
-      <c r="Y120" s="6" t="n"/>
-      <c r="Z120" s="6" t="n"/>
-    </row>
-    <row r="121" ht="15.75" customHeight="1" s="5">
-      <c r="A121" s="6" t="n"/>
-      <c r="B121" s="6" t="n"/>
-      <c r="C121" s="6" t="n"/>
-      <c r="D121" s="6" t="n"/>
-      <c r="E121" s="6" t="n"/>
-      <c r="F121" s="6" t="n"/>
-      <c r="G121" s="6" t="n"/>
-      <c r="H121" s="6" t="n"/>
-      <c r="I121" s="6" t="n"/>
-      <c r="J121" s="6" t="n"/>
-      <c r="K121" s="6" t="n"/>
-      <c r="L121" s="6" t="n"/>
-      <c r="M121" s="6" t="n"/>
-      <c r="N121" s="6" t="n"/>
-      <c r="O121" s="6" t="n"/>
-      <c r="P121" s="6" t="n"/>
-      <c r="Q121" s="6" t="n"/>
-      <c r="R121" s="6" t="n"/>
-      <c r="S121" s="6" t="n"/>
-      <c r="T121" s="6" t="n"/>
-      <c r="U121" s="6" t="n"/>
-      <c r="V121" s="6" t="n"/>
-      <c r="W121" s="6" t="n"/>
-      <c r="X121" s="6" t="n"/>
-      <c r="Y121" s="6" t="n"/>
-      <c r="Z121" s="6" t="n"/>
-    </row>
-    <row r="122" ht="15.75" customHeight="1" s="5">
-      <c r="A122" s="6" t="n"/>
-      <c r="B122" s="6" t="n"/>
-      <c r="C122" s="6" t="n"/>
-      <c r="D122" s="6" t="n"/>
-      <c r="E122" s="6" t="n"/>
-      <c r="F122" s="6" t="n"/>
-      <c r="G122" s="6" t="n"/>
-      <c r="H122" s="6" t="n"/>
-      <c r="I122" s="6" t="n"/>
-      <c r="J122" s="6" t="n"/>
-      <c r="K122" s="6" t="n"/>
-      <c r="L122" s="6" t="n"/>
-      <c r="M122" s="6" t="n"/>
-      <c r="N122" s="6" t="n"/>
-      <c r="O122" s="6" t="n"/>
-      <c r="P122" s="6" t="n"/>
-      <c r="Q122" s="6" t="n"/>
-      <c r="R122" s="6" t="n"/>
-      <c r="S122" s="6" t="n"/>
-      <c r="T122" s="6" t="n"/>
-      <c r="U122" s="6" t="n"/>
-      <c r="V122" s="6" t="n"/>
-      <c r="W122" s="6" t="n"/>
-      <c r="X122" s="6" t="n"/>
-      <c r="Y122" s="6" t="n"/>
-      <c r="Z122" s="6" t="n"/>
-    </row>
-    <row r="123" ht="15.75" customHeight="1" s="5">
-      <c r="A123" s="6" t="n"/>
-      <c r="B123" s="6" t="n"/>
-      <c r="C123" s="6" t="n"/>
-      <c r="D123" s="6" t="n"/>
-      <c r="E123" s="6" t="n"/>
-      <c r="F123" s="6" t="n"/>
-      <c r="G123" s="6" t="n"/>
-      <c r="H123" s="6" t="n"/>
-      <c r="I123" s="6" t="n"/>
-      <c r="J123" s="6" t="n"/>
-      <c r="K123" s="6" t="n"/>
-      <c r="L123" s="6" t="n"/>
-      <c r="M123" s="6" t="n"/>
-      <c r="N123" s="6" t="n"/>
-      <c r="O123" s="6" t="n"/>
-      <c r="P123" s="6" t="n"/>
-      <c r="Q123" s="6" t="n"/>
-      <c r="R123" s="6" t="n"/>
-      <c r="S123" s="6" t="n"/>
-      <c r="T123" s="6" t="n"/>
-      <c r="U123" s="6" t="n"/>
-      <c r="V123" s="6" t="n"/>
-      <c r="W123" s="6" t="n"/>
-      <c r="X123" s="6" t="n"/>
-      <c r="Y123" s="6" t="n"/>
-      <c r="Z123" s="6" t="n"/>
-    </row>
-    <row r="124" ht="15.75" customHeight="1" s="5">
-      <c r="A124" s="6" t="n"/>
-      <c r="B124" s="6" t="n"/>
-      <c r="C124" s="6" t="n"/>
-      <c r="D124" s="6" t="n"/>
-      <c r="E124" s="6" t="n"/>
-      <c r="F124" s="6" t="n"/>
-      <c r="G124" s="6" t="n"/>
-      <c r="H124" s="6" t="n"/>
-      <c r="I124" s="6" t="n"/>
-      <c r="J124" s="6" t="n"/>
-      <c r="K124" s="6" t="n"/>
-      <c r="L124" s="6" t="n"/>
-      <c r="M124" s="6" t="n"/>
-      <c r="N124" s="6" t="n"/>
-      <c r="O124" s="6" t="n"/>
-      <c r="P124" s="6" t="n"/>
-      <c r="Q124" s="6" t="n"/>
-      <c r="R124" s="6" t="n"/>
-      <c r="S124" s="6" t="n"/>
-      <c r="T124" s="6" t="n"/>
-      <c r="U124" s="6" t="n"/>
-      <c r="V124" s="6" t="n"/>
-      <c r="W124" s="6" t="n"/>
-      <c r="X124" s="6" t="n"/>
-      <c r="Y124" s="6" t="n"/>
-      <c r="Z124" s="6" t="n"/>
-    </row>
-    <row r="125" ht="15.75" customHeight="1" s="5">
-      <c r="A125" s="6" t="n"/>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="6" t="n"/>
-      <c r="D125" s="6" t="n"/>
-      <c r="E125" s="6" t="n"/>
-      <c r="F125" s="6" t="n"/>
-      <c r="G125" s="6" t="n"/>
-      <c r="H125" s="6" t="n"/>
-      <c r="I125" s="6" t="n"/>
-      <c r="J125" s="6" t="n"/>
-      <c r="K125" s="6" t="n"/>
-      <c r="L125" s="6" t="n"/>
-      <c r="M125" s="6" t="n"/>
-      <c r="N125" s="6" t="n"/>
-      <c r="O125" s="6" t="n"/>
-      <c r="P125" s="6" t="n"/>
-      <c r="Q125" s="6" t="n"/>
-      <c r="R125" s="6" t="n"/>
-      <c r="S125" s="6" t="n"/>
-      <c r="T125" s="6" t="n"/>
-      <c r="U125" s="6" t="n"/>
-      <c r="V125" s="6" t="n"/>
-      <c r="W125" s="6" t="n"/>
-      <c r="X125" s="6" t="n"/>
-      <c r="Y125" s="6" t="n"/>
-      <c r="Z125" s="6" t="n"/>
-    </row>
-    <row r="126" ht="15.75" customHeight="1" s="5">
-      <c r="A126" s="6" t="n"/>
-      <c r="B126" s="6" t="n"/>
-      <c r="C126" s="6" t="n"/>
-      <c r="D126" s="6" t="n"/>
-      <c r="E126" s="6" t="n"/>
-      <c r="F126" s="6" t="n"/>
-      <c r="G126" s="6" t="n"/>
-      <c r="H126" s="6" t="n"/>
-      <c r="I126" s="6" t="n"/>
-      <c r="J126" s="6" t="n"/>
-      <c r="K126" s="6" t="n"/>
-      <c r="L126" s="6" t="n"/>
-      <c r="M126" s="6" t="n"/>
-      <c r="N126" s="6" t="n"/>
-      <c r="O126" s="6" t="n"/>
-      <c r="P126" s="6" t="n"/>
-      <c r="Q126" s="6" t="n"/>
-      <c r="R126" s="6" t="n"/>
-      <c r="S126" s="6" t="n"/>
-      <c r="T126" s="6" t="n"/>
-      <c r="U126" s="6" t="n"/>
-      <c r="V126" s="6" t="n"/>
-      <c r="W126" s="6" t="n"/>
-      <c r="X126" s="6" t="n"/>
-      <c r="Y126" s="6" t="n"/>
-      <c r="Z126" s="6" t="n"/>
-    </row>
-    <row r="127" ht="15.75" customHeight="1" s="5">
-      <c r="A127" s="6" t="n"/>
-      <c r="B127" s="6" t="n"/>
-      <c r="C127" s="6" t="n"/>
-      <c r="D127" s="6" t="n"/>
-      <c r="E127" s="6" t="n"/>
-      <c r="F127" s="6" t="n"/>
-      <c r="G127" s="6" t="n"/>
-      <c r="H127" s="6" t="n"/>
-      <c r="I127" s="6" t="n"/>
-      <c r="J127" s="6" t="n"/>
-      <c r="K127" s="6" t="n"/>
-      <c r="L127" s="6" t="n"/>
-      <c r="M127" s="6" t="n"/>
-      <c r="N127" s="6" t="n"/>
-      <c r="O127" s="6" t="n"/>
-      <c r="P127" s="6" t="n"/>
-      <c r="Q127" s="6" t="n"/>
-      <c r="R127" s="6" t="n"/>
-      <c r="S127" s="6" t="n"/>
-      <c r="T127" s="6" t="n"/>
-      <c r="U127" s="6" t="n"/>
-      <c r="V127" s="6" t="n"/>
-      <c r="W127" s="6" t="n"/>
-      <c r="X127" s="6" t="n"/>
-      <c r="Y127" s="6" t="n"/>
-      <c r="Z127" s="6" t="n"/>
-    </row>
-    <row r="128" ht="15.75" customHeight="1" s="5">
-      <c r="A128" s="6" t="n"/>
-      <c r="B128" s="6" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-      <c r="E128" s="6" t="n"/>
-      <c r="F128" s="6" t="n"/>
-      <c r="G128" s="6" t="n"/>
-      <c r="H128" s="6" t="n"/>
-      <c r="I128" s="6" t="n"/>
-      <c r="J128" s="6" t="n"/>
-      <c r="K128" s="6" t="n"/>
-      <c r="L128" s="6" t="n"/>
-      <c r="M128" s="6" t="n"/>
-      <c r="N128" s="6" t="n"/>
-      <c r="O128" s="6" t="n"/>
-      <c r="P128" s="6" t="n"/>
-      <c r="Q128" s="6" t="n"/>
-      <c r="R128" s="6" t="n"/>
-      <c r="S128" s="6" t="n"/>
-      <c r="T128" s="6" t="n"/>
-      <c r="U128" s="6" t="n"/>
-      <c r="V128" s="6" t="n"/>
-      <c r="W128" s="6" t="n"/>
-      <c r="X128" s="6" t="n"/>
-      <c r="Y128" s="6" t="n"/>
-      <c r="Z128" s="6" t="n"/>
-    </row>
-    <row r="129" ht="15.75" customHeight="1" s="5">
-      <c r="A129" s="6" t="n"/>
-      <c r="B129" s="6" t="n"/>
-      <c r="C129" s="6" t="n"/>
-      <c r="D129" s="6" t="n"/>
-      <c r="E129" s="6" t="n"/>
-      <c r="F129" s="6" t="n"/>
-      <c r="G129" s="6" t="n"/>
-      <c r="H129" s="6" t="n"/>
-      <c r="I129" s="6" t="n"/>
-      <c r="J129" s="6" t="n"/>
-      <c r="K129" s="6" t="n"/>
-      <c r="L129" s="6" t="n"/>
-      <c r="M129" s="6" t="n"/>
-      <c r="N129" s="6" t="n"/>
-      <c r="O129" s="6" t="n"/>
-      <c r="P129" s="6" t="n"/>
-      <c r="Q129" s="6" t="n"/>
-      <c r="R129" s="6" t="n"/>
-      <c r="S129" s="6" t="n"/>
-      <c r="T129" s="6" t="n"/>
-      <c r="U129" s="6" t="n"/>
-      <c r="V129" s="6" t="n"/>
-      <c r="W129" s="6" t="n"/>
-      <c r="X129" s="6" t="n"/>
-      <c r="Y129" s="6" t="n"/>
-      <c r="Z129" s="6" t="n"/>
-    </row>
-    <row r="130" ht="15.75" customHeight="1" s="5">
-      <c r="A130" s="6" t="n"/>
-      <c r="B130" s="6" t="n"/>
-      <c r="C130" s="6" t="n"/>
-      <c r="D130" s="6" t="n"/>
-      <c r="E130" s="6" t="n"/>
-      <c r="F130" s="6" t="n"/>
-      <c r="G130" s="6" t="n"/>
-      <c r="H130" s="6" t="n"/>
-      <c r="I130" s="6" t="n"/>
-      <c r="J130" s="6" t="n"/>
-      <c r="K130" s="6" t="n"/>
-      <c r="L130" s="6" t="n"/>
-      <c r="M130" s="6" t="n"/>
-      <c r="N130" s="6" t="n"/>
-      <c r="O130" s="6" t="n"/>
-      <c r="P130" s="6" t="n"/>
-      <c r="Q130" s="6" t="n"/>
-      <c r="R130" s="6" t="n"/>
-      <c r="S130" s="6" t="n"/>
-      <c r="T130" s="6" t="n"/>
-      <c r="U130" s="6" t="n"/>
-      <c r="V130" s="6" t="n"/>
-      <c r="W130" s="6" t="n"/>
-      <c r="X130" s="6" t="n"/>
-      <c r="Y130" s="6" t="n"/>
-      <c r="Z130" s="6" t="n"/>
-    </row>
-    <row r="131" ht="15.75" customHeight="1" s="5">
-      <c r="A131" s="6" t="n"/>
-      <c r="B131" s="6" t="n"/>
-      <c r="C131" s="6" t="n"/>
-      <c r="D131" s="6" t="n"/>
-      <c r="E131" s="6" t="n"/>
-      <c r="F131" s="6" t="n"/>
-      <c r="G131" s="6" t="n"/>
-      <c r="H131" s="6" t="n"/>
-      <c r="I131" s="6" t="n"/>
-      <c r="J131" s="6" t="n"/>
-      <c r="K131" s="6" t="n"/>
-      <c r="L131" s="6" t="n"/>
-      <c r="M131" s="6" t="n"/>
-      <c r="N131" s="6" t="n"/>
-      <c r="O131" s="6" t="n"/>
-      <c r="P131" s="6" t="n"/>
-      <c r="Q131" s="6" t="n"/>
-      <c r="R131" s="6" t="n"/>
-      <c r="S131" s="6" t="n"/>
-      <c r="T131" s="6" t="n"/>
-      <c r="U131" s="6" t="n"/>
-      <c r="V131" s="6" t="n"/>
-      <c r="W131" s="6" t="n"/>
-      <c r="X131" s="6" t="n"/>
-      <c r="Y131" s="6" t="n"/>
-      <c r="Z131" s="6" t="n"/>
-    </row>
-    <row r="132" ht="15.75" customHeight="1" s="5">
-      <c r="A132" s="6" t="n"/>
-      <c r="B132" s="6" t="n"/>
-      <c r="C132" s="6" t="n"/>
-      <c r="D132" s="6" t="n"/>
-      <c r="E132" s="6" t="n"/>
-      <c r="F132" s="6" t="n"/>
-      <c r="G132" s="6" t="n"/>
-      <c r="H132" s="6" t="n"/>
-      <c r="I132" s="6" t="n"/>
-      <c r="J132" s="6" t="n"/>
-      <c r="K132" s="6" t="n"/>
-      <c r="L132" s="6" t="n"/>
-      <c r="M132" s="6" t="n"/>
-      <c r="N132" s="6" t="n"/>
-      <c r="O132" s="6" t="n"/>
-      <c r="P132" s="6" t="n"/>
-      <c r="Q132" s="6" t="n"/>
-      <c r="R132" s="6" t="n"/>
-      <c r="S132" s="6" t="n"/>
-      <c r="T132" s="6" t="n"/>
-      <c r="U132" s="6" t="n"/>
-      <c r="V132" s="6" t="n"/>
-      <c r="W132" s="6" t="n"/>
-      <c r="X132" s="6" t="n"/>
-      <c r="Y132" s="6" t="n"/>
-      <c r="Z132" s="6" t="n"/>
-    </row>
-    <row r="133" ht="15.75" customHeight="1" s="5">
-      <c r="A133" s="6" t="n"/>
-      <c r="B133" s="6" t="n"/>
-      <c r="C133" s="6" t="n"/>
-      <c r="D133" s="6" t="n"/>
-      <c r="E133" s="6" t="n"/>
-      <c r="F133" s="6" t="n"/>
-      <c r="G133" s="6" t="n"/>
-      <c r="H133" s="6" t="n"/>
-      <c r="I133" s="6" t="n"/>
-      <c r="J133" s="6" t="n"/>
-      <c r="K133" s="6" t="n"/>
-      <c r="L133" s="6" t="n"/>
-      <c r="M133" s="6" t="n"/>
-      <c r="N133" s="6" t="n"/>
-      <c r="O133" s="6" t="n"/>
-      <c r="P133" s="6" t="n"/>
-      <c r="Q133" s="6" t="n"/>
-      <c r="R133" s="6" t="n"/>
-      <c r="S133" s="6" t="n"/>
-      <c r="T133" s="6" t="n"/>
-      <c r="U133" s="6" t="n"/>
-      <c r="V133" s="6" t="n"/>
-      <c r="W133" s="6" t="n"/>
-      <c r="X133" s="6" t="n"/>
-      <c r="Y133" s="6" t="n"/>
-      <c r="Z133" s="6" t="n"/>
-    </row>
-    <row r="134" ht="15.75" customHeight="1" s="5">
-      <c r="A134" s="6" t="n"/>
-      <c r="B134" s="6" t="n"/>
-      <c r="C134" s="6" t="n"/>
-      <c r="D134" s="6" t="n"/>
-      <c r="E134" s="6" t="n"/>
-      <c r="F134" s="6" t="n"/>
-      <c r="G134" s="6" t="n"/>
-      <c r="H134" s="6" t="n"/>
-      <c r="I134" s="6" t="n"/>
-      <c r="J134" s="6" t="n"/>
-      <c r="K134" s="6" t="n"/>
-      <c r="L134" s="6" t="n"/>
-      <c r="M134" s="6" t="n"/>
-      <c r="N134" s="6" t="n"/>
-      <c r="O134" s="6" t="n"/>
-      <c r="P134" s="6" t="n"/>
-      <c r="Q134" s="6" t="n"/>
-      <c r="R134" s="6" t="n"/>
-      <c r="S134" s="6" t="n"/>
-      <c r="T134" s="6" t="n"/>
-      <c r="U134" s="6" t="n"/>
-      <c r="V134" s="6" t="n"/>
-      <c r="W134" s="6" t="n"/>
-      <c r="X134" s="6" t="n"/>
-      <c r="Y134" s="6" t="n"/>
-      <c r="Z134" s="6" t="n"/>
-    </row>
-    <row r="135" ht="15.75" customHeight="1" s="5">
-      <c r="A135" s="6" t="n"/>
-      <c r="B135" s="6" t="n"/>
-      <c r="C135" s="6" t="n"/>
-      <c r="D135" s="6" t="n"/>
-      <c r="E135" s="6" t="n"/>
-      <c r="F135" s="6" t="n"/>
-      <c r="G135" s="6" t="n"/>
-      <c r="H135" s="6" t="n"/>
-      <c r="I135" s="6" t="n"/>
-      <c r="J135" s="6" t="n"/>
-      <c r="K135" s="6" t="n"/>
-      <c r="L135" s="6" t="n"/>
-      <c r="M135" s="6" t="n"/>
-      <c r="N135" s="6" t="n"/>
-      <c r="O135" s="6" t="n"/>
-      <c r="P135" s="6" t="n"/>
-      <c r="Q135" s="6" t="n"/>
-      <c r="R135" s="6" t="n"/>
-      <c r="S135" s="6" t="n"/>
-      <c r="T135" s="6" t="n"/>
-      <c r="U135" s="6" t="n"/>
-      <c r="V135" s="6" t="n"/>
-      <c r="W135" s="6" t="n"/>
-      <c r="X135" s="6" t="n"/>
-      <c r="Y135" s="6" t="n"/>
-      <c r="Z135" s="6" t="n"/>
-    </row>
-    <row r="136" ht="15.75" customHeight="1" s="5">
-      <c r="A136" s="6" t="n"/>
-      <c r="B136" s="6" t="n"/>
-      <c r="C136" s="6" t="n"/>
-      <c r="D136" s="6" t="n"/>
-      <c r="E136" s="6" t="n"/>
-      <c r="F136" s="6" t="n"/>
-      <c r="G136" s="6" t="n"/>
-      <c r="H136" s="6" t="n"/>
-      <c r="I136" s="6" t="n"/>
-      <c r="J136" s="6" t="n"/>
-      <c r="K136" s="6" t="n"/>
-      <c r="L136" s="6" t="n"/>
-      <c r="M136" s="6" t="n"/>
-      <c r="N136" s="6" t="n"/>
-      <c r="O136" s="6" t="n"/>
-      <c r="P136" s="6" t="n"/>
-      <c r="Q136" s="6" t="n"/>
-      <c r="R136" s="6" t="n"/>
-      <c r="S136" s="6" t="n"/>
-      <c r="T136" s="6" t="n"/>
-      <c r="U136" s="6" t="n"/>
-      <c r="V136" s="6" t="n"/>
-      <c r="W136" s="6" t="n"/>
-      <c r="X136" s="6" t="n"/>
-      <c r="Y136" s="6" t="n"/>
-      <c r="Z136" s="6" t="n"/>
-    </row>
-    <row r="137" ht="15.75" customHeight="1" s="5">
-      <c r="A137" s="6" t="n"/>
-      <c r="B137" s="6" t="n"/>
-      <c r="C137" s="6" t="n"/>
-      <c r="D137" s="6" t="n"/>
-      <c r="E137" s="6" t="n"/>
-      <c r="F137" s="6" t="n"/>
-      <c r="G137" s="6" t="n"/>
-      <c r="H137" s="6" t="n"/>
-      <c r="I137" s="6" t="n"/>
-      <c r="J137" s="6" t="n"/>
-      <c r="K137" s="6" t="n"/>
-      <c r="L137" s="6" t="n"/>
-      <c r="M137" s="6" t="n"/>
-      <c r="N137" s="6" t="n"/>
-      <c r="O137" s="6" t="n"/>
-      <c r="P137" s="6" t="n"/>
-      <c r="Q137" s="6" t="n"/>
-      <c r="R137" s="6" t="n"/>
-      <c r="S137" s="6" t="n"/>
-      <c r="T137" s="6" t="n"/>
-      <c r="U137" s="6" t="n"/>
-      <c r="V137" s="6" t="n"/>
-      <c r="W137" s="6" t="n"/>
-      <c r="X137" s="6" t="n"/>
-      <c r="Y137" s="6" t="n"/>
-      <c r="Z137" s="6" t="n"/>
-    </row>
-    <row r="138" ht="15.75" customHeight="1" s="5">
-      <c r="A138" s="6" t="n"/>
-      <c r="B138" s="6" t="n"/>
-      <c r="C138" s="6" t="n"/>
-      <c r="D138" s="6" t="n"/>
-      <c r="E138" s="6" t="n"/>
-      <c r="F138" s="6" t="n"/>
-      <c r="G138" s="6" t="n"/>
-      <c r="H138" s="6" t="n"/>
-      <c r="I138" s="6" t="n"/>
-      <c r="J138" s="6" t="n"/>
-      <c r="K138" s="6" t="n"/>
-      <c r="L138" s="6" t="n"/>
-      <c r="M138" s="6" t="n"/>
-      <c r="N138" s="6" t="n"/>
-      <c r="O138" s="6" t="n"/>
-      <c r="P138" s="6" t="n"/>
-      <c r="Q138" s="6" t="n"/>
-      <c r="R138" s="6" t="n"/>
-      <c r="S138" s="6" t="n"/>
-      <c r="T138" s="6" t="n"/>
-      <c r="U138" s="6" t="n"/>
-      <c r="V138" s="6" t="n"/>
-      <c r="W138" s="6" t="n"/>
-      <c r="X138" s="6" t="n"/>
-      <c r="Y138" s="6" t="n"/>
-      <c r="Z138" s="6" t="n"/>
-    </row>
-    <row r="139" ht="15.75" customHeight="1" s="5">
-      <c r="A139" s="6" t="n"/>
-      <c r="B139" s="6" t="n"/>
-      <c r="C139" s="6" t="n"/>
-      <c r="D139" s="6" t="n"/>
-      <c r="E139" s="6" t="n"/>
-      <c r="F139" s="6" t="n"/>
-      <c r="G139" s="6" t="n"/>
-      <c r="H139" s="6" t="n"/>
-      <c r="I139" s="6" t="n"/>
-      <c r="J139" s="6" t="n"/>
-      <c r="K139" s="6" t="n"/>
-      <c r="L139" s="6" t="n"/>
-      <c r="M139" s="6" t="n"/>
-      <c r="N139" s="6" t="n"/>
-      <c r="O139" s="6" t="n"/>
-      <c r="P139" s="6" t="n"/>
-      <c r="Q139" s="6" t="n"/>
-      <c r="R139" s="6" t="n"/>
-      <c r="S139" s="6" t="n"/>
-      <c r="T139" s="6" t="n"/>
-      <c r="U139" s="6" t="n"/>
-      <c r="V139" s="6" t="n"/>
-      <c r="W139" s="6" t="n"/>
-      <c r="X139" s="6" t="n"/>
-      <c r="Y139" s="6" t="n"/>
-      <c r="Z139" s="6" t="n"/>
-    </row>
-    <row r="140" ht="15.75" customHeight="1" s="5">
-      <c r="A140" s="6" t="n"/>
-      <c r="B140" s="6" t="n"/>
-      <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6" t="n"/>
-      <c r="E140" s="6" t="n"/>
-      <c r="F140" s="6" t="n"/>
-      <c r="G140" s="6" t="n"/>
-      <c r="H140" s="6" t="n"/>
-      <c r="I140" s="6" t="n"/>
-      <c r="J140" s="6" t="n"/>
-      <c r="K140" s="6" t="n"/>
-      <c r="L140" s="6" t="n"/>
-      <c r="M140" s="6" t="n"/>
-      <c r="N140" s="6" t="n"/>
-      <c r="O140" s="6" t="n"/>
-      <c r="P140" s="6" t="n"/>
-      <c r="Q140" s="6" t="n"/>
-      <c r="R140" s="6" t="n"/>
-      <c r="S140" s="6" t="n"/>
-      <c r="T140" s="6" t="n"/>
-      <c r="U140" s="6" t="n"/>
-      <c r="V140" s="6" t="n"/>
-      <c r="W140" s="6" t="n"/>
-      <c r="X140" s="6" t="n"/>
-      <c r="Y140" s="6" t="n"/>
-      <c r="Z140" s="6" t="n"/>
-    </row>
-    <row r="141" ht="15.75" customHeight="1" s="5">
-      <c r="A141" s="6" t="n"/>
-      <c r="B141" s="6" t="n"/>
-      <c r="C141" s="6" t="n"/>
-      <c r="D141" s="6" t="n"/>
-      <c r="E141" s="6" t="n"/>
-      <c r="F141" s="6" t="n"/>
-      <c r="G141" s="6" t="n"/>
-      <c r="H141" s="6" t="n"/>
-      <c r="I141" s="6" t="n"/>
-      <c r="J141" s="6" t="n"/>
-      <c r="K141" s="6" t="n"/>
-      <c r="L141" s="6" t="n"/>
-      <c r="M141" s="6" t="n"/>
-      <c r="N141" s="6" t="n"/>
-      <c r="O141" s="6" t="n"/>
-      <c r="P141" s="6" t="n"/>
-      <c r="Q141" s="6" t="n"/>
-      <c r="R141" s="6" t="n"/>
-      <c r="S141" s="6" t="n"/>
-      <c r="T141" s="6" t="n"/>
-      <c r="U141" s="6" t="n"/>
-      <c r="V141" s="6" t="n"/>
-      <c r="W141" s="6" t="n"/>
-      <c r="X141" s="6" t="n"/>
-      <c r="Y141" s="6" t="n"/>
-      <c r="Z141" s="6" t="n"/>
-    </row>
-    <row r="142" ht="15.75" customHeight="1" s="5">
-      <c r="A142" s="6" t="n"/>
-      <c r="B142" s="6" t="n"/>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="n"/>
-      <c r="E142" s="6" t="n"/>
-      <c r="F142" s="6" t="n"/>
-      <c r="G142" s="6" t="n"/>
-      <c r="H142" s="6" t="n"/>
-      <c r="I142" s="6" t="n"/>
-      <c r="J142" s="6" t="n"/>
-      <c r="K142" s="6" t="n"/>
-      <c r="L142" s="6" t="n"/>
-      <c r="M142" s="6" t="n"/>
-      <c r="N142" s="6" t="n"/>
-      <c r="O142" s="6" t="n"/>
-      <c r="P142" s="6" t="n"/>
-      <c r="Q142" s="6" t="n"/>
-      <c r="R142" s="6" t="n"/>
-      <c r="S142" s="6" t="n"/>
-      <c r="T142" s="6" t="n"/>
-      <c r="U142" s="6" t="n"/>
-      <c r="V142" s="6" t="n"/>
-      <c r="W142" s="6" t="n"/>
-      <c r="X142" s="6" t="n"/>
-      <c r="Y142" s="6" t="n"/>
-      <c r="Z142" s="6" t="n"/>
-    </row>
-    <row r="143" ht="15.75" customHeight="1" s="5">
-      <c r="A143" s="6" t="n"/>
-      <c r="B143" s="6" t="n"/>
-      <c r="C143" s="6" t="n"/>
-      <c r="D143" s="6" t="n"/>
-      <c r="E143" s="6" t="n"/>
-      <c r="F143" s="6" t="n"/>
-      <c r="G143" s="6" t="n"/>
-      <c r="H143" s="6" t="n"/>
-      <c r="I143" s="6" t="n"/>
-      <c r="J143" s="6" t="n"/>
-      <c r="K143" s="6" t="n"/>
-      <c r="L143" s="6" t="n"/>
-      <c r="M143" s="6" t="n"/>
-      <c r="N143" s="6" t="n"/>
-      <c r="O143" s="6" t="n"/>
-      <c r="P143" s="6" t="n"/>
-      <c r="Q143" s="6" t="n"/>
-      <c r="R143" s="6" t="n"/>
-      <c r="S143" s="6" t="n"/>
-      <c r="T143" s="6" t="n"/>
-      <c r="U143" s="6" t="n"/>
-      <c r="V143" s="6" t="n"/>
-      <c r="W143" s="6" t="n"/>
-      <c r="X143" s="6" t="n"/>
-      <c r="Y143" s="6" t="n"/>
-      <c r="Z143" s="6" t="n"/>
-    </row>
-    <row r="144" ht="15.75" customHeight="1" s="5">
-      <c r="A144" s="6" t="n"/>
-      <c r="B144" s="6" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6" t="n"/>
-      <c r="E144" s="6" t="n"/>
-      <c r="F144" s="6" t="n"/>
-      <c r="G144" s="6" t="n"/>
-      <c r="H144" s="6" t="n"/>
-      <c r="I144" s="6" t="n"/>
-      <c r="J144" s="6" t="n"/>
-      <c r="K144" s="6" t="n"/>
-      <c r="L144" s="6" t="n"/>
-      <c r="M144" s="6" t="n"/>
-      <c r="N144" s="6" t="n"/>
-      <c r="O144" s="6" t="n"/>
-      <c r="P144" s="6" t="n"/>
-      <c r="Q144" s="6" t="n"/>
-      <c r="R144" s="6" t="n"/>
-      <c r="S144" s="6" t="n"/>
-      <c r="T144" s="6" t="n"/>
-      <c r="U144" s="6" t="n"/>
-      <c r="V144" s="6" t="n"/>
-      <c r="W144" s="6" t="n"/>
-      <c r="X144" s="6" t="n"/>
-      <c r="Y144" s="6" t="n"/>
-      <c r="Z144" s="6" t="n"/>
-    </row>
-    <row r="145" ht="15.75" customHeight="1" s="5">
-      <c r="A145" s="6" t="n"/>
-      <c r="B145" s="6" t="n"/>
-      <c r="C145" s="6" t="n"/>
-      <c r="D145" s="6" t="n"/>
-      <c r="E145" s="6" t="n"/>
-      <c r="F145" s="6" t="n"/>
-      <c r="G145" s="6" t="n"/>
-      <c r="H145" s="6" t="n"/>
-      <c r="I145" s="6" t="n"/>
-      <c r="J145" s="6" t="n"/>
-      <c r="K145" s="6" t="n"/>
-      <c r="L145" s="6" t="n"/>
-      <c r="M145" s="6" t="n"/>
-      <c r="N145" s="6" t="n"/>
-      <c r="O145" s="6" t="n"/>
-      <c r="P145" s="6" t="n"/>
-      <c r="Q145" s="6" t="n"/>
-      <c r="R145" s="6" t="n"/>
-      <c r="S145" s="6" t="n"/>
-      <c r="T145" s="6" t="n"/>
-      <c r="U145" s="6" t="n"/>
-      <c r="V145" s="6" t="n"/>
-      <c r="W145" s="6" t="n"/>
-      <c r="X145" s="6" t="n"/>
-      <c r="Y145" s="6" t="n"/>
-      <c r="Z145" s="6" t="n"/>
-    </row>
-    <row r="146" ht="15.75" customHeight="1" s="5">
-      <c r="A146" s="6" t="n"/>
-      <c r="B146" s="6" t="n"/>
-      <c r="C146" s="6" t="n"/>
-      <c r="D146" s="6" t="n"/>
-      <c r="E146" s="6" t="n"/>
-      <c r="F146" s="6" t="n"/>
-      <c r="G146" s="6" t="n"/>
-      <c r="H146" s="6" t="n"/>
-      <c r="I146" s="6" t="n"/>
-      <c r="J146" s="6" t="n"/>
-      <c r="K146" s="6" t="n"/>
-      <c r="L146" s="6" t="n"/>
-      <c r="M146" s="6" t="n"/>
-      <c r="N146" s="6" t="n"/>
-      <c r="O146" s="6" t="n"/>
-      <c r="P146" s="6" t="n"/>
-      <c r="Q146" s="6" t="n"/>
-      <c r="R146" s="6" t="n"/>
-      <c r="S146" s="6" t="n"/>
-      <c r="T146" s="6" t="n"/>
-      <c r="U146" s="6" t="n"/>
-      <c r="V146" s="6" t="n"/>
-      <c r="W146" s="6" t="n"/>
-      <c r="X146" s="6" t="n"/>
-      <c r="Y146" s="6" t="n"/>
-      <c r="Z146" s="6" t="n"/>
-    </row>
-    <row r="147" ht="15.75" customHeight="1" s="5">
-      <c r="A147" s="6" t="n"/>
-      <c r="B147" s="6" t="n"/>
-      <c r="C147" s="6" t="n"/>
-      <c r="D147" s="6" t="n"/>
-      <c r="E147" s="6" t="n"/>
-      <c r="F147" s="6" t="n"/>
-      <c r="G147" s="6" t="n"/>
-      <c r="H147" s="6" t="n"/>
-      <c r="I147" s="6" t="n"/>
-      <c r="J147" s="6" t="n"/>
-      <c r="K147" s="6" t="n"/>
-      <c r="L147" s="6" t="n"/>
-      <c r="M147" s="6" t="n"/>
-      <c r="N147" s="6" t="n"/>
-      <c r="O147" s="6" t="n"/>
-      <c r="P147" s="6" t="n"/>
-      <c r="Q147" s="6" t="n"/>
-      <c r="R147" s="6" t="n"/>
-      <c r="S147" s="6" t="n"/>
-      <c r="T147" s="6" t="n"/>
-      <c r="U147" s="6" t="n"/>
-      <c r="V147" s="6" t="n"/>
-      <c r="W147" s="6" t="n"/>
-      <c r="X147" s="6" t="n"/>
-      <c r="Y147" s="6" t="n"/>
-      <c r="Z147" s="6" t="n"/>
-    </row>
-    <row r="148" ht="15.75" customHeight="1" s="5">
-      <c r="A148" s="6" t="n"/>
-      <c r="B148" s="6" t="n"/>
-      <c r="C148" s="6" t="n"/>
-      <c r="D148" s="6" t="n"/>
-      <c r="E148" s="6" t="n"/>
-      <c r="F148" s="6" t="n"/>
-      <c r="G148" s="6" t="n"/>
-      <c r="H148" s="6" t="n"/>
-      <c r="I148" s="6" t="n"/>
-      <c r="J148" s="6" t="n"/>
-      <c r="K148" s="6" t="n"/>
-      <c r="L148" s="6" t="n"/>
-      <c r="M148" s="6" t="n"/>
-      <c r="N148" s="6" t="n"/>
-      <c r="O148" s="6" t="n"/>
-      <c r="P148" s="6" t="n"/>
-      <c r="Q148" s="6" t="n"/>
-      <c r="R148" s="6" t="n"/>
-      <c r="S148" s="6" t="n"/>
-      <c r="T148" s="6" t="n"/>
-      <c r="U148" s="6" t="n"/>
-      <c r="V148" s="6" t="n"/>
-      <c r="W148" s="6" t="n"/>
-      <c r="X148" s="6" t="n"/>
-      <c r="Y148" s="6" t="n"/>
-      <c r="Z148" s="6" t="n"/>
-    </row>
-    <row r="149" ht="15.75" customHeight="1" s="5">
-      <c r="A149" s="6" t="n"/>
-      <c r="B149" s="6" t="n"/>
-      <c r="C149" s="6" t="n"/>
-      <c r="D149" s="6" t="n"/>
-      <c r="E149" s="6" t="n"/>
-      <c r="F149" s="6" t="n"/>
-      <c r="G149" s="6" t="n"/>
-      <c r="H149" s="6" t="n"/>
-      <c r="I149" s="6" t="n"/>
-      <c r="J149" s="6" t="n"/>
-      <c r="K149" s="6" t="n"/>
-      <c r="L149" s="6" t="n"/>
-      <c r="M149" s="6" t="n"/>
-      <c r="N149" s="6" t="n"/>
-      <c r="O149" s="6" t="n"/>
-      <c r="P149" s="6" t="n"/>
-      <c r="Q149" s="6" t="n"/>
-      <c r="R149" s="6" t="n"/>
-      <c r="S149" s="6" t="n"/>
-      <c r="T149" s="6" t="n"/>
-      <c r="U149" s="6" t="n"/>
-      <c r="V149" s="6" t="n"/>
-      <c r="W149" s="6" t="n"/>
-      <c r="X149" s="6" t="n"/>
-      <c r="Y149" s="6" t="n"/>
-      <c r="Z149" s="6" t="n"/>
-    </row>
-    <row r="150" ht="15.75" customHeight="1" s="5">
-      <c r="A150" s="6" t="n"/>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="6" t="n"/>
-      <c r="D150" s="6" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
-      <c r="G150" s="6" t="n"/>
-      <c r="H150" s="6" t="n"/>
-      <c r="I150" s="6" t="n"/>
-      <c r="J150" s="6" t="n"/>
-      <c r="K150" s="6" t="n"/>
-      <c r="L150" s="6" t="n"/>
-      <c r="M150" s="6" t="n"/>
-      <c r="N150" s="6" t="n"/>
-      <c r="O150" s="6" t="n"/>
-      <c r="P150" s="6" t="n"/>
-      <c r="Q150" s="6" t="n"/>
-      <c r="R150" s="6" t="n"/>
-      <c r="S150" s="6" t="n"/>
-      <c r="T150" s="6" t="n"/>
-      <c r="U150" s="6" t="n"/>
-      <c r="V150" s="6" t="n"/>
-      <c r="W150" s="6" t="n"/>
-      <c r="X150" s="6" t="n"/>
-      <c r="Y150" s="6" t="n"/>
-      <c r="Z150" s="6" t="n"/>
-    </row>
-    <row r="151" ht="15.75" customHeight="1" s="5">
-      <c r="A151" s="6" t="n"/>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="6" t="n"/>
-      <c r="D151" s="6" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="F151" s="6" t="n"/>
-      <c r="G151" s="6" t="n"/>
-      <c r="H151" s="6" t="n"/>
-      <c r="I151" s="6" t="n"/>
-      <c r="J151" s="6" t="n"/>
-      <c r="K151" s="6" t="n"/>
-      <c r="L151" s="6" t="n"/>
-      <c r="M151" s="6" t="n"/>
-      <c r="N151" s="6" t="n"/>
-      <c r="O151" s="6" t="n"/>
-      <c r="P151" s="6" t="n"/>
-      <c r="Q151" s="6" t="n"/>
-      <c r="R151" s="6" t="n"/>
-      <c r="S151" s="6" t="n"/>
-      <c r="T151" s="6" t="n"/>
-      <c r="U151" s="6" t="n"/>
-      <c r="V151" s="6" t="n"/>
-      <c r="W151" s="6" t="n"/>
-      <c r="X151" s="6" t="n"/>
-      <c r="Y151" s="6" t="n"/>
-      <c r="Z151" s="6" t="n"/>
-    </row>
-    <row r="152" ht="15.75" customHeight="1" s="5">
-      <c r="A152" s="6" t="n"/>
-      <c r="B152" s="6" t="n"/>
-      <c r="C152" s="6" t="n"/>
-      <c r="D152" s="6" t="n"/>
-      <c r="E152" s="6" t="n"/>
-      <c r="F152" s="6" t="n"/>
-      <c r="G152" s="6" t="n"/>
-      <c r="H152" s="6" t="n"/>
-      <c r="I152" s="6" t="n"/>
-      <c r="J152" s="6" t="n"/>
-      <c r="K152" s="6" t="n"/>
-      <c r="L152" s="6" t="n"/>
-      <c r="M152" s="6" t="n"/>
-      <c r="N152" s="6" t="n"/>
-      <c r="O152" s="6" t="n"/>
-      <c r="P152" s="6" t="n"/>
-      <c r="Q152" s="6" t="n"/>
-      <c r="R152" s="6" t="n"/>
-      <c r="S152" s="6" t="n"/>
-      <c r="T152" s="6" t="n"/>
-      <c r="U152" s="6" t="n"/>
-      <c r="V152" s="6" t="n"/>
-      <c r="W152" s="6" t="n"/>
-      <c r="X152" s="6" t="n"/>
-      <c r="Y152" s="6" t="n"/>
-      <c r="Z152" s="6" t="n"/>
-    </row>
-    <row r="153" ht="15.75" customHeight="1" s="5">
-      <c r="A153" s="6" t="n"/>
-      <c r="B153" s="6" t="n"/>
-      <c r="C153" s="6" t="n"/>
-      <c r="D153" s="6" t="n"/>
-      <c r="E153" s="6" t="n"/>
-      <c r="F153" s="6" t="n"/>
-      <c r="G153" s="6" t="n"/>
-      <c r="H153" s="6" t="n"/>
-      <c r="I153" s="6" t="n"/>
-      <c r="J153" s="6" t="n"/>
-      <c r="K153" s="6" t="n"/>
-      <c r="L153" s="6" t="n"/>
-      <c r="M153" s="6" t="n"/>
-      <c r="N153" s="6" t="n"/>
-      <c r="O153" s="6" t="n"/>
-      <c r="P153" s="6" t="n"/>
-      <c r="Q153" s="6" t="n"/>
-      <c r="R153" s="6" t="n"/>
-      <c r="S153" s="6" t="n"/>
-      <c r="T153" s="6" t="n"/>
-      <c r="U153" s="6" t="n"/>
-      <c r="V153" s="6" t="n"/>
-      <c r="W153" s="6" t="n"/>
-      <c r="X153" s="6" t="n"/>
-      <c r="Y153" s="6" t="n"/>
-      <c r="Z153" s="6" t="n"/>
-    </row>
-    <row r="154" ht="15.75" customHeight="1" s="5">
-      <c r="A154" s="6" t="n"/>
-      <c r="B154" s="6" t="n"/>
-      <c r="C154" s="6" t="n"/>
-      <c r="D154" s="6" t="n"/>
-      <c r="E154" s="6" t="n"/>
-      <c r="F154" s="6" t="n"/>
-      <c r="G154" s="6" t="n"/>
-      <c r="H154" s="6" t="n"/>
-      <c r="I154" s="6" t="n"/>
-      <c r="J154" s="6" t="n"/>
-      <c r="K154" s="6" t="n"/>
-      <c r="L154" s="6" t="n"/>
-      <c r="M154" s="6" t="n"/>
-      <c r="N154" s="6" t="n"/>
-      <c r="O154" s="6" t="n"/>
-      <c r="P154" s="6" t="n"/>
-      <c r="Q154" s="6" t="n"/>
-      <c r="R154" s="6" t="n"/>
-      <c r="S154" s="6" t="n"/>
-      <c r="T154" s="6" t="n"/>
-      <c r="U154" s="6" t="n"/>
-      <c r="V154" s="6" t="n"/>
-      <c r="W154" s="6" t="n"/>
-      <c r="X154" s="6" t="n"/>
-      <c r="Y154" s="6" t="n"/>
-      <c r="Z154" s="6" t="n"/>
-    </row>
-    <row r="155" ht="15.75" customHeight="1" s="5">
-      <c r="A155" s="6" t="n"/>
-      <c r="B155" s="6" t="n"/>
-      <c r="C155" s="6" t="n"/>
-      <c r="D155" s="6" t="n"/>
-      <c r="E155" s="6" t="n"/>
-      <c r="F155" s="6" t="n"/>
-      <c r="G155" s="6" t="n"/>
-      <c r="H155" s="6" t="n"/>
-      <c r="I155" s="6" t="n"/>
-      <c r="J155" s="6" t="n"/>
-      <c r="K155" s="6" t="n"/>
-      <c r="L155" s="6" t="n"/>
-      <c r="M155" s="6" t="n"/>
-      <c r="N155" s="6" t="n"/>
-      <c r="O155" s="6" t="n"/>
-      <c r="P155" s="6" t="n"/>
-      <c r="Q155" s="6" t="n"/>
-      <c r="R155" s="6" t="n"/>
-      <c r="S155" s="6" t="n"/>
-      <c r="T155" s="6" t="n"/>
-      <c r="U155" s="6" t="n"/>
-      <c r="V155" s="6" t="n"/>
-      <c r="W155" s="6" t="n"/>
-      <c r="X155" s="6" t="n"/>
-      <c r="Y155" s="6" t="n"/>
-      <c r="Z155" s="6" t="n"/>
-    </row>
-    <row r="156" ht="15.75" customHeight="1" s="5">
-      <c r="A156" s="6" t="n"/>
-      <c r="B156" s="6" t="n"/>
-      <c r="C156" s="6" t="n"/>
-      <c r="D156" s="6" t="n"/>
-      <c r="E156" s="6" t="n"/>
-      <c r="F156" s="6" t="n"/>
-      <c r="G156" s="6" t="n"/>
-      <c r="H156" s="6" t="n"/>
-      <c r="I156" s="6" t="n"/>
-      <c r="J156" s="6" t="n"/>
-      <c r="K156" s="6" t="n"/>
-      <c r="L156" s="6" t="n"/>
-      <c r="M156" s="6" t="n"/>
-      <c r="N156" s="6" t="n"/>
-      <c r="O156" s="6" t="n"/>
-      <c r="P156" s="6" t="n"/>
-      <c r="Q156" s="6" t="n"/>
-      <c r="R156" s="6" t="n"/>
-      <c r="S156" s="6" t="n"/>
-      <c r="T156" s="6" t="n"/>
-      <c r="U156" s="6" t="n"/>
-      <c r="V156" s="6" t="n"/>
-      <c r="W156" s="6" t="n"/>
-      <c r="X156" s="6" t="n"/>
-      <c r="Y156" s="6" t="n"/>
-      <c r="Z156" s="6" t="n"/>
-    </row>
-    <row r="157" ht="15.75" customHeight="1" s="5">
-      <c r="A157" s="6" t="n"/>
-      <c r="B157" s="6" t="n"/>
-      <c r="C157" s="6" t="n"/>
-      <c r="D157" s="6" t="n"/>
-      <c r="E157" s="6" t="n"/>
-      <c r="F157" s="6" t="n"/>
-      <c r="G157" s="6" t="n"/>
-      <c r="H157" s="6" t="n"/>
-      <c r="I157" s="6" t="n"/>
-      <c r="J157" s="6" t="n"/>
-      <c r="K157" s="6" t="n"/>
-      <c r="L157" s="6" t="n"/>
-      <c r="M157" s="6" t="n"/>
-      <c r="N157" s="6" t="n"/>
-      <c r="O157" s="6" t="n"/>
-      <c r="P157" s="6" t="n"/>
-      <c r="Q157" s="6" t="n"/>
-      <c r="R157" s="6" t="n"/>
-      <c r="S157" s="6" t="n"/>
-      <c r="T157" s="6" t="n"/>
-      <c r="U157" s="6" t="n"/>
-      <c r="V157" s="6" t="n"/>
-      <c r="W157" s="6" t="n"/>
-      <c r="X157" s="6" t="n"/>
-      <c r="Y157" s="6" t="n"/>
-      <c r="Z157" s="6" t="n"/>
-    </row>
-    <row r="158" ht="15.75" customHeight="1" s="5">
-      <c r="A158" s="6" t="n"/>
-      <c r="B158" s="6" t="n"/>
-      <c r="C158" s="6" t="n"/>
-      <c r="D158" s="6" t="n"/>
-      <c r="E158" s="6" t="n"/>
-      <c r="F158" s="6" t="n"/>
-      <c r="G158" s="6" t="n"/>
-      <c r="H158" s="6" t="n"/>
-      <c r="I158" s="6" t="n"/>
-      <c r="J158" s="6" t="n"/>
-      <c r="K158" s="6" t="n"/>
-      <c r="L158" s="6" t="n"/>
-      <c r="M158" s="6" t="n"/>
-      <c r="N158" s="6" t="n"/>
-      <c r="O158" s="6" t="n"/>
-      <c r="P158" s="6" t="n"/>
-      <c r="Q158" s="6" t="n"/>
-      <c r="R158" s="6" t="n"/>
-      <c r="S158" s="6" t="n"/>
-      <c r="T158" s="6" t="n"/>
-      <c r="U158" s="6" t="n"/>
-      <c r="V158" s="6" t="n"/>
-      <c r="W158" s="6" t="n"/>
-      <c r="X158" s="6" t="n"/>
-      <c r="Y158" s="6" t="n"/>
-      <c r="Z158" s="6" t="n"/>
-    </row>
-    <row r="159" ht="15.75" customHeight="1" s="5">
-      <c r="A159" s="6" t="n"/>
-      <c r="B159" s="6" t="n"/>
-      <c r="C159" s="6" t="n"/>
-      <c r="D159" s="6" t="n"/>
-      <c r="E159" s="6" t="n"/>
-      <c r="F159" s="6" t="n"/>
-      <c r="G159" s="6" t="n"/>
-      <c r="H159" s="6" t="n"/>
-      <c r="I159" s="6" t="n"/>
-      <c r="J159" s="6" t="n"/>
-      <c r="K159" s="6" t="n"/>
-      <c r="L159" s="6" t="n"/>
-      <c r="M159" s="6" t="n"/>
-      <c r="N159" s="6" t="n"/>
-      <c r="O159" s="6" t="n"/>
-      <c r="P159" s="6" t="n"/>
-      <c r="Q159" s="6" t="n"/>
-      <c r="R159" s="6" t="n"/>
-      <c r="S159" s="6" t="n"/>
-      <c r="T159" s="6" t="n"/>
-      <c r="U159" s="6" t="n"/>
-      <c r="V159" s="6" t="n"/>
-      <c r="W159" s="6" t="n"/>
-      <c r="X159" s="6" t="n"/>
-      <c r="Y159" s="6" t="n"/>
-      <c r="Z159" s="6" t="n"/>
-    </row>
-    <row r="160" ht="15.75" customHeight="1" s="5">
-      <c r="A160" s="6" t="n"/>
-      <c r="B160" s="6" t="n"/>
-      <c r="C160" s="6" t="n"/>
-      <c r="D160" s="6" t="n"/>
-      <c r="E160" s="6" t="n"/>
-      <c r="F160" s="6" t="n"/>
-      <c r="G160" s="6" t="n"/>
-      <c r="H160" s="6" t="n"/>
-      <c r="I160" s="6" t="n"/>
-      <c r="J160" s="6" t="n"/>
-      <c r="K160" s="6" t="n"/>
-      <c r="L160" s="6" t="n"/>
-      <c r="M160" s="6" t="n"/>
-      <c r="N160" s="6" t="n"/>
-      <c r="O160" s="6" t="n"/>
-      <c r="P160" s="6" t="n"/>
-      <c r="Q160" s="6" t="n"/>
-      <c r="R160" s="6" t="n"/>
-      <c r="S160" s="6" t="n"/>
-      <c r="T160" s="6" t="n"/>
-      <c r="U160" s="6" t="n"/>
-      <c r="V160" s="6" t="n"/>
-      <c r="W160" s="6" t="n"/>
-      <c r="X160" s="6" t="n"/>
-      <c r="Y160" s="6" t="n"/>
-      <c r="Z160" s="6" t="n"/>
-    </row>
-    <row r="161" ht="15.75" customHeight="1" s="5">
-      <c r="A161" s="6" t="n"/>
-      <c r="B161" s="6" t="n"/>
-      <c r="C161" s="6" t="n"/>
-      <c r="D161" s="6" t="n"/>
-      <c r="E161" s="6" t="n"/>
-      <c r="F161" s="6" t="n"/>
-      <c r="G161" s="6" t="n"/>
-      <c r="H161" s="6" t="n"/>
-      <c r="I161" s="6" t="n"/>
-      <c r="J161" s="6" t="n"/>
-      <c r="K161" s="6" t="n"/>
-      <c r="L161" s="6" t="n"/>
-      <c r="M161" s="6" t="n"/>
-      <c r="N161" s="6" t="n"/>
-      <c r="O161" s="6" t="n"/>
-      <c r="P161" s="6" t="n"/>
-      <c r="Q161" s="6" t="n"/>
-      <c r="R161" s="6" t="n"/>
-      <c r="S161" s="6" t="n"/>
-      <c r="T161" s="6" t="n"/>
-      <c r="U161" s="6" t="n"/>
-      <c r="V161" s="6" t="n"/>
-      <c r="W161" s="6" t="n"/>
-      <c r="X161" s="6" t="n"/>
-      <c r="Y161" s="6" t="n"/>
-      <c r="Z161" s="6" t="n"/>
-    </row>
-    <row r="162" ht="15.75" customHeight="1" s="5">
-      <c r="A162" s="6" t="n"/>
-      <c r="B162" s="6" t="n"/>
-      <c r="C162" s="6" t="n"/>
-      <c r="D162" s="6" t="n"/>
-      <c r="E162" s="6" t="n"/>
-      <c r="F162" s="6" t="n"/>
-      <c r="G162" s="6" t="n"/>
-      <c r="H162" s="6" t="n"/>
-      <c r="I162" s="6" t="n"/>
-      <c r="J162" s="6" t="n"/>
-      <c r="K162" s="6" t="n"/>
-      <c r="L162" s="6" t="n"/>
-      <c r="M162" s="6" t="n"/>
-      <c r="N162" s="6" t="n"/>
-      <c r="O162" s="6" t="n"/>
-      <c r="P162" s="6" t="n"/>
-      <c r="Q162" s="6" t="n"/>
-      <c r="R162" s="6" t="n"/>
-      <c r="S162" s="6" t="n"/>
-      <c r="T162" s="6" t="n"/>
-      <c r="U162" s="6" t="n"/>
-      <c r="V162" s="6" t="n"/>
-      <c r="W162" s="6" t="n"/>
-      <c r="X162" s="6" t="n"/>
-      <c r="Y162" s="6" t="n"/>
-      <c r="Z162" s="6" t="n"/>
-    </row>
-    <row r="163" ht="15.75" customHeight="1" s="5">
-      <c r="A163" s="6" t="n"/>
-      <c r="B163" s="6" t="n"/>
-      <c r="C163" s="6" t="n"/>
-      <c r="D163" s="6" t="n"/>
-      <c r="E163" s="6" t="n"/>
-      <c r="F163" s="6" t="n"/>
-      <c r="G163" s="6" t="n"/>
-      <c r="H163" s="6" t="n"/>
-      <c r="I163" s="6" t="n"/>
-      <c r="J163" s="6" t="n"/>
-      <c r="K163" s="6" t="n"/>
-      <c r="L163" s="6" t="n"/>
-      <c r="M163" s="6" t="n"/>
-      <c r="N163" s="6" t="n"/>
-      <c r="O163" s="6" t="n"/>
-      <c r="P163" s="6" t="n"/>
-      <c r="Q163" s="6" t="n"/>
-      <c r="R163" s="6" t="n"/>
-      <c r="S163" s="6" t="n"/>
-      <c r="T163" s="6" t="n"/>
-      <c r="U163" s="6" t="n"/>
-      <c r="V163" s="6" t="n"/>
-      <c r="W163" s="6" t="n"/>
-      <c r="X163" s="6" t="n"/>
-      <c r="Y163" s="6" t="n"/>
-      <c r="Z163" s="6" t="n"/>
-    </row>
-    <row r="164" ht="15.75" customHeight="1" s="5">
-      <c r="A164" s="6" t="n"/>
-      <c r="B164" s="6" t="n"/>
-      <c r="C164" s="6" t="n"/>
-      <c r="D164" s="6" t="n"/>
-      <c r="E164" s="6" t="n"/>
-      <c r="F164" s="6" t="n"/>
-      <c r="G164" s="6" t="n"/>
-      <c r="H164" s="6" t="n"/>
-      <c r="I164" s="6" t="n"/>
-      <c r="J164" s="6" t="n"/>
-      <c r="K164" s="6" t="n"/>
-      <c r="L164" s="6" t="n"/>
-      <c r="M164" s="6" t="n"/>
-      <c r="N164" s="6" t="n"/>
-      <c r="O164" s="6" t="n"/>
-      <c r="P164" s="6" t="n"/>
-      <c r="Q164" s="6" t="n"/>
-      <c r="R164" s="6" t="n"/>
-      <c r="S164" s="6" t="n"/>
-      <c r="T164" s="6" t="n"/>
-      <c r="U164" s="6" t="n"/>
-      <c r="V164" s="6" t="n"/>
-      <c r="W164" s="6" t="n"/>
-      <c r="X164" s="6" t="n"/>
-      <c r="Y164" s="6" t="n"/>
-      <c r="Z164" s="6" t="n"/>
-    </row>
-    <row r="165" ht="15.75" customHeight="1" s="5">
-      <c r="A165" s="6" t="n"/>
-      <c r="B165" s="6" t="n"/>
-      <c r="C165" s="6" t="n"/>
-      <c r="D165" s="6" t="n"/>
-      <c r="E165" s="6" t="n"/>
-      <c r="F165" s="6" t="n"/>
-      <c r="G165" s="6" t="n"/>
-      <c r="H165" s="6" t="n"/>
-      <c r="I165" s="6" t="n"/>
-      <c r="J165" s="6" t="n"/>
-      <c r="K165" s="6" t="n"/>
-      <c r="L165" s="6" t="n"/>
-      <c r="M165" s="6" t="n"/>
-      <c r="N165" s="6" t="n"/>
-      <c r="O165" s="6" t="n"/>
-      <c r="P165" s="6" t="n"/>
-      <c r="Q165" s="6" t="n"/>
-      <c r="R165" s="6" t="n"/>
-      <c r="S165" s="6" t="n"/>
-      <c r="T165" s="6" t="n"/>
-      <c r="U165" s="6" t="n"/>
-      <c r="V165" s="6" t="n"/>
-      <c r="W165" s="6" t="n"/>
-      <c r="X165" s="6" t="n"/>
-      <c r="Y165" s="6" t="n"/>
-      <c r="Z165" s="6" t="n"/>
-    </row>
-    <row r="166" ht="15.75" customHeight="1" s="5">
-      <c r="A166" s="6" t="n"/>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="6" t="n"/>
-      <c r="D166" s="6" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
-      <c r="G166" s="6" t="n"/>
-      <c r="H166" s="6" t="n"/>
-      <c r="I166" s="6" t="n"/>
-      <c r="J166" s="6" t="n"/>
-      <c r="K166" s="6" t="n"/>
-      <c r="L166" s="6" t="n"/>
-      <c r="M166" s="6" t="n"/>
-      <c r="N166" s="6" t="n"/>
-      <c r="O166" s="6" t="n"/>
-      <c r="P166" s="6" t="n"/>
-      <c r="Q166" s="6" t="n"/>
-      <c r="R166" s="6" t="n"/>
-      <c r="S166" s="6" t="n"/>
-      <c r="T166" s="6" t="n"/>
-      <c r="U166" s="6" t="n"/>
-      <c r="V166" s="6" t="n"/>
-      <c r="W166" s="6" t="n"/>
-      <c r="X166" s="6" t="n"/>
-      <c r="Y166" s="6" t="n"/>
-      <c r="Z166" s="6" t="n"/>
-    </row>
-    <row r="167" ht="15.75" customHeight="1" s="5">
-      <c r="A167" s="6" t="n"/>
-      <c r="B167" s="6" t="n"/>
-      <c r="C167" s="6" t="n"/>
-      <c r="D167" s="6" t="n"/>
-      <c r="E167" s="6" t="n"/>
-      <c r="F167" s="6" t="n"/>
-      <c r="G167" s="6" t="n"/>
-      <c r="H167" s="6" t="n"/>
-      <c r="I167" s="6" t="n"/>
-      <c r="J167" s="6" t="n"/>
-      <c r="K167" s="6" t="n"/>
-      <c r="L167" s="6" t="n"/>
-      <c r="M167" s="6" t="n"/>
-      <c r="N167" s="6" t="n"/>
-      <c r="O167" s="6" t="n"/>
-      <c r="P167" s="6" t="n"/>
-      <c r="Q167" s="6" t="n"/>
-      <c r="R167" s="6" t="n"/>
-      <c r="S167" s="6" t="n"/>
-      <c r="T167" s="6" t="n"/>
-      <c r="U167" s="6" t="n"/>
-      <c r="V167" s="6" t="n"/>
-      <c r="W167" s="6" t="n"/>
-      <c r="X167" s="6" t="n"/>
-      <c r="Y167" s="6" t="n"/>
-      <c r="Z167" s="6" t="n"/>
-    </row>
-    <row r="168" ht="15.75" customHeight="1" s="5">
-      <c r="A168" s="6" t="n"/>
-      <c r="B168" s="6" t="n"/>
-      <c r="C168" s="6" t="n"/>
-      <c r="D168" s="6" t="n"/>
-      <c r="E168" s="6" t="n"/>
-      <c r="F168" s="6" t="n"/>
-      <c r="G168" s="6" t="n"/>
-      <c r="H168" s="6" t="n"/>
-      <c r="I168" s="6" t="n"/>
-      <c r="J168" s="6" t="n"/>
-      <c r="K168" s="6" t="n"/>
-      <c r="L168" s="6" t="n"/>
-      <c r="M168" s="6" t="n"/>
-      <c r="N168" s="6" t="n"/>
-      <c r="O168" s="6" t="n"/>
-      <c r="P168" s="6" t="n"/>
-      <c r="Q168" s="6" t="n"/>
-      <c r="R168" s="6" t="n"/>
-      <c r="S168" s="6" t="n"/>
-      <c r="T168" s="6" t="n"/>
-      <c r="U168" s="6" t="n"/>
-      <c r="V168" s="6" t="n"/>
-      <c r="W168" s="6" t="n"/>
-      <c r="X168" s="6" t="n"/>
-      <c r="Y168" s="6" t="n"/>
-      <c r="Z168" s="6" t="n"/>
-    </row>
-    <row r="169" ht="15.75" customHeight="1" s="5">
-      <c r="A169" s="6" t="n"/>
-      <c r="B169" s="6" t="n"/>
-      <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-      <c r="E169" s="6" t="n"/>
-      <c r="F169" s="6" t="n"/>
-      <c r="G169" s="6" t="n"/>
-      <c r="H169" s="6" t="n"/>
-      <c r="I169" s="6" t="n"/>
-      <c r="J169" s="6" t="n"/>
-      <c r="K169" s="6" t="n"/>
-      <c r="L169" s="6" t="n"/>
-      <c r="M169" s="6" t="n"/>
-      <c r="N169" s="6" t="n"/>
-      <c r="O169" s="6" t="n"/>
-      <c r="P169" s="6" t="n"/>
-      <c r="Q169" s="6" t="n"/>
-      <c r="R169" s="6" t="n"/>
-      <c r="S169" s="6" t="n"/>
-      <c r="T169" s="6" t="n"/>
-      <c r="U169" s="6" t="n"/>
-      <c r="V169" s="6" t="n"/>
-      <c r="W169" s="6" t="n"/>
-      <c r="X169" s="6" t="n"/>
-      <c r="Y169" s="6" t="n"/>
-      <c r="Z169" s="6" t="n"/>
-    </row>
-    <row r="170" ht="15.75" customHeight="1" s="5">
-      <c r="A170" s="6" t="n"/>
-      <c r="B170" s="6" t="n"/>
-      <c r="C170" s="6" t="n"/>
-      <c r="D170" s="6" t="n"/>
-      <c r="E170" s="6" t="n"/>
-      <c r="F170" s="6" t="n"/>
-      <c r="G170" s="6" t="n"/>
-      <c r="H170" s="6" t="n"/>
-      <c r="I170" s="6" t="n"/>
-      <c r="J170" s="6" t="n"/>
-      <c r="K170" s="6" t="n"/>
-      <c r="L170" s="6" t="n"/>
-      <c r="M170" s="6" t="n"/>
-      <c r="N170" s="6" t="n"/>
-      <c r="O170" s="6" t="n"/>
-      <c r="P170" s="6" t="n"/>
-      <c r="Q170" s="6" t="n"/>
-      <c r="R170" s="6" t="n"/>
-      <c r="S170" s="6" t="n"/>
-      <c r="T170" s="6" t="n"/>
-      <c r="U170" s="6" t="n"/>
-      <c r="V170" s="6" t="n"/>
-      <c r="W170" s="6" t="n"/>
-      <c r="X170" s="6" t="n"/>
-      <c r="Y170" s="6" t="n"/>
-      <c r="Z170" s="6" t="n"/>
-    </row>
-    <row r="171" ht="15.75" customHeight="1" s="5">
-      <c r="A171" s="6" t="n"/>
-      <c r="B171" s="6" t="n"/>
-      <c r="C171" s="6" t="n"/>
-      <c r="D171" s="6" t="n"/>
-      <c r="E171" s="6" t="n"/>
-      <c r="F171" s="6" t="n"/>
-      <c r="G171" s="6" t="n"/>
-      <c r="H171" s="6" t="n"/>
-      <c r="I171" s="6" t="n"/>
-      <c r="J171" s="6" t="n"/>
-      <c r="K171" s="6" t="n"/>
-      <c r="L171" s="6" t="n"/>
-      <c r="M171" s="6" t="n"/>
-      <c r="N171" s="6" t="n"/>
-      <c r="O171" s="6" t="n"/>
-      <c r="P171" s="6" t="n"/>
-      <c r="Q171" s="6" t="n"/>
-      <c r="R171" s="6" t="n"/>
-      <c r="S171" s="6" t="n"/>
-      <c r="T171" s="6" t="n"/>
-      <c r="U171" s="6" t="n"/>
-      <c r="V171" s="6" t="n"/>
-      <c r="W171" s="6" t="n"/>
-      <c r="X171" s="6" t="n"/>
-      <c r="Y171" s="6" t="n"/>
-      <c r="Z171" s="6" t="n"/>
-    </row>
-    <row r="172" ht="15.75" customHeight="1" s="5">
-      <c r="A172" s="6" t="n"/>
-      <c r="B172" s="6" t="n"/>
-      <c r="C172" s="6" t="n"/>
-      <c r="D172" s="6" t="n"/>
-      <c r="E172" s="6" t="n"/>
-      <c r="F172" s="6" t="n"/>
-      <c r="G172" s="6" t="n"/>
-      <c r="H172" s="6" t="n"/>
-      <c r="I172" s="6" t="n"/>
-      <c r="J172" s="6" t="n"/>
-      <c r="K172" s="6" t="n"/>
-      <c r="L172" s="6" t="n"/>
-      <c r="M172" s="6" t="n"/>
-      <c r="N172" s="6" t="n"/>
-      <c r="O172" s="6" t="n"/>
-      <c r="P172" s="6" t="n"/>
-      <c r="Q172" s="6" t="n"/>
-      <c r="R172" s="6" t="n"/>
-      <c r="S172" s="6" t="n"/>
-      <c r="T172" s="6" t="n"/>
-      <c r="U172" s="6" t="n"/>
-      <c r="V172" s="6" t="n"/>
-      <c r="W172" s="6" t="n"/>
-      <c r="X172" s="6" t="n"/>
-      <c r="Y172" s="6" t="n"/>
-      <c r="Z172" s="6" t="n"/>
-    </row>
-    <row r="173" ht="15.75" customHeight="1" s="5">
-      <c r="A173" s="6" t="n"/>
-      <c r="B173" s="6" t="n"/>
-      <c r="C173" s="6" t="n"/>
-      <c r="D173" s="6" t="n"/>
-      <c r="E173" s="6" t="n"/>
-      <c r="F173" s="6" t="n"/>
-      <c r="G173" s="6" t="n"/>
-      <c r="H173" s="6" t="n"/>
-      <c r="I173" s="6" t="n"/>
-      <c r="J173" s="6" t="n"/>
-      <c r="K173" s="6" t="n"/>
-      <c r="L173" s="6" t="n"/>
-      <c r="M173" s="6" t="n"/>
-      <c r="N173" s="6" t="n"/>
-      <c r="O173" s="6" t="n"/>
-      <c r="P173" s="6" t="n"/>
-      <c r="Q173" s="6" t="n"/>
-      <c r="R173" s="6" t="n"/>
-      <c r="S173" s="6" t="n"/>
-      <c r="T173" s="6" t="n"/>
-      <c r="U173" s="6" t="n"/>
-      <c r="V173" s="6" t="n"/>
-      <c r="W173" s="6" t="n"/>
-      <c r="X173" s="6" t="n"/>
-      <c r="Y173" s="6" t="n"/>
-      <c r="Z173" s="6" t="n"/>
-    </row>
-    <row r="174" ht="15.75" customHeight="1" s="5">
-      <c r="A174" s="6" t="n"/>
-      <c r="B174" s="6" t="n"/>
-      <c r="C174" s="6" t="n"/>
-      <c r="D174" s="6" t="n"/>
-      <c r="E174" s="6" t="n"/>
-      <c r="F174" s="6" t="n"/>
-      <c r="G174" s="6" t="n"/>
-      <c r="H174" s="6" t="n"/>
-      <c r="I174" s="6" t="n"/>
-      <c r="J174" s="6" t="n"/>
-      <c r="K174" s="6" t="n"/>
-      <c r="L174" s="6" t="n"/>
-      <c r="M174" s="6" t="n"/>
-      <c r="N174" s="6" t="n"/>
-      <c r="O174" s="6" t="n"/>
-      <c r="P174" s="6" t="n"/>
-      <c r="Q174" s="6" t="n"/>
-      <c r="R174" s="6" t="n"/>
-      <c r="S174" s="6" t="n"/>
-      <c r="T174" s="6" t="n"/>
-      <c r="U174" s="6" t="n"/>
-      <c r="V174" s="6" t="n"/>
-      <c r="W174" s="6" t="n"/>
-      <c r="X174" s="6" t="n"/>
-      <c r="Y174" s="6" t="n"/>
-      <c r="Z174" s="6" t="n"/>
-    </row>
-    <row r="175" ht="15.75" customHeight="1" s="5">
-      <c r="A175" s="6" t="n"/>
-      <c r="B175" s="6" t="n"/>
-      <c r="C175" s="6" t="n"/>
-      <c r="D175" s="6" t="n"/>
-      <c r="E175" s="6" t="n"/>
-      <c r="F175" s="6" t="n"/>
-      <c r="G175" s="6" t="n"/>
-      <c r="H175" s="6" t="n"/>
-      <c r="I175" s="6" t="n"/>
-      <c r="J175" s="6" t="n"/>
-      <c r="K175" s="6" t="n"/>
-      <c r="L175" s="6" t="n"/>
-      <c r="M175" s="6" t="n"/>
-      <c r="N175" s="6" t="n"/>
-      <c r="O175" s="6" t="n"/>
-      <c r="P175" s="6" t="n"/>
-      <c r="Q175" s="6" t="n"/>
-      <c r="R175" s="6" t="n"/>
-      <c r="S175" s="6" t="n"/>
-      <c r="T175" s="6" t="n"/>
-      <c r="U175" s="6" t="n"/>
-      <c r="V175" s="6" t="n"/>
-      <c r="W175" s="6" t="n"/>
-      <c r="X175" s="6" t="n"/>
-      <c r="Y175" s="6" t="n"/>
-      <c r="Z175" s="6" t="n"/>
-    </row>
-    <row r="176" ht="15.75" customHeight="1" s="5">
-      <c r="A176" s="6" t="n"/>
-      <c r="B176" s="6" t="n"/>
-      <c r="C176" s="6" t="n"/>
-      <c r="D176" s="6" t="n"/>
-      <c r="E176" s="6" t="n"/>
-      <c r="F176" s="6" t="n"/>
-      <c r="G176" s="6" t="n"/>
-      <c r="H176" s="6" t="n"/>
-      <c r="I176" s="6" t="n"/>
-      <c r="J176" s="6" t="n"/>
-      <c r="K176" s="6" t="n"/>
-      <c r="L176" s="6" t="n"/>
-      <c r="M176" s="6" t="n"/>
-      <c r="N176" s="6" t="n"/>
-      <c r="O176" s="6" t="n"/>
-      <c r="P176" s="6" t="n"/>
-      <c r="Q176" s="6" t="n"/>
-      <c r="R176" s="6" t="n"/>
-      <c r="S176" s="6" t="n"/>
-      <c r="T176" s="6" t="n"/>
-      <c r="U176" s="6" t="n"/>
-      <c r="V176" s="6" t="n"/>
-      <c r="W176" s="6" t="n"/>
-      <c r="X176" s="6" t="n"/>
-      <c r="Y176" s="6" t="n"/>
-      <c r="Z176" s="6" t="n"/>
-    </row>
-    <row r="177" ht="15.75" customHeight="1" s="5">
-      <c r="A177" s="6" t="n"/>
-      <c r="B177" s="6" t="n"/>
-      <c r="C177" s="6" t="n"/>
-      <c r="D177" s="6" t="n"/>
-      <c r="E177" s="6" t="n"/>
-      <c r="F177" s="6" t="n"/>
-      <c r="G177" s="6" t="n"/>
-      <c r="H177" s="6" t="n"/>
-      <c r="I177" s="6" t="n"/>
-      <c r="J177" s="6" t="n"/>
-      <c r="K177" s="6" t="n"/>
-      <c r="L177" s="6" t="n"/>
-      <c r="M177" s="6" t="n"/>
-      <c r="N177" s="6" t="n"/>
-      <c r="O177" s="6" t="n"/>
-      <c r="P177" s="6" t="n"/>
-      <c r="Q177" s="6" t="n"/>
-      <c r="R177" s="6" t="n"/>
-      <c r="S177" s="6" t="n"/>
-      <c r="T177" s="6" t="n"/>
-      <c r="U177" s="6" t="n"/>
-      <c r="V177" s="6" t="n"/>
-      <c r="W177" s="6" t="n"/>
-      <c r="X177" s="6" t="n"/>
-      <c r="Y177" s="6" t="n"/>
-      <c r="Z177" s="6" t="n"/>
-    </row>
-    <row r="178" ht="15.75" customHeight="1" s="5">
-      <c r="A178" s="6" t="n"/>
-      <c r="B178" s="6" t="n"/>
-      <c r="C178" s="6" t="n"/>
-      <c r="D178" s="6" t="n"/>
-      <c r="E178" s="6" t="n"/>
-      <c r="F178" s="6" t="n"/>
-      <c r="G178" s="6" t="n"/>
-      <c r="H178" s="6" t="n"/>
-      <c r="I178" s="6" t="n"/>
-      <c r="J178" s="6" t="n"/>
-      <c r="K178" s="6" t="n"/>
-      <c r="L178" s="6" t="n"/>
-      <c r="M178" s="6" t="n"/>
-      <c r="N178" s="6" t="n"/>
-      <c r="O178" s="6" t="n"/>
-      <c r="P178" s="6" t="n"/>
-      <c r="Q178" s="6" t="n"/>
-      <c r="R178" s="6" t="n"/>
-      <c r="S178" s="6" t="n"/>
-      <c r="T178" s="6" t="n"/>
-      <c r="U178" s="6" t="n"/>
-      <c r="V178" s="6" t="n"/>
-      <c r="W178" s="6" t="n"/>
-      <c r="X178" s="6" t="n"/>
-      <c r="Y178" s="6" t="n"/>
-      <c r="Z178" s="6" t="n"/>
-    </row>
-    <row r="179" ht="15.75" customHeight="1" s="5">
-      <c r="A179" s="6" t="n"/>
-      <c r="B179" s="6" t="n"/>
-      <c r="C179" s="6" t="n"/>
-      <c r="D179" s="6" t="n"/>
-      <c r="E179" s="6" t="n"/>
-      <c r="F179" s="6" t="n"/>
-      <c r="G179" s="6" t="n"/>
-      <c r="H179" s="6" t="n"/>
-      <c r="I179" s="6" t="n"/>
-      <c r="J179" s="6" t="n"/>
-      <c r="K179" s="6" t="n"/>
-      <c r="L179" s="6" t="n"/>
-      <c r="M179" s="6" t="n"/>
-      <c r="N179" s="6" t="n"/>
-      <c r="O179" s="6" t="n"/>
-      <c r="P179" s="6" t="n"/>
-      <c r="Q179" s="6" t="n"/>
-      <c r="R179" s="6" t="n"/>
-      <c r="S179" s="6" t="n"/>
-      <c r="T179" s="6" t="n"/>
-      <c r="U179" s="6" t="n"/>
-      <c r="V179" s="6" t="n"/>
-      <c r="W179" s="6" t="n"/>
-      <c r="X179" s="6" t="n"/>
-      <c r="Y179" s="6" t="n"/>
-      <c r="Z179" s="6" t="n"/>
-    </row>
-    <row r="180" ht="15.75" customHeight="1" s="5">
-      <c r="A180" s="6" t="n"/>
-      <c r="B180" s="6" t="n"/>
-      <c r="C180" s="6" t="n"/>
-      <c r="D180" s="6" t="n"/>
-      <c r="E180" s="6" t="n"/>
-      <c r="F180" s="6" t="n"/>
-      <c r="G180" s="6" t="n"/>
-      <c r="H180" s="6" t="n"/>
-      <c r="I180" s="6" t="n"/>
-      <c r="J180" s="6" t="n"/>
-      <c r="K180" s="6" t="n"/>
-      <c r="L180" s="6" t="n"/>
-      <c r="M180" s="6" t="n"/>
-      <c r="N180" s="6" t="n"/>
-      <c r="O180" s="6" t="n"/>
-      <c r="P180" s="6" t="n"/>
-      <c r="Q180" s="6" t="n"/>
-      <c r="R180" s="6" t="n"/>
-      <c r="S180" s="6" t="n"/>
-      <c r="T180" s="6" t="n"/>
-      <c r="U180" s="6" t="n"/>
-      <c r="V180" s="6" t="n"/>
-      <c r="W180" s="6" t="n"/>
-      <c r="X180" s="6" t="n"/>
-      <c r="Y180" s="6" t="n"/>
-      <c r="Z180" s="6" t="n"/>
-    </row>
-    <row r="181" ht="15.75" customHeight="1" s="5">
-      <c r="A181" s="6" t="n"/>
-      <c r="B181" s="6" t="n"/>
-      <c r="C181" s="6" t="n"/>
-      <c r="D181" s="6" t="n"/>
-      <c r="E181" s="6" t="n"/>
-      <c r="F181" s="6" t="n"/>
-      <c r="G181" s="6" t="n"/>
-      <c r="H181" s="6" t="n"/>
-      <c r="I181" s="6" t="n"/>
-      <c r="J181" s="6" t="n"/>
-      <c r="K181" s="6" t="n"/>
-      <c r="L181" s="6" t="n"/>
-      <c r="M181" s="6" t="n"/>
-      <c r="N181" s="6" t="n"/>
-      <c r="O181" s="6" t="n"/>
-      <c r="P181" s="6" t="n"/>
-      <c r="Q181" s="6" t="n"/>
-      <c r="R181" s="6" t="n"/>
-      <c r="S181" s="6" t="n"/>
-      <c r="T181" s="6" t="n"/>
-      <c r="U181" s="6" t="n"/>
-      <c r="V181" s="6" t="n"/>
-      <c r="W181" s="6" t="n"/>
-      <c r="X181" s="6" t="n"/>
-      <c r="Y181" s="6" t="n"/>
-      <c r="Z181" s="6" t="n"/>
-    </row>
-    <row r="182" ht="15.75" customHeight="1" s="5">
-      <c r="A182" s="6" t="n"/>
-      <c r="B182" s="6" t="n"/>
-      <c r="C182" s="6" t="n"/>
-      <c r="D182" s="6" t="n"/>
-      <c r="E182" s="6" t="n"/>
-      <c r="F182" s="6" t="n"/>
-      <c r="G182" s="6" t="n"/>
-      <c r="H182" s="6" t="n"/>
-      <c r="I182" s="6" t="n"/>
-      <c r="J182" s="6" t="n"/>
-      <c r="K182" s="6" t="n"/>
-      <c r="L182" s="6" t="n"/>
-      <c r="M182" s="6" t="n"/>
-      <c r="N182" s="6" t="n"/>
-      <c r="O182" s="6" t="n"/>
-      <c r="P182" s="6" t="n"/>
-      <c r="Q182" s="6" t="n"/>
-      <c r="R182" s="6" t="n"/>
-      <c r="S182" s="6" t="n"/>
-      <c r="T182" s="6" t="n"/>
-      <c r="U182" s="6" t="n"/>
-      <c r="V182" s="6" t="n"/>
-      <c r="W182" s="6" t="n"/>
-      <c r="X182" s="6" t="n"/>
-      <c r="Y182" s="6" t="n"/>
-      <c r="Z182" s="6" t="n"/>
-    </row>
-    <row r="183" ht="15.75" customHeight="1" s="5">
-      <c r="A183" s="6" t="n"/>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="n"/>
-      <c r="D183" s="6" t="n"/>
-      <c r="E183" s="6" t="n"/>
-      <c r="F183" s="6" t="n"/>
-      <c r="G183" s="6" t="n"/>
-      <c r="H183" s="6" t="n"/>
-      <c r="I183" s="6" t="n"/>
-      <c r="J183" s="6" t="n"/>
-      <c r="K183" s="6" t="n"/>
-      <c r="L183" s="6" t="n"/>
-      <c r="M183" s="6" t="n"/>
-      <c r="N183" s="6" t="n"/>
-      <c r="O183" s="6" t="n"/>
-      <c r="P183" s="6" t="n"/>
-      <c r="Q183" s="6" t="n"/>
-      <c r="R183" s="6" t="n"/>
-      <c r="S183" s="6" t="n"/>
-      <c r="T183" s="6" t="n"/>
-      <c r="U183" s="6" t="n"/>
-      <c r="V183" s="6" t="n"/>
-      <c r="W183" s="6" t="n"/>
-      <c r="X183" s="6" t="n"/>
-      <c r="Y183" s="6" t="n"/>
-      <c r="Z183" s="6" t="n"/>
-    </row>
-    <row r="184" ht="15.75" customHeight="1" s="5">
-      <c r="A184" s="6" t="n"/>
-      <c r="B184" s="6" t="n"/>
-      <c r="C184" s="6" t="n"/>
-      <c r="D184" s="6" t="n"/>
-      <c r="E184" s="6" t="n"/>
-      <c r="F184" s="6" t="n"/>
-      <c r="G184" s="6" t="n"/>
-      <c r="H184" s="6" t="n"/>
-      <c r="I184" s="6" t="n"/>
-      <c r="J184" s="6" t="n"/>
-      <c r="K184" s="6" t="n"/>
-      <c r="L184" s="6" t="n"/>
-      <c r="M184" s="6" t="n"/>
-      <c r="N184" s="6" t="n"/>
-      <c r="O184" s="6" t="n"/>
-      <c r="P184" s="6" t="n"/>
-      <c r="Q184" s="6" t="n"/>
-      <c r="R184" s="6" t="n"/>
-      <c r="S184" s="6" t="n"/>
-      <c r="T184" s="6" t="n"/>
-      <c r="U184" s="6" t="n"/>
-      <c r="V184" s="6" t="n"/>
-      <c r="W184" s="6" t="n"/>
-      <c r="X184" s="6" t="n"/>
-      <c r="Y184" s="6" t="n"/>
-      <c r="Z184" s="6" t="n"/>
-    </row>
-    <row r="185" ht="15.75" customHeight="1" s="5">
-      <c r="A185" s="6" t="n"/>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6" t="n"/>
-      <c r="E185" s="6" t="n"/>
-      <c r="F185" s="6" t="n"/>
-      <c r="G185" s="6" t="n"/>
-      <c r="H185" s="6" t="n"/>
-      <c r="I185" s="6" t="n"/>
-      <c r="J185" s="6" t="n"/>
-      <c r="K185" s="6" t="n"/>
-      <c r="L185" s="6" t="n"/>
-      <c r="M185" s="6" t="n"/>
-      <c r="N185" s="6" t="n"/>
-      <c r="O185" s="6" t="n"/>
-      <c r="P185" s="6" t="n"/>
-      <c r="Q185" s="6" t="n"/>
-      <c r="R185" s="6" t="n"/>
-      <c r="S185" s="6" t="n"/>
-      <c r="T185" s="6" t="n"/>
-      <c r="U185" s="6" t="n"/>
-      <c r="V185" s="6" t="n"/>
-      <c r="W185" s="6" t="n"/>
-      <c r="X185" s="6" t="n"/>
-      <c r="Y185" s="6" t="n"/>
-      <c r="Z185" s="6" t="n"/>
-    </row>
-    <row r="186" ht="15.75" customHeight="1" s="5">
-      <c r="A186" s="6" t="n"/>
-      <c r="B186" s="6" t="n"/>
-      <c r="C186" s="6" t="n"/>
-      <c r="D186" s="6" t="n"/>
-      <c r="E186" s="6" t="n"/>
-      <c r="F186" s="6" t="n"/>
-      <c r="G186" s="6" t="n"/>
-      <c r="H186" s="6" t="n"/>
-      <c r="I186" s="6" t="n"/>
-      <c r="J186" s="6" t="n"/>
-      <c r="K186" s="6" t="n"/>
-      <c r="L186" s="6" t="n"/>
-      <c r="M186" s="6" t="n"/>
-      <c r="N186" s="6" t="n"/>
-      <c r="O186" s="6" t="n"/>
-      <c r="P186" s="6" t="n"/>
-      <c r="Q186" s="6" t="n"/>
-      <c r="R186" s="6" t="n"/>
-      <c r="S186" s="6" t="n"/>
-      <c r="T186" s="6" t="n"/>
-      <c r="U186" s="6" t="n"/>
-      <c r="V186" s="6" t="n"/>
-      <c r="W186" s="6" t="n"/>
-      <c r="X186" s="6" t="n"/>
-      <c r="Y186" s="6" t="n"/>
-      <c r="Z186" s="6" t="n"/>
-    </row>
-    <row r="187" ht="15.75" customHeight="1" s="5">
-      <c r="A187" s="6" t="n"/>
-      <c r="B187" s="6" t="n"/>
-      <c r="C187" s="6" t="n"/>
-      <c r="D187" s="6" t="n"/>
-      <c r="E187" s="6" t="n"/>
-      <c r="F187" s="6" t="n"/>
-      <c r="G187" s="6" t="n"/>
-      <c r="H187" s="6" t="n"/>
-      <c r="I187" s="6" t="n"/>
-      <c r="J187" s="6" t="n"/>
-      <c r="K187" s="6" t="n"/>
-      <c r="L187" s="6" t="n"/>
-      <c r="M187" s="6" t="n"/>
-      <c r="N187" s="6" t="n"/>
-      <c r="O187" s="6" t="n"/>
-      <c r="P187" s="6" t="n"/>
-      <c r="Q187" s="6" t="n"/>
-      <c r="R187" s="6" t="n"/>
-      <c r="S187" s="6" t="n"/>
-      <c r="T187" s="6" t="n"/>
-      <c r="U187" s="6" t="n"/>
-      <c r="V187" s="6" t="n"/>
-      <c r="W187" s="6" t="n"/>
-      <c r="X187" s="6" t="n"/>
-      <c r="Y187" s="6" t="n"/>
-      <c r="Z187" s="6" t="n"/>
-    </row>
-    <row r="188" ht="15.75" customHeight="1" s="5">
-      <c r="A188" s="6" t="n"/>
-      <c r="B188" s="6" t="n"/>
-      <c r="C188" s="6" t="n"/>
-      <c r="D188" s="6" t="n"/>
-      <c r="E188" s="6" t="n"/>
-      <c r="F188" s="6" t="n"/>
-      <c r="G188" s="6" t="n"/>
-      <c r="H188" s="6" t="n"/>
-      <c r="I188" s="6" t="n"/>
-      <c r="J188" s="6" t="n"/>
-      <c r="K188" s="6" t="n"/>
-      <c r="L188" s="6" t="n"/>
-      <c r="M188" s="6" t="n"/>
-      <c r="N188" s="6" t="n"/>
-      <c r="O188" s="6" t="n"/>
-      <c r="P188" s="6" t="n"/>
-      <c r="Q188" s="6" t="n"/>
-      <c r="R188" s="6" t="n"/>
-      <c r="S188" s="6" t="n"/>
-      <c r="T188" s="6" t="n"/>
-      <c r="U188" s="6" t="n"/>
-      <c r="V188" s="6" t="n"/>
-      <c r="W188" s="6" t="n"/>
-      <c r="X188" s="6" t="n"/>
-      <c r="Y188" s="6" t="n"/>
-      <c r="Z188" s="6" t="n"/>
-    </row>
-    <row r="189" ht="15.75" customHeight="1" s="5">
-      <c r="A189" s="6" t="n"/>
-      <c r="B189" s="6" t="n"/>
-      <c r="C189" s="6" t="n"/>
-      <c r="D189" s="6" t="n"/>
-      <c r="E189" s="6" t="n"/>
-      <c r="F189" s="6" t="n"/>
-      <c r="G189" s="6" t="n"/>
-      <c r="H189" s="6" t="n"/>
-      <c r="I189" s="6" t="n"/>
-      <c r="J189" s="6" t="n"/>
-      <c r="K189" s="6" t="n"/>
-      <c r="L189" s="6" t="n"/>
-      <c r="M189" s="6" t="n"/>
-      <c r="N189" s="6" t="n"/>
-      <c r="O189" s="6" t="n"/>
-      <c r="P189" s="6" t="n"/>
-      <c r="Q189" s="6" t="n"/>
-      <c r="R189" s="6" t="n"/>
-      <c r="S189" s="6" t="n"/>
-      <c r="T189" s="6" t="n"/>
-      <c r="U189" s="6" t="n"/>
-      <c r="V189" s="6" t="n"/>
-      <c r="W189" s="6" t="n"/>
-      <c r="X189" s="6" t="n"/>
-      <c r="Y189" s="6" t="n"/>
-      <c r="Z189" s="6" t="n"/>
-    </row>
-    <row r="190" ht="15.75" customHeight="1" s="5">
-      <c r="A190" s="6" t="n"/>
-      <c r="B190" s="6" t="n"/>
-      <c r="C190" s="6" t="n"/>
-      <c r="D190" s="6" t="n"/>
-      <c r="E190" s="6" t="n"/>
-      <c r="F190" s="6" t="n"/>
-      <c r="G190" s="6" t="n"/>
-      <c r="H190" s="6" t="n"/>
-      <c r="I190" s="6" t="n"/>
-      <c r="J190" s="6" t="n"/>
-      <c r="K190" s="6" t="n"/>
-      <c r="L190" s="6" t="n"/>
-      <c r="M190" s="6" t="n"/>
-      <c r="N190" s="6" t="n"/>
-      <c r="O190" s="6" t="n"/>
-      <c r="P190" s="6" t="n"/>
-      <c r="Q190" s="6" t="n"/>
-      <c r="R190" s="6" t="n"/>
-      <c r="S190" s="6" t="n"/>
-      <c r="T190" s="6" t="n"/>
-      <c r="U190" s="6" t="n"/>
-      <c r="V190" s="6" t="n"/>
-      <c r="W190" s="6" t="n"/>
-      <c r="X190" s="6" t="n"/>
-      <c r="Y190" s="6" t="n"/>
-      <c r="Z190" s="6" t="n"/>
-    </row>
-    <row r="191" ht="15.75" customHeight="1" s="5">
-      <c r="A191" s="6" t="n"/>
-      <c r="B191" s="6" t="n"/>
-      <c r="C191" s="6" t="n"/>
-      <c r="D191" s="6" t="n"/>
-      <c r="E191" s="6" t="n"/>
-      <c r="F191" s="6" t="n"/>
-      <c r="G191" s="6" t="n"/>
-      <c r="H191" s="6" t="n"/>
-      <c r="I191" s="6" t="n"/>
-      <c r="J191" s="6" t="n"/>
-      <c r="K191" s="6" t="n"/>
-      <c r="L191" s="6" t="n"/>
-      <c r="M191" s="6" t="n"/>
-      <c r="N191" s="6" t="n"/>
-      <c r="O191" s="6" t="n"/>
-      <c r="P191" s="6" t="n"/>
-      <c r="Q191" s="6" t="n"/>
-      <c r="R191" s="6" t="n"/>
-      <c r="S191" s="6" t="n"/>
-      <c r="T191" s="6" t="n"/>
-      <c r="U191" s="6" t="n"/>
-      <c r="V191" s="6" t="n"/>
-      <c r="W191" s="6" t="n"/>
-      <c r="X191" s="6" t="n"/>
-      <c r="Y191" s="6" t="n"/>
-      <c r="Z191" s="6" t="n"/>
-    </row>
-    <row r="192" ht="15.75" customHeight="1" s="5">
-      <c r="A192" s="6" t="n"/>
-      <c r="B192" s="6" t="n"/>
-      <c r="C192" s="6" t="n"/>
-      <c r="D192" s="6" t="n"/>
-      <c r="E192" s="6" t="n"/>
-      <c r="F192" s="6" t="n"/>
-      <c r="G192" s="6" t="n"/>
-      <c r="H192" s="6" t="n"/>
-      <c r="I192" s="6" t="n"/>
-      <c r="J192" s="6" t="n"/>
-      <c r="K192" s="6" t="n"/>
-      <c r="L192" s="6" t="n"/>
-      <c r="M192" s="6" t="n"/>
-      <c r="N192" s="6" t="n"/>
-      <c r="O192" s="6" t="n"/>
-      <c r="P192" s="6" t="n"/>
-      <c r="Q192" s="6" t="n"/>
-      <c r="R192" s="6" t="n"/>
-      <c r="S192" s="6" t="n"/>
-      <c r="T192" s="6" t="n"/>
-      <c r="U192" s="6" t="n"/>
-      <c r="V192" s="6" t="n"/>
-      <c r="W192" s="6" t="n"/>
-      <c r="X192" s="6" t="n"/>
-      <c r="Y192" s="6" t="n"/>
-      <c r="Z192" s="6" t="n"/>
-    </row>
-    <row r="193" ht="15.75" customHeight="1" s="5">
-      <c r="A193" s="6" t="n"/>
-      <c r="B193" s="6" t="n"/>
-      <c r="C193" s="6" t="n"/>
-      <c r="D193" s="6" t="n"/>
-      <c r="E193" s="6" t="n"/>
-      <c r="F193" s="6" t="n"/>
-      <c r="G193" s="6" t="n"/>
-      <c r="H193" s="6" t="n"/>
-      <c r="I193" s="6" t="n"/>
-      <c r="J193" s="6" t="n"/>
-      <c r="K193" s="6" t="n"/>
-      <c r="L193" s="6" t="n"/>
-      <c r="M193" s="6" t="n"/>
-      <c r="N193" s="6" t="n"/>
-      <c r="O193" s="6" t="n"/>
-      <c r="P193" s="6" t="n"/>
-      <c r="Q193" s="6" t="n"/>
-      <c r="R193" s="6" t="n"/>
-      <c r="S193" s="6" t="n"/>
-      <c r="T193" s="6" t="n"/>
-      <c r="U193" s="6" t="n"/>
-      <c r="V193" s="6" t="n"/>
-      <c r="W193" s="6" t="n"/>
-      <c r="X193" s="6" t="n"/>
-      <c r="Y193" s="6" t="n"/>
-      <c r="Z193" s="6" t="n"/>
-    </row>
-    <row r="194" ht="15.75" customHeight="1" s="5">
-      <c r="A194" s="6" t="n"/>
-      <c r="B194" s="6" t="n"/>
-      <c r="C194" s="6" t="n"/>
-      <c r="D194" s="6" t="n"/>
-      <c r="E194" s="6" t="n"/>
-      <c r="F194" s="6" t="n"/>
-      <c r="G194" s="6" t="n"/>
-      <c r="H194" s="6" t="n"/>
-      <c r="I194" s="6" t="n"/>
-      <c r="J194" s="6" t="n"/>
-      <c r="K194" s="6" t="n"/>
-      <c r="L194" s="6" t="n"/>
-      <c r="M194" s="6" t="n"/>
-      <c r="N194" s="6" t="n"/>
-      <c r="O194" s="6" t="n"/>
-      <c r="P194" s="6" t="n"/>
-      <c r="Q194" s="6" t="n"/>
-      <c r="R194" s="6" t="n"/>
-      <c r="S194" s="6" t="n"/>
-      <c r="T194" s="6" t="n"/>
-      <c r="U194" s="6" t="n"/>
-      <c r="V194" s="6" t="n"/>
-      <c r="W194" s="6" t="n"/>
-      <c r="X194" s="6" t="n"/>
-      <c r="Y194" s="6" t="n"/>
-      <c r="Z194" s="6" t="n"/>
-    </row>
-    <row r="195" ht="15.75" customHeight="1" s="5">
-      <c r="A195" s="6" t="n"/>
-      <c r="B195" s="6" t="n"/>
-      <c r="C195" s="6" t="n"/>
-      <c r="D195" s="6" t="n"/>
-      <c r="E195" s="6" t="n"/>
-      <c r="F195" s="6" t="n"/>
-      <c r="G195" s="6" t="n"/>
-      <c r="H195" s="6" t="n"/>
-      <c r="I195" s="6" t="n"/>
-      <c r="J195" s="6" t="n"/>
-      <c r="K195" s="6" t="n"/>
-      <c r="L195" s="6" t="n"/>
-      <c r="M195" s="6" t="n"/>
-      <c r="N195" s="6" t="n"/>
-      <c r="O195" s="6" t="n"/>
-      <c r="P195" s="6" t="n"/>
-      <c r="Q195" s="6" t="n"/>
-      <c r="R195" s="6" t="n"/>
-      <c r="S195" s="6" t="n"/>
-      <c r="T195" s="6" t="n"/>
-      <c r="U195" s="6" t="n"/>
-      <c r="V195" s="6" t="n"/>
-      <c r="W195" s="6" t="n"/>
-      <c r="X195" s="6" t="n"/>
-      <c r="Y195" s="6" t="n"/>
-      <c r="Z195" s="6" t="n"/>
-    </row>
-    <row r="196" ht="15.75" customHeight="1" s="5">
-      <c r="A196" s="6" t="n"/>
-      <c r="B196" s="6" t="n"/>
-      <c r="C196" s="6" t="n"/>
-      <c r="D196" s="6" t="n"/>
-      <c r="E196" s="6" t="n"/>
-      <c r="F196" s="6" t="n"/>
-      <c r="G196" s="6" t="n"/>
-      <c r="H196" s="6" t="n"/>
-      <c r="I196" s="6" t="n"/>
-      <c r="J196" s="6" t="n"/>
-      <c r="K196" s="6" t="n"/>
-      <c r="L196" s="6" t="n"/>
-      <c r="M196" s="6" t="n"/>
-      <c r="N196" s="6" t="n"/>
-      <c r="O196" s="6" t="n"/>
-      <c r="P196" s="6" t="n"/>
-      <c r="Q196" s="6" t="n"/>
-      <c r="R196" s="6" t="n"/>
-      <c r="S196" s="6" t="n"/>
-      <c r="T196" s="6" t="n"/>
-      <c r="U196" s="6" t="n"/>
-      <c r="V196" s="6" t="n"/>
-      <c r="W196" s="6" t="n"/>
-      <c r="X196" s="6" t="n"/>
-      <c r="Y196" s="6" t="n"/>
-      <c r="Z196" s="6" t="n"/>
-    </row>
-    <row r="197" ht="15.75" customHeight="1" s="5">
-      <c r="A197" s="6" t="n"/>
-      <c r="B197" s="6" t="n"/>
-      <c r="C197" s="6" t="n"/>
-      <c r="D197" s="6" t="n"/>
-      <c r="E197" s="6" t="n"/>
-      <c r="F197" s="6" t="n"/>
-      <c r="G197" s="6" t="n"/>
-      <c r="H197" s="6" t="n"/>
-      <c r="I197" s="6" t="n"/>
-      <c r="J197" s="6" t="n"/>
-      <c r="K197" s="6" t="n"/>
-      <c r="L197" s="6" t="n"/>
-      <c r="M197" s="6" t="n"/>
-      <c r="N197" s="6" t="n"/>
-      <c r="O197" s="6" t="n"/>
-      <c r="P197" s="6" t="n"/>
-      <c r="Q197" s="6" t="n"/>
-      <c r="R197" s="6" t="n"/>
-      <c r="S197" s="6" t="n"/>
-      <c r="T197" s="6" t="n"/>
-      <c r="U197" s="6" t="n"/>
-      <c r="V197" s="6" t="n"/>
-      <c r="W197" s="6" t="n"/>
-      <c r="X197" s="6" t="n"/>
-      <c r="Y197" s="6" t="n"/>
-      <c r="Z197" s="6" t="n"/>
-    </row>
-    <row r="198" ht="15.75" customHeight="1" s="5">
-      <c r="A198" s="6" t="n"/>
-      <c r="B198" s="6" t="n"/>
-      <c r="C198" s="6" t="n"/>
-      <c r="D198" s="6" t="n"/>
-      <c r="E198" s="6" t="n"/>
-      <c r="F198" s="6" t="n"/>
-      <c r="G198" s="6" t="n"/>
-      <c r="H198" s="6" t="n"/>
-      <c r="I198" s="6" t="n"/>
-      <c r="J198" s="6" t="n"/>
-      <c r="K198" s="6" t="n"/>
-      <c r="L198" s="6" t="n"/>
-      <c r="M198" s="6" t="n"/>
-      <c r="N198" s="6" t="n"/>
-      <c r="O198" s="6" t="n"/>
-      <c r="P198" s="6" t="n"/>
-      <c r="Q198" s="6" t="n"/>
-      <c r="R198" s="6" t="n"/>
-      <c r="S198" s="6" t="n"/>
-      <c r="T198" s="6" t="n"/>
-      <c r="U198" s="6" t="n"/>
-      <c r="V198" s="6" t="n"/>
-      <c r="W198" s="6" t="n"/>
-      <c r="X198" s="6" t="n"/>
-      <c r="Y198" s="6" t="n"/>
-      <c r="Z198" s="6" t="n"/>
-    </row>
-    <row r="199" ht="15.75" customHeight="1" s="5">
-      <c r="A199" s="6" t="n"/>
-      <c r="B199" s="6" t="n"/>
-      <c r="C199" s="6" t="n"/>
-      <c r="D199" s="6" t="n"/>
-      <c r="E199" s="6" t="n"/>
-      <c r="F199" s="6" t="n"/>
-      <c r="G199" s="6" t="n"/>
-      <c r="H199" s="6" t="n"/>
-      <c r="I199" s="6" t="n"/>
-      <c r="J199" s="6" t="n"/>
-      <c r="K199" s="6" t="n"/>
-      <c r="L199" s="6" t="n"/>
-      <c r="M199" s="6" t="n"/>
-      <c r="N199" s="6" t="n"/>
-      <c r="O199" s="6" t="n"/>
-      <c r="P199" s="6" t="n"/>
-      <c r="Q199" s="6" t="n"/>
-      <c r="R199" s="6" t="n"/>
-      <c r="S199" s="6" t="n"/>
-      <c r="T199" s="6" t="n"/>
-      <c r="U199" s="6" t="n"/>
-      <c r="V199" s="6" t="n"/>
-      <c r="W199" s="6" t="n"/>
-      <c r="X199" s="6" t="n"/>
-      <c r="Y199" s="6" t="n"/>
-      <c r="Z199" s="6" t="n"/>
-    </row>
-    <row r="200" ht="15.75" customHeight="1" s="5">
-      <c r="A200" s="6" t="n"/>
-      <c r="B200" s="6" t="n"/>
-      <c r="C200" s="6" t="n"/>
-      <c r="D200" s="6" t="n"/>
-      <c r="E200" s="6" t="n"/>
-      <c r="F200" s="6" t="n"/>
-      <c r="G200" s="6" t="n"/>
-      <c r="H200" s="6" t="n"/>
-      <c r="I200" s="6" t="n"/>
-      <c r="J200" s="6" t="n"/>
-      <c r="K200" s="6" t="n"/>
-      <c r="L200" s="6" t="n"/>
-      <c r="M200" s="6" t="n"/>
-      <c r="N200" s="6" t="n"/>
-      <c r="O200" s="6" t="n"/>
-      <c r="P200" s="6" t="n"/>
-      <c r="Q200" s="6" t="n"/>
-      <c r="R200" s="6" t="n"/>
-      <c r="S200" s="6" t="n"/>
-      <c r="T200" s="6" t="n"/>
-      <c r="U200" s="6" t="n"/>
-      <c r="V200" s="6" t="n"/>
-      <c r="W200" s="6" t="n"/>
-      <c r="X200" s="6" t="n"/>
-      <c r="Y200" s="6" t="n"/>
-      <c r="Z200" s="6" t="n"/>
-    </row>
-    <row r="201" ht="15.75" customHeight="1" s="5">
-      <c r="A201" s="6" t="n"/>
-      <c r="B201" s="6" t="n"/>
-      <c r="C201" s="6" t="n"/>
-      <c r="D201" s="6" t="n"/>
-      <c r="E201" s="6" t="n"/>
-      <c r="F201" s="6" t="n"/>
-      <c r="G201" s="6" t="n"/>
-      <c r="H201" s="6" t="n"/>
-      <c r="I201" s="6" t="n"/>
-      <c r="J201" s="6" t="n"/>
-      <c r="K201" s="6" t="n"/>
-      <c r="L201" s="6" t="n"/>
-      <c r="M201" s="6" t="n"/>
-      <c r="N201" s="6" t="n"/>
-      <c r="O201" s="6" t="n"/>
-      <c r="P201" s="6" t="n"/>
-      <c r="Q201" s="6" t="n"/>
-      <c r="R201" s="6" t="n"/>
-      <c r="S201" s="6" t="n"/>
-      <c r="T201" s="6" t="n"/>
-      <c r="U201" s="6" t="n"/>
-      <c r="V201" s="6" t="n"/>
-      <c r="W201" s="6" t="n"/>
-      <c r="X201" s="6" t="n"/>
-      <c r="Y201" s="6" t="n"/>
-      <c r="Z201" s="6" t="n"/>
-    </row>
-    <row r="202" ht="15.75" customHeight="1" s="5">
-      <c r="A202" s="6" t="n"/>
-      <c r="B202" s="6" t="n"/>
-      <c r="C202" s="6" t="n"/>
-      <c r="D202" s="6" t="n"/>
-      <c r="E202" s="6" t="n"/>
-      <c r="F202" s="6" t="n"/>
-      <c r="G202" s="6" t="n"/>
-      <c r="H202" s="6" t="n"/>
-      <c r="I202" s="6" t="n"/>
-      <c r="J202" s="6" t="n"/>
-      <c r="K202" s="6" t="n"/>
-      <c r="L202" s="6" t="n"/>
-      <c r="M202" s="6" t="n"/>
-      <c r="N202" s="6" t="n"/>
-      <c r="O202" s="6" t="n"/>
-      <c r="P202" s="6" t="n"/>
-      <c r="Q202" s="6" t="n"/>
-      <c r="R202" s="6" t="n"/>
-      <c r="S202" s="6" t="n"/>
-      <c r="T202" s="6" t="n"/>
-      <c r="U202" s="6" t="n"/>
-      <c r="V202" s="6" t="n"/>
-      <c r="W202" s="6" t="n"/>
-      <c r="X202" s="6" t="n"/>
-      <c r="Y202" s="6" t="n"/>
-      <c r="Z202" s="6" t="n"/>
-    </row>
-    <row r="203" ht="15.75" customHeight="1" s="5">
-      <c r="A203" s="6" t="n"/>
-      <c r="B203" s="6" t="n"/>
-      <c r="C203" s="6" t="n"/>
-      <c r="D203" s="6" t="n"/>
-      <c r="E203" s="6" t="n"/>
-      <c r="F203" s="6" t="n"/>
-      <c r="G203" s="6" t="n"/>
-      <c r="H203" s="6" t="n"/>
-      <c r="I203" s="6" t="n"/>
-      <c r="J203" s="6" t="n"/>
-      <c r="K203" s="6" t="n"/>
-      <c r="L203" s="6" t="n"/>
-      <c r="M203" s="6" t="n"/>
-      <c r="N203" s="6" t="n"/>
-      <c r="O203" s="6" t="n"/>
-      <c r="P203" s="6" t="n"/>
-      <c r="Q203" s="6" t="n"/>
-      <c r="R203" s="6" t="n"/>
-      <c r="S203" s="6" t="n"/>
-      <c r="T203" s="6" t="n"/>
-      <c r="U203" s="6" t="n"/>
-      <c r="V203" s="6" t="n"/>
-      <c r="W203" s="6" t="n"/>
-      <c r="X203" s="6" t="n"/>
-      <c r="Y203" s="6" t="n"/>
-      <c r="Z203" s="6" t="n"/>
-    </row>
-    <row r="204" ht="15.75" customHeight="1" s="5">
-      <c r="A204" s="6" t="n"/>
-      <c r="B204" s="6" t="n"/>
-      <c r="C204" s="6" t="n"/>
-      <c r="D204" s="6" t="n"/>
-      <c r="E204" s="6" t="n"/>
-      <c r="F204" s="6" t="n"/>
-      <c r="G204" s="6" t="n"/>
-      <c r="H204" s="6" t="n"/>
-      <c r="I204" s="6" t="n"/>
-      <c r="J204" s="6" t="n"/>
-      <c r="K204" s="6" t="n"/>
-      <c r="L204" s="6" t="n"/>
-      <c r="M204" s="6" t="n"/>
-      <c r="N204" s="6" t="n"/>
-      <c r="O204" s="6" t="n"/>
-      <c r="P204" s="6" t="n"/>
-      <c r="Q204" s="6" t="n"/>
-      <c r="R204" s="6" t="n"/>
-      <c r="S204" s="6" t="n"/>
-      <c r="T204" s="6" t="n"/>
-      <c r="U204" s="6" t="n"/>
-      <c r="V204" s="6" t="n"/>
-      <c r="W204" s="6" t="n"/>
-      <c r="X204" s="6" t="n"/>
-      <c r="Y204" s="6" t="n"/>
-      <c r="Z204" s="6" t="n"/>
-    </row>
-    <row r="205" ht="15.75" customHeight="1" s="5">
-      <c r="A205" s="6" t="n"/>
-      <c r="B205" s="6" t="n"/>
-      <c r="C205" s="6" t="n"/>
-      <c r="D205" s="6" t="n"/>
-      <c r="E205" s="6" t="n"/>
-      <c r="F205" s="6" t="n"/>
-      <c r="G205" s="6" t="n"/>
-      <c r="H205" s="6" t="n"/>
-      <c r="I205" s="6" t="n"/>
-      <c r="J205" s="6" t="n"/>
-      <c r="K205" s="6" t="n"/>
-      <c r="L205" s="6" t="n"/>
-      <c r="M205" s="6" t="n"/>
-      <c r="N205" s="6" t="n"/>
-      <c r="O205" s="6" t="n"/>
-      <c r="P205" s="6" t="n"/>
-      <c r="Q205" s="6" t="n"/>
-      <c r="R205" s="6" t="n"/>
-      <c r="S205" s="6" t="n"/>
-      <c r="T205" s="6" t="n"/>
-      <c r="U205" s="6" t="n"/>
-      <c r="V205" s="6" t="n"/>
-      <c r="W205" s="6" t="n"/>
-      <c r="X205" s="6" t="n"/>
-      <c r="Y205" s="6" t="n"/>
-      <c r="Z205" s="6" t="n"/>
-    </row>
-    <row r="206" ht="15.75" customHeight="1" s="5">
-      <c r="A206" s="6" t="n"/>
-      <c r="B206" s="6" t="n"/>
-      <c r="C206" s="6" t="n"/>
-      <c r="D206" s="6" t="n"/>
-      <c r="E206" s="6" t="n"/>
-      <c r="F206" s="6" t="n"/>
-      <c r="G206" s="6" t="n"/>
-      <c r="H206" s="6" t="n"/>
-      <c r="I206" s="6" t="n"/>
-      <c r="J206" s="6" t="n"/>
-      <c r="K206" s="6" t="n"/>
-      <c r="L206" s="6" t="n"/>
-      <c r="M206" s="6" t="n"/>
-      <c r="N206" s="6" t="n"/>
-      <c r="O206" s="6" t="n"/>
-      <c r="P206" s="6" t="n"/>
-      <c r="Q206" s="6" t="n"/>
-      <c r="R206" s="6" t="n"/>
-      <c r="S206" s="6" t="n"/>
-      <c r="T206" s="6" t="n"/>
-      <c r="U206" s="6" t="n"/>
-      <c r="V206" s="6" t="n"/>
-      <c r="W206" s="6" t="n"/>
-      <c r="X206" s="6" t="n"/>
-      <c r="Y206" s="6" t="n"/>
-      <c r="Z206" s="6" t="n"/>
-    </row>
-    <row r="207" ht="15.75" customHeight="1" s="5">
-      <c r="A207" s="6" t="n"/>
-      <c r="B207" s="6" t="n"/>
-      <c r="C207" s="6" t="n"/>
-      <c r="D207" s="6" t="n"/>
-      <c r="E207" s="6" t="n"/>
-      <c r="F207" s="6" t="n"/>
-      <c r="G207" s="6" t="n"/>
-      <c r="H207" s="6" t="n"/>
-      <c r="I207" s="6" t="n"/>
-      <c r="J207" s="6" t="n"/>
-      <c r="K207" s="6" t="n"/>
-      <c r="L207" s="6" t="n"/>
-      <c r="M207" s="6" t="n"/>
-      <c r="N207" s="6" t="n"/>
-      <c r="O207" s="6" t="n"/>
-      <c r="P207" s="6" t="n"/>
-      <c r="Q207" s="6" t="n"/>
-      <c r="R207" s="6" t="n"/>
-      <c r="S207" s="6" t="n"/>
-      <c r="T207" s="6" t="n"/>
-      <c r="U207" s="6" t="n"/>
-      <c r="V207" s="6" t="n"/>
-      <c r="W207" s="6" t="n"/>
-      <c r="X207" s="6" t="n"/>
-      <c r="Y207" s="6" t="n"/>
-      <c r="Z207" s="6" t="n"/>
-    </row>
-    <row r="208" ht="15.75" customHeight="1" s="5">
-      <c r="A208" s="6" t="n"/>
-      <c r="B208" s="6" t="n"/>
-      <c r="C208" s="6" t="n"/>
-      <c r="D208" s="6" t="n"/>
-      <c r="E208" s="6" t="n"/>
-      <c r="F208" s="6" t="n"/>
-      <c r="G208" s="6" t="n"/>
-      <c r="H208" s="6" t="n"/>
-      <c r="I208" s="6" t="n"/>
-      <c r="J208" s="6" t="n"/>
-      <c r="K208" s="6" t="n"/>
-      <c r="L208" s="6" t="n"/>
-      <c r="M208" s="6" t="n"/>
-      <c r="N208" s="6" t="n"/>
-      <c r="O208" s="6" t="n"/>
-      <c r="P208" s="6" t="n"/>
-      <c r="Q208" s="6" t="n"/>
-      <c r="R208" s="6" t="n"/>
-      <c r="S208" s="6" t="n"/>
-      <c r="T208" s="6" t="n"/>
-      <c r="U208" s="6" t="n"/>
-      <c r="V208" s="6" t="n"/>
-      <c r="W208" s="6" t="n"/>
-      <c r="X208" s="6" t="n"/>
-      <c r="Y208" s="6" t="n"/>
-      <c r="Z208" s="6" t="n"/>
-    </row>
-    <row r="209" ht="15.75" customHeight="1" s="5">
-      <c r="A209" s="6" t="n"/>
-      <c r="B209" s="6" t="n"/>
-      <c r="C209" s="6" t="n"/>
-      <c r="D209" s="6" t="n"/>
-      <c r="E209" s="6" t="n"/>
-      <c r="F209" s="6" t="n"/>
-      <c r="G209" s="6" t="n"/>
-      <c r="H209" s="6" t="n"/>
-      <c r="I209" s="6" t="n"/>
-      <c r="J209" s="6" t="n"/>
-      <c r="K209" s="6" t="n"/>
-      <c r="L209" s="6" t="n"/>
-      <c r="M209" s="6" t="n"/>
-      <c r="N209" s="6" t="n"/>
-      <c r="O209" s="6" t="n"/>
-      <c r="P209" s="6" t="n"/>
-      <c r="Q209" s="6" t="n"/>
-      <c r="R209" s="6" t="n"/>
-      <c r="S209" s="6" t="n"/>
-      <c r="T209" s="6" t="n"/>
-      <c r="U209" s="6" t="n"/>
-      <c r="V209" s="6" t="n"/>
-      <c r="W209" s="6" t="n"/>
-      <c r="X209" s="6" t="n"/>
-      <c r="Y209" s="6" t="n"/>
-      <c r="Z209" s="6" t="n"/>
-    </row>
-    <row r="210" ht="15.75" customHeight="1" s="5">
-      <c r="A210" s="6" t="n"/>
-      <c r="B210" s="6" t="n"/>
-      <c r="C210" s="6" t="n"/>
-      <c r="D210" s="6" t="n"/>
-      <c r="E210" s="6" t="n"/>
-      <c r="F210" s="6" t="n"/>
-      <c r="G210" s="6" t="n"/>
-      <c r="H210" s="6" t="n"/>
-      <c r="I210" s="6" t="n"/>
-      <c r="J210" s="6" t="n"/>
-      <c r="K210" s="6" t="n"/>
-      <c r="L210" s="6" t="n"/>
-      <c r="M210" s="6" t="n"/>
-      <c r="N210" s="6" t="n"/>
-      <c r="O210" s="6" t="n"/>
-      <c r="P210" s="6" t="n"/>
-      <c r="Q210" s="6" t="n"/>
-      <c r="R210" s="6" t="n"/>
-      <c r="S210" s="6" t="n"/>
-      <c r="T210" s="6" t="n"/>
-      <c r="U210" s="6" t="n"/>
-      <c r="V210" s="6" t="n"/>
-      <c r="W210" s="6" t="n"/>
-      <c r="X210" s="6" t="n"/>
-      <c r="Y210" s="6" t="n"/>
-      <c r="Z210" s="6" t="n"/>
-    </row>
-    <row r="211" ht="15.75" customHeight="1" s="5">
-      <c r="A211" s="6" t="n"/>
-      <c r="B211" s="6" t="n"/>
-      <c r="C211" s="6" t="n"/>
-      <c r="D211" s="6" t="n"/>
-      <c r="E211" s="6" t="n"/>
-      <c r="F211" s="6" t="n"/>
-      <c r="G211" s="6" t="n"/>
-      <c r="H211" s="6" t="n"/>
-      <c r="I211" s="6" t="n"/>
-      <c r="J211" s="6" t="n"/>
-      <c r="K211" s="6" t="n"/>
-      <c r="L211" s="6" t="n"/>
-      <c r="M211" s="6" t="n"/>
-      <c r="N211" s="6" t="n"/>
-      <c r="O211" s="6" t="n"/>
-      <c r="P211" s="6" t="n"/>
-      <c r="Q211" s="6" t="n"/>
-      <c r="R211" s="6" t="n"/>
-      <c r="S211" s="6" t="n"/>
-      <c r="T211" s="6" t="n"/>
-      <c r="U211" s="6" t="n"/>
-      <c r="V211" s="6" t="n"/>
-      <c r="W211" s="6" t="n"/>
-      <c r="X211" s="6" t="n"/>
-      <c r="Y211" s="6" t="n"/>
-      <c r="Z211" s="6" t="n"/>
-    </row>
-    <row r="212" ht="15.75" customHeight="1" s="5">
-      <c r="A212" s="6" t="n"/>
-      <c r="B212" s="6" t="n"/>
-      <c r="C212" s="6" t="n"/>
-      <c r="D212" s="6" t="n"/>
-      <c r="E212" s="6" t="n"/>
-      <c r="F212" s="6" t="n"/>
-      <c r="G212" s="6" t="n"/>
-      <c r="H212" s="6" t="n"/>
-      <c r="I212" s="6" t="n"/>
-      <c r="J212" s="6" t="n"/>
-      <c r="K212" s="6" t="n"/>
-      <c r="L212" s="6" t="n"/>
-      <c r="M212" s="6" t="n"/>
-      <c r="N212" s="6" t="n"/>
-      <c r="O212" s="6" t="n"/>
-      <c r="P212" s="6" t="n"/>
-      <c r="Q212" s="6" t="n"/>
-      <c r="R212" s="6" t="n"/>
-      <c r="S212" s="6" t="n"/>
-      <c r="T212" s="6" t="n"/>
-      <c r="U212" s="6" t="n"/>
-      <c r="V212" s="6" t="n"/>
-      <c r="W212" s="6" t="n"/>
-      <c r="X212" s="6" t="n"/>
-      <c r="Y212" s="6" t="n"/>
-      <c r="Z212" s="6" t="n"/>
-    </row>
-    <row r="213" ht="15.75" customHeight="1" s="5">
-      <c r="A213" s="6" t="n"/>
-      <c r="B213" s="6" t="n"/>
-      <c r="C213" s="6" t="n"/>
-      <c r="D213" s="6" t="n"/>
-      <c r="E213" s="6" t="n"/>
-      <c r="F213" s="6" t="n"/>
-      <c r="G213" s="6" t="n"/>
-      <c r="H213" s="6" t="n"/>
-      <c r="I213" s="6" t="n"/>
-      <c r="J213" s="6" t="n"/>
-      <c r="K213" s="6" t="n"/>
-      <c r="L213" s="6" t="n"/>
-      <c r="M213" s="6" t="n"/>
-      <c r="N213" s="6" t="n"/>
-      <c r="O213" s="6" t="n"/>
-      <c r="P213" s="6" t="n"/>
-      <c r="Q213" s="6" t="n"/>
-      <c r="R213" s="6" t="n"/>
-      <c r="S213" s="6" t="n"/>
-      <c r="T213" s="6" t="n"/>
-      <c r="U213" s="6" t="n"/>
-      <c r="V213" s="6" t="n"/>
-      <c r="W213" s="6" t="n"/>
-      <c r="X213" s="6" t="n"/>
-      <c r="Y213" s="6" t="n"/>
-      <c r="Z213" s="6" t="n"/>
-    </row>
-    <row r="214" ht="15.75" customHeight="1" s="5">
-      <c r="A214" s="6" t="n"/>
-      <c r="B214" s="6" t="n"/>
-      <c r="C214" s="6" t="n"/>
-      <c r="D214" s="6" t="n"/>
-      <c r="E214" s="6" t="n"/>
-      <c r="F214" s="6" t="n"/>
-      <c r="G214" s="6" t="n"/>
-      <c r="H214" s="6" t="n"/>
-      <c r="I214" s="6" t="n"/>
-      <c r="J214" s="6" t="n"/>
-      <c r="K214" s="6" t="n"/>
-      <c r="L214" s="6" t="n"/>
-      <c r="M214" s="6" t="n"/>
-      <c r="N214" s="6" t="n"/>
-      <c r="O214" s="6" t="n"/>
-      <c r="P214" s="6" t="n"/>
-      <c r="Q214" s="6" t="n"/>
-      <c r="R214" s="6" t="n"/>
-      <c r="S214" s="6" t="n"/>
-      <c r="T214" s="6" t="n"/>
-      <c r="U214" s="6" t="n"/>
-      <c r="V214" s="6" t="n"/>
-      <c r="W214" s="6" t="n"/>
-      <c r="X214" s="6" t="n"/>
-      <c r="Y214" s="6" t="n"/>
-      <c r="Z214" s="6" t="n"/>
-    </row>
-    <row r="215" ht="15.75" customHeight="1" s="5">
-      <c r="A215" s="6" t="n"/>
-      <c r="B215" s="6" t="n"/>
-      <c r="C215" s="6" t="n"/>
-      <c r="D215" s="6" t="n"/>
-      <c r="E215" s="6" t="n"/>
-      <c r="F215" s="6" t="n"/>
-      <c r="G215" s="6" t="n"/>
-      <c r="H215" s="6" t="n"/>
-      <c r="I215" s="6" t="n"/>
-      <c r="J215" s="6" t="n"/>
-      <c r="K215" s="6" t="n"/>
-      <c r="L215" s="6" t="n"/>
-      <c r="M215" s="6" t="n"/>
-      <c r="N215" s="6" t="n"/>
-      <c r="O215" s="6" t="n"/>
-      <c r="P215" s="6" t="n"/>
-      <c r="Q215" s="6" t="n"/>
-      <c r="R215" s="6" t="n"/>
-      <c r="S215" s="6" t="n"/>
-      <c r="T215" s="6" t="n"/>
-      <c r="U215" s="6" t="n"/>
-      <c r="V215" s="6" t="n"/>
-      <c r="W215" s="6" t="n"/>
-      <c r="X215" s="6" t="n"/>
-      <c r="Y215" s="6" t="n"/>
-      <c r="Z215" s="6" t="n"/>
-    </row>
-    <row r="216" ht="15.75" customHeight="1" s="5">
-      <c r="A216" s="6" t="n"/>
-      <c r="B216" s="6" t="n"/>
-      <c r="C216" s="6" t="n"/>
-      <c r="D216" s="6" t="n"/>
-      <c r="E216" s="6" t="n"/>
-      <c r="F216" s="6" t="n"/>
-      <c r="G216" s="6" t="n"/>
-      <c r="H216" s="6" t="n"/>
-      <c r="I216" s="6" t="n"/>
-      <c r="J216" s="6" t="n"/>
-      <c r="K216" s="6" t="n"/>
-      <c r="L216" s="6" t="n"/>
-      <c r="M216" s="6" t="n"/>
-      <c r="N216" s="6" t="n"/>
-      <c r="O216" s="6" t="n"/>
-      <c r="P216" s="6" t="n"/>
-      <c r="Q216" s="6" t="n"/>
-      <c r="R216" s="6" t="n"/>
-      <c r="S216" s="6" t="n"/>
-      <c r="T216" s="6" t="n"/>
-      <c r="U216" s="6" t="n"/>
-      <c r="V216" s="6" t="n"/>
-      <c r="W216" s="6" t="n"/>
-      <c r="X216" s="6" t="n"/>
-      <c r="Y216" s="6" t="n"/>
-      <c r="Z216" s="6" t="n"/>
-    </row>
-    <row r="217" ht="15.75" customHeight="1" s="5">
-      <c r="A217" s="6" t="n"/>
-      <c r="B217" s="6" t="n"/>
-      <c r="C217" s="6" t="n"/>
-      <c r="D217" s="6" t="n"/>
-      <c r="E217" s="6" t="n"/>
-      <c r="F217" s="6" t="n"/>
-      <c r="G217" s="6" t="n"/>
-      <c r="H217" s="6" t="n"/>
-      <c r="I217" s="6" t="n"/>
-      <c r="J217" s="6" t="n"/>
-      <c r="K217" s="6" t="n"/>
-      <c r="L217" s="6" t="n"/>
-      <c r="M217" s="6" t="n"/>
-      <c r="N217" s="6" t="n"/>
-      <c r="O217" s="6" t="n"/>
-      <c r="P217" s="6" t="n"/>
-      <c r="Q217" s="6" t="n"/>
-      <c r="R217" s="6" t="n"/>
-      <c r="S217" s="6" t="n"/>
-      <c r="T217" s="6" t="n"/>
-      <c r="U217" s="6" t="n"/>
-      <c r="V217" s="6" t="n"/>
-      <c r="W217" s="6" t="n"/>
-      <c r="X217" s="6" t="n"/>
-      <c r="Y217" s="6" t="n"/>
-      <c r="Z217" s="6" t="n"/>
-    </row>
-    <row r="218" ht="15.75" customHeight="1" s="5">
-      <c r="A218" s="6" t="n"/>
-      <c r="B218" s="6" t="n"/>
-      <c r="C218" s="6" t="n"/>
-      <c r="D218" s="6" t="n"/>
-      <c r="E218" s="6" t="n"/>
-      <c r="F218" s="6" t="n"/>
-      <c r="G218" s="6" t="n"/>
-      <c r="H218" s="6" t="n"/>
-      <c r="I218" s="6" t="n"/>
-      <c r="J218" s="6" t="n"/>
-      <c r="K218" s="6" t="n"/>
-      <c r="L218" s="6" t="n"/>
-      <c r="M218" s="6" t="n"/>
-      <c r="N218" s="6" t="n"/>
-      <c r="O218" s="6" t="n"/>
-      <c r="P218" s="6" t="n"/>
-      <c r="Q218" s="6" t="n"/>
-      <c r="R218" s="6" t="n"/>
-      <c r="S218" s="6" t="n"/>
-      <c r="T218" s="6" t="n"/>
-      <c r="U218" s="6" t="n"/>
-      <c r="V218" s="6" t="n"/>
-      <c r="W218" s="6" t="n"/>
-      <c r="X218" s="6" t="n"/>
-      <c r="Y218" s="6" t="n"/>
-      <c r="Z218" s="6" t="n"/>
-    </row>
-    <row r="219" ht="15.75" customHeight="1" s="5">
-      <c r="A219" s="6" t="n"/>
-      <c r="B219" s="6" t="n"/>
-      <c r="C219" s="6" t="n"/>
-      <c r="D219" s="6" t="n"/>
-      <c r="E219" s="6" t="n"/>
-      <c r="F219" s="6" t="n"/>
-      <c r="G219" s="6" t="n"/>
-      <c r="H219" s="6" t="n"/>
-      <c r="I219" s="6" t="n"/>
-      <c r="J219" s="6" t="n"/>
-      <c r="K219" s="6" t="n"/>
-      <c r="L219" s="6" t="n"/>
-      <c r="M219" s="6" t="n"/>
-      <c r="N219" s="6" t="n"/>
-      <c r="O219" s="6" t="n"/>
-      <c r="P219" s="6" t="n"/>
-      <c r="Q219" s="6" t="n"/>
-      <c r="R219" s="6" t="n"/>
-      <c r="S219" s="6" t="n"/>
-      <c r="T219" s="6" t="n"/>
-      <c r="U219" s="6" t="n"/>
-      <c r="V219" s="6" t="n"/>
-      <c r="W219" s="6" t="n"/>
-      <c r="X219" s="6" t="n"/>
-      <c r="Y219" s="6" t="n"/>
-      <c r="Z219" s="6" t="n"/>
-    </row>
-    <row r="220" ht="15.75" customHeight="1" s="5">
-      <c r="A220" s="6" t="n"/>
-      <c r="B220" s="6" t="n"/>
-      <c r="C220" s="6" t="n"/>
-      <c r="D220" s="6" t="n"/>
-      <c r="E220" s="6" t="n"/>
-      <c r="F220" s="6" t="n"/>
-      <c r="G220" s="6" t="n"/>
-      <c r="H220" s="6" t="n"/>
-      <c r="I220" s="6" t="n"/>
-      <c r="J220" s="6" t="n"/>
-      <c r="K220" s="6" t="n"/>
-      <c r="L220" s="6" t="n"/>
-      <c r="M220" s="6" t="n"/>
-      <c r="N220" s="6" t="n"/>
-      <c r="O220" s="6" t="n"/>
-      <c r="P220" s="6" t="n"/>
-      <c r="Q220" s="6" t="n"/>
-      <c r="R220" s="6" t="n"/>
-      <c r="S220" s="6" t="n"/>
-      <c r="T220" s="6" t="n"/>
-      <c r="U220" s="6" t="n"/>
-      <c r="V220" s="6" t="n"/>
-      <c r="W220" s="6" t="n"/>
-      <c r="X220" s="6" t="n"/>
-      <c r="Y220" s="6" t="n"/>
-      <c r="Z220" s="6" t="n"/>
-    </row>
-    <row r="221" ht="15.75" customHeight="1" s="5">
-      <c r="A221" s="6" t="n"/>
-      <c r="B221" s="6" t="n"/>
-      <c r="C221" s="6" t="n"/>
-      <c r="D221" s="6" t="n"/>
-      <c r="E221" s="6" t="n"/>
-      <c r="F221" s="6" t="n"/>
-      <c r="G221" s="6" t="n"/>
-      <c r="H221" s="6" t="n"/>
-      <c r="I221" s="6" t="n"/>
-      <c r="J221" s="6" t="n"/>
-      <c r="K221" s="6" t="n"/>
-      <c r="L221" s="6" t="n"/>
-      <c r="M221" s="6" t="n"/>
-      <c r="N221" s="6" t="n"/>
-      <c r="O221" s="6" t="n"/>
-      <c r="P221" s="6" t="n"/>
-      <c r="Q221" s="6" t="n"/>
-      <c r="R221" s="6" t="n"/>
-      <c r="S221" s="6" t="n"/>
-      <c r="T221" s="6" t="n"/>
-      <c r="U221" s="6" t="n"/>
-      <c r="V221" s="6" t="n"/>
-      <c r="W221" s="6" t="n"/>
-      <c r="X221" s="6" t="n"/>
-      <c r="Y221" s="6" t="n"/>
-      <c r="Z221" s="6" t="n"/>
-    </row>
-    <row r="222" ht="15.75" customHeight="1" s="5">
-      <c r="A222" s="6" t="n"/>
-      <c r="B222" s="6" t="n"/>
-      <c r="C222" s="6" t="n"/>
-      <c r="D222" s="6" t="n"/>
-      <c r="E222" s="6" t="n"/>
-      <c r="F222" s="6" t="n"/>
-      <c r="G222" s="6" t="n"/>
-      <c r="H222" s="6" t="n"/>
-      <c r="I222" s="6" t="n"/>
-      <c r="J222" s="6" t="n"/>
-      <c r="K222" s="6" t="n"/>
-      <c r="L222" s="6" t="n"/>
-      <c r="M222" s="6" t="n"/>
-      <c r="N222" s="6" t="n"/>
-      <c r="O222" s="6" t="n"/>
-      <c r="P222" s="6" t="n"/>
-      <c r="Q222" s="6" t="n"/>
-      <c r="R222" s="6" t="n"/>
-      <c r="S222" s="6" t="n"/>
-      <c r="T222" s="6" t="n"/>
-      <c r="U222" s="6" t="n"/>
-      <c r="V222" s="6" t="n"/>
-      <c r="W222" s="6" t="n"/>
-      <c r="X222" s="6" t="n"/>
-      <c r="Y222" s="6" t="n"/>
-      <c r="Z222" s="6" t="n"/>
-    </row>
-    <row r="223" ht="15.75" customHeight="1" s="5">
-      <c r="A223" s="6" t="n"/>
-      <c r="B223" s="6" t="n"/>
-      <c r="C223" s="6" t="n"/>
-      <c r="D223" s="6" t="n"/>
-      <c r="E223" s="6" t="n"/>
-      <c r="F223" s="6" t="n"/>
-      <c r="G223" s="6" t="n"/>
-      <c r="H223" s="6" t="n"/>
-      <c r="I223" s="6" t="n"/>
-      <c r="J223" s="6" t="n"/>
-      <c r="K223" s="6" t="n"/>
-      <c r="L223" s="6" t="n"/>
-      <c r="M223" s="6" t="n"/>
-      <c r="N223" s="6" t="n"/>
-      <c r="O223" s="6" t="n"/>
-      <c r="P223" s="6" t="n"/>
-      <c r="Q223" s="6" t="n"/>
-      <c r="R223" s="6" t="n"/>
-      <c r="S223" s="6" t="n"/>
-      <c r="T223" s="6" t="n"/>
-      <c r="U223" s="6" t="n"/>
-      <c r="V223" s="6" t="n"/>
-      <c r="W223" s="6" t="n"/>
-      <c r="X223" s="6" t="n"/>
-      <c r="Y223" s="6" t="n"/>
-      <c r="Z223" s="6" t="n"/>
-    </row>
-    <row r="224" ht="15.75" customHeight="1" s="5">
-      <c r="A224" s="6" t="n"/>
-      <c r="B224" s="6" t="n"/>
-      <c r="C224" s="6" t="n"/>
-      <c r="D224" s="6" t="n"/>
-      <c r="E224" s="6" t="n"/>
-      <c r="F224" s="6" t="n"/>
-      <c r="G224" s="6" t="n"/>
-      <c r="H224" s="6" t="n"/>
-      <c r="I224" s="6" t="n"/>
-      <c r="J224" s="6" t="n"/>
-      <c r="K224" s="6" t="n"/>
-      <c r="L224" s="6" t="n"/>
-      <c r="M224" s="6" t="n"/>
-      <c r="N224" s="6" t="n"/>
-      <c r="O224" s="6" t="n"/>
-      <c r="P224" s="6" t="n"/>
-      <c r="Q224" s="6" t="n"/>
-      <c r="R224" s="6" t="n"/>
-      <c r="S224" s="6" t="n"/>
-      <c r="T224" s="6" t="n"/>
-      <c r="U224" s="6" t="n"/>
-      <c r="V224" s="6" t="n"/>
-      <c r="W224" s="6" t="n"/>
-      <c r="X224" s="6" t="n"/>
-      <c r="Y224" s="6" t="n"/>
-      <c r="Z224" s="6" t="n"/>
-    </row>
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>STRESS-26</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="inlineStr">
+        <is>
+          <t>Steering Config Reload Under Traffic — Heap Corruption Race in stAgentSvc</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>Tunneling / Stress</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>Regression test for ENG-1070921 (Mivne Group blocker). stAgentSvc.exe crashes with HEAP_CORRUPTION_ACTIONABLE_BlockNotBusy_DOUBLE_FREE when a steering config reload coincides with high network traffic.
+Root cause is two independent data races: (1) CustomDnsPorts::isCustomDnsPort reads m_customDnsSettings and m_ipRanges on the packet-processing hot path while readCustomDnsSettings rebuilds them during a policy reload with no synchronization (2) CDetectOnprem::OnpremdetectThread called onpremStatusInfoListPtr-&gt;push_back outside m_threadLock, so concurrent on-prem detection threads corrupt the shared vector. Both are triggered by the same real-world pattern: policy update while the client is under active traffic. Test must force both code paths under load and watch usermode crash dumps, not just service uptime.</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>1. Enroll Windows endpoint (non-VDI) with steering enabled; ensure tunnel is UP and Custom DNS Ports plus at least one On-Prem Detection label are configured in the steering policy
+2. Clear old dump files from defined paths
+3. Before start; enable PageHeap for stAgentSvc.exe (gflags /p /enable stAgentSvc.exe /full) to make heap corruption fail-fast
+3. Launch sustained network traffic in parallel: 1000+ concurrent HTTP/HTTPS flows per second, plus 500 DNS queries per second (mix TCP DNS and UDP DNS), for 30 mins
+4. In parallel with the traffic, push a steering policy update from the tenant every 30 seconds so nsdiag -u forces readCustomDnsSettings and on-prem label re-evaluation on the endpoint
+5. In parallel, toggle the endpoint on-prem/off-prem state every 60 seconds (e.g., by flipping the on-prem detection egress IP or on-prem test URL reachability) so CDetectOnprem::OnpremdetectThread fires repeatedly with push_back into onpremStatusInfoListPtr
+6. Monitor throughout: stAgentSvc.exe PID (must not change), stAgentSvc memory (lower than 200 MB), tunnel status, no dump generated during this period
+7. Repeat for n times (by the --iterations option)</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>Zero new *.dmp files.
+stAgentSvc.exe PID unchanged (no silent crash + restart).
+Tunnel stays connected (or reconnects within 60s of any network state change); Custom DNS steering and on-prem detection remain correct after every reload.</t>
+        </is>
+      </c>
+      <c r="G70" s="7" t="inlineStr">
+        <is>
+          <t>Mass endpoint outage: stAgentSvc crashes intermittently on all endpoints where a steering policy reload coincides with traffic, leaving 'Internet Security has an error' in the system tray and completely blocking web access until the user manually restarts the service or reboots. Customer halts NSClient rollout org-wide (Mivne Group scenario, 20+ endpoints, Blocker). Security gap: SWG/NPA policy enforcement lost during every crash window.</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>IMF/ENG: ENG-1070921, ENG-1070166, ENG-951275 | PR: PR-8768 (CustomDnsPorts shared_mutex), PR-8824 (detectOnprem push_back under m_threadLock)</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>system-res-test-gen (date 2026-07-01)</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" s="5"/>
+    <row r="72" ht="15.75" customHeight="1" s="5"/>
+    <row r="73" ht="15.75" customHeight="1" s="5"/>
+    <row r="74" ht="15.75" customHeight="1" s="5"/>
+    <row r="75" ht="15.75" customHeight="1" s="5"/>
+    <row r="76" ht="15.75" customHeight="1" s="5"/>
+    <row r="77" ht="15.75" customHeight="1" s="5"/>
+    <row r="78" ht="15.75" customHeight="1" s="5"/>
+    <row r="79" ht="15.75" customHeight="1" s="5"/>
+    <row r="80" ht="15.75" customHeight="1" s="5"/>
+    <row r="81" ht="15.75" customHeight="1" s="5"/>
+    <row r="82" ht="15.75" customHeight="1" s="5"/>
+    <row r="83" ht="15.75" customHeight="1" s="5"/>
+    <row r="84" ht="15.75" customHeight="1" s="5"/>
+    <row r="85" ht="15.75" customHeight="1" s="5"/>
+    <row r="86" ht="15.75" customHeight="1" s="5"/>
+    <row r="87" ht="15.75" customHeight="1" s="5"/>
+    <row r="88" ht="15.75" customHeight="1" s="5"/>
+    <row r="89" ht="15.75" customHeight="1" s="5"/>
+    <row r="90" ht="15.75" customHeight="1" s="5"/>
+    <row r="91" ht="15.75" customHeight="1" s="5"/>
+    <row r="92" ht="15.75" customHeight="1" s="5"/>
+    <row r="93" ht="15.75" customHeight="1" s="5"/>
+    <row r="94" ht="15.75" customHeight="1" s="5"/>
+    <row r="95" ht="15.75" customHeight="1" s="5"/>
+    <row r="96" ht="15.75" customHeight="1" s="5"/>
+    <row r="97" ht="15.75" customHeight="1" s="5"/>
+    <row r="98" ht="15.75" customHeight="1" s="5"/>
+    <row r="99" ht="15.75" customHeight="1" s="5"/>
+    <row r="100" ht="15.75" customHeight="1" s="5"/>
+    <row r="101" ht="15.75" customHeight="1" s="5"/>
+    <row r="102" ht="15.75" customHeight="1" s="5"/>
+    <row r="103" ht="15.75" customHeight="1" s="5"/>
+    <row r="104" ht="15.75" customHeight="1" s="5"/>
+    <row r="105" ht="15.75" customHeight="1" s="5"/>
+    <row r="106" ht="15.75" customHeight="1" s="5"/>
+    <row r="107" ht="15.75" customHeight="1" s="5"/>
+    <row r="108" ht="15.75" customHeight="1" s="5"/>
+    <row r="109" ht="15.75" customHeight="1" s="5"/>
+    <row r="110" ht="15.75" customHeight="1" s="5"/>
+    <row r="111" ht="15.75" customHeight="1" s="5"/>
+    <row r="112" ht="15.75" customHeight="1" s="5"/>
+    <row r="113" ht="15.75" customHeight="1" s="5"/>
+    <row r="114" ht="15.75" customHeight="1" s="5"/>
+    <row r="115" ht="15.75" customHeight="1" s="5"/>
+    <row r="116" ht="15.75" customHeight="1" s="5"/>
+    <row r="117" ht="15.75" customHeight="1" s="5"/>
+    <row r="118" ht="15.75" customHeight="1" s="5"/>
+    <row r="119" ht="15.75" customHeight="1" s="5"/>
+    <row r="120" ht="15.75" customHeight="1" s="5"/>
+    <row r="121" ht="15.75" customHeight="1" s="5"/>
+    <row r="122" ht="15.75" customHeight="1" s="5"/>
+    <row r="123" ht="15.75" customHeight="1" s="5"/>
+    <row r="124" ht="15.75" customHeight="1" s="5"/>
+    <row r="125" ht="15.75" customHeight="1" s="5"/>
+    <row r="126" ht="15.75" customHeight="1" s="5"/>
+    <row r="127" ht="15.75" customHeight="1" s="5"/>
+    <row r="128" ht="15.75" customHeight="1" s="5"/>
+    <row r="129" ht="15.75" customHeight="1" s="5"/>
+    <row r="130" ht="15.75" customHeight="1" s="5"/>
+    <row r="131" ht="15.75" customHeight="1" s="5"/>
+    <row r="132" ht="15.75" customHeight="1" s="5"/>
+    <row r="133" ht="15.75" customHeight="1" s="5"/>
+    <row r="134" ht="15.75" customHeight="1" s="5"/>
+    <row r="135" ht="15.75" customHeight="1" s="5"/>
+    <row r="136" ht="15.75" customHeight="1" s="5"/>
+    <row r="137" ht="15.75" customHeight="1" s="5"/>
+    <row r="138" ht="15.75" customHeight="1" s="5"/>
+    <row r="139" ht="15.75" customHeight="1" s="5"/>
+    <row r="140" ht="15.75" customHeight="1" s="5"/>
+    <row r="141" ht="15.75" customHeight="1" s="5"/>
+    <row r="142" ht="15.75" customHeight="1" s="5"/>
+    <row r="143" ht="15.75" customHeight="1" s="5"/>
+    <row r="144" ht="15.75" customHeight="1" s="5"/>
+    <row r="145" ht="15.75" customHeight="1" s="5"/>
+    <row r="146" ht="15.75" customHeight="1" s="5"/>
+    <row r="147" ht="15.75" customHeight="1" s="5"/>
+    <row r="148" ht="15.75" customHeight="1" s="5"/>
+    <row r="149" ht="15.75" customHeight="1" s="5"/>
+    <row r="150" ht="15.75" customHeight="1" s="5"/>
+    <row r="151" ht="15.75" customHeight="1" s="5"/>
+    <row r="152" ht="15.75" customHeight="1" s="5"/>
+    <row r="153" ht="15.75" customHeight="1" s="5"/>
+    <row r="154" ht="15.75" customHeight="1" s="5"/>
+    <row r="155" ht="15.75" customHeight="1" s="5"/>
+    <row r="156" ht="15.75" customHeight="1" s="5"/>
+    <row r="157" ht="15.75" customHeight="1" s="5"/>
+    <row r="158" ht="15.75" customHeight="1" s="5"/>
+    <row r="159" ht="15.75" customHeight="1" s="5"/>
+    <row r="160" ht="15.75" customHeight="1" s="5"/>
+    <row r="161" ht="15.75" customHeight="1" s="5"/>
+    <row r="162" ht="15.75" customHeight="1" s="5"/>
+    <row r="163" ht="15.75" customHeight="1" s="5"/>
+    <row r="164" ht="15.75" customHeight="1" s="5"/>
+    <row r="165" ht="15.75" customHeight="1" s="5"/>
+    <row r="166" ht="15.75" customHeight="1" s="5"/>
+    <row r="167" ht="15.75" customHeight="1" s="5"/>
+    <row r="168" ht="15.75" customHeight="1" s="5"/>
+    <row r="169" ht="15.75" customHeight="1" s="5"/>
+    <row r="170" ht="15.75" customHeight="1" s="5"/>
+    <row r="171" ht="15.75" customHeight="1" s="5"/>
+    <row r="172" ht="15.75" customHeight="1" s="5"/>
+    <row r="173" ht="15.75" customHeight="1" s="5"/>
+    <row r="174" ht="15.75" customHeight="1" s="5"/>
+    <row r="175" ht="15.75" customHeight="1" s="5"/>
+    <row r="176" ht="15.75" customHeight="1" s="5"/>
+    <row r="177" ht="15.75" customHeight="1" s="5"/>
+    <row r="178" ht="15.75" customHeight="1" s="5"/>
+    <row r="179" ht="15.75" customHeight="1" s="5"/>
+    <row r="180" ht="15.75" customHeight="1" s="5"/>
+    <row r="181" ht="15.75" customHeight="1" s="5"/>
+    <row r="182" ht="15.75" customHeight="1" s="5"/>
+    <row r="183" ht="15.75" customHeight="1" s="5"/>
+    <row r="184" ht="15.75" customHeight="1" s="5"/>
+    <row r="185" ht="15.75" customHeight="1" s="5"/>
+    <row r="186" ht="15.75" customHeight="1" s="5"/>
+    <row r="187" ht="15.75" customHeight="1" s="5"/>
+    <row r="188" ht="15.75" customHeight="1" s="5"/>
+    <row r="189" ht="15.75" customHeight="1" s="5"/>
+    <row r="190" ht="15.75" customHeight="1" s="5"/>
+    <row r="191" ht="15.75" customHeight="1" s="5"/>
+    <row r="192" ht="15.75" customHeight="1" s="5"/>
+    <row r="193" ht="15.75" customHeight="1" s="5"/>
+    <row r="194" ht="15.75" customHeight="1" s="5"/>
+    <row r="195" ht="15.75" customHeight="1" s="5"/>
+    <row r="196" ht="15.75" customHeight="1" s="5"/>
+    <row r="197" ht="15.75" customHeight="1" s="5"/>
+    <row r="198" ht="15.75" customHeight="1" s="5"/>
+    <row r="199" ht="15.75" customHeight="1" s="5"/>
+    <row r="200" ht="15.75" customHeight="1" s="5"/>
+    <row r="201" ht="15.75" customHeight="1" s="5"/>
+    <row r="202" ht="15.75" customHeight="1" s="5"/>
+    <row r="203" ht="15.75" customHeight="1" s="5"/>
+    <row r="204" ht="15.75" customHeight="1" s="5"/>
+    <row r="205" ht="15.75" customHeight="1" s="5"/>
+    <row r="206" ht="15.75" customHeight="1" s="5"/>
+    <row r="207" ht="15.75" customHeight="1" s="5"/>
+    <row r="208" ht="15.75" customHeight="1" s="5"/>
+    <row r="209" ht="15.75" customHeight="1" s="5"/>
+    <row r="210" ht="15.75" customHeight="1" s="5"/>
+    <row r="211" ht="15.75" customHeight="1" s="5"/>
+    <row r="212" ht="15.75" customHeight="1" s="5"/>
+    <row r="213" ht="15.75" customHeight="1" s="5"/>
+    <row r="214" ht="15.75" customHeight="1" s="5"/>
+    <row r="215" ht="15.75" customHeight="1" s="5"/>
+    <row r="216" ht="15.75" customHeight="1" s="5"/>
+    <row r="217" ht="15.75" customHeight="1" s="5"/>
+    <row r="218" ht="15.75" customHeight="1" s="5"/>
+    <row r="219" ht="15.75" customHeight="1" s="5"/>
+    <row r="220" ht="15.75" customHeight="1" s="5"/>
+    <row r="221" ht="15.75" customHeight="1" s="5"/>
+    <row r="222" ht="15.75" customHeight="1" s="5"/>
+    <row r="223" ht="15.75" customHeight="1" s="5"/>
+    <row r="224" ht="15.75" customHeight="1" s="5"/>
     <row r="225" ht="15.75" customHeight="1" s="5"/>
     <row r="226" ht="15.75" customHeight="1" s="5"/>
     <row r="227" ht="15.75" customHeight="1" s="5"/>

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -2089,8 +2089,7 @@
 3. Restore connectivity
 4. Verify DNS traffic steered after recovery
 5. Change steering mode during FailClose active
-6. Verify correct enforcement after mode change completes
-7. Repeat 1~6 for 20 times</t>
+6. Verify correct enforcement after mode change completes</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
@@ -2158,8 +2157,7 @@
 2. Monitor client status API call rate from endpoint
 3. Verify client implements backoff/throttling
 4. Verify client config downloads still succeed during status storm
-5. Monitor backend response times
-6. Repeat 1~5 for 20 times</t>
+5. Monitor backend response times</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
@@ -2227,8 +2225,7 @@
 2. Put device to Modern Standby
 3. Wake device and verify client status updates correctly
 4. Trigger auto-upgrade while device in AOAC mode
-5. Verify enrollment survives upgrade + wake cycle
-6. Repeat 1~5 for 20 times</t>
+5. Verify enrollment survives upgrade + wake cycle</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
@@ -2296,8 +2293,7 @@
 2. Block gateway IP at firewall
 3. Reboot device
 4. After boot, verify all non-exempt traffic is blocked
-5. Unblock gateway and verify tunnel re-establishes
-6. Repeat 1~5 for 20 times</t>
+5. Unblock gateway and verify tunnel re-establishes</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
@@ -2366,8 +2362,7 @@
 3. Verify uninstall blocked
 4. Send IOCTL commands to driver attempting disable
 5. Verify driver rejects unauthorized IOCTL
-6. Verify service remains running and protected
-7. Repeat 1~6 for 20 times</t>
+6. Verify service remains running and protected</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
@@ -2435,8 +2430,7 @@
 2. Generate large DNS TCP responses (&gt;512 bytes, fragmented)
 3. Verify packets not dropped or corrupted
 4. Monitor for BSOD/crash
-5. Verify DNS resolution latency stays under threshold
-6. Repeat 1~5 for 20 times</t>
+5. Verify DNS resolution latency stays under threshold</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -2505,8 +2499,7 @@
 3. Verify packets not dropped or corrupted
 4. Run DNS load test on Citrix/VDI with 50+ concurrent sessions
 5. Monitor for BSOD/crash
-6. Verify DNS resolution latency stays under threshold
-7. Repeat 1~6 for 20 times</t>
+6. Verify DNS resolution latency stays under threshold</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
@@ -2574,8 +2567,7 @@
 2. Start auto-upgrade.
 3. Kill msiexec process mid-installation (simulating crash).
 4. Reboot.
-5. Verify UpgradeInProgress registry is eventually cleared and watchdog resumes monitoring.
-6. Repeat 1~5 for 20 times</t>
+5. Verify UpgradeInProgress registry is eventually cleared and watchdog resumes monitoring.</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -2643,8 +2635,7 @@
 2. Verify client performs GSLB re-evaluation and selects better DP
 3. Block DTLS port
 4. Verify automatic failover to TLS within timeout
-5. Restore DTLS and verify client returns to DTLS
-6. Repeat 1~5 for 20 times</t>
+5. Restore DTLS and verify client returns to DTLS</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -2712,8 +2703,7 @@
 2. Restart service and verify recovery from backup
 3. Delete user cert while config encryption enabled
 4. Verify client re-downloads config without crash
-5. Verify client does not remain disabled
-6. Repeat 1~5 for 20 times</t>
+5. Verify client does not remain disabled</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -2782,8 +2772,7 @@
 3. Verify upgrade triggers at correct time
 4. Interrupt upgrade mid-MSI (kill msiexec process)
 5. Reboot and verify Legacy Monitor retries and completes upgrade
-6. Verify client not silently removed
-7. Repeat 1~6 for 5 times</t>
+6. Verify client not silently removed</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -2852,8 +2841,7 @@
 3. Login User B simultaneously on same machine
 4. Verify User A connections not disrupted
 5. Verify User B gets correct steering config
-6. Logout User A and verify User B tunnel persists
-7. Repeat 1~6 for 20 times</t>
+6. Logout User A and verify User B tunnel persists</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -2922,8 +2910,7 @@
 3. Verify enrollment completes without timeout
 4. Test enrollment during Windows Autopilot OOBE
 5. Verify no blank enrollment window from concurrent webview2
-6. Verify enrollment on subsequent Citrix sessions
-7. Repeat 1~6 for 20 times</t>
+6. Verify enrollment on subsequent Citrix sessions</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -2991,8 +2978,7 @@
 2. Verify only that app's traffic bypasses tunnel
 3. Generate traffic from other apps
 4. Verify other apps still steered through tunnel
-5. Change steering config and verify cert-pinned exception still scoped correctly
-6. Repeat 1~5 for 20 times</t>
+5. Change steering config and verify cert-pinned exception still scoped correctly</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -3059,8 +3045,7 @@
           <t>1. Configure client with FailClose + All Traffic steering
 2. Repeatedly stop/start service via net stop stAgentSvc
 3. Toggle sleep/wake and network adapters concurrently
-4. Monitor for crash dumps in C:\dump
-5. Repeat 1~4 for 20 times</t>
+4. Monitor for crash dumps in C:\dump</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -3129,8 +3114,7 @@
 3. Verify steering disabled per on-prem policy
 4. Switch to off-prem network (different egress IP)
 5. Verify client detects transition and reconnects tunnel
-6. Verify steering re-enabled within 30s
-7. Repeat 1~6 for 20 times</t>
+6. Verify steering re-enabled within 30s</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -3197,8 +3181,7 @@
           <t>1. Enable self-protection and watchdog.
 2. Trigger auto-upgrade from R135.
 3. Force reboot during CA_RollbackInstallDriver phase.
-4. Boot and verify client presence.
-5. Repeat 1~4 for 5 times</t>
+4. Boot and verify client presence.</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
@@ -3266,8 +3249,7 @@
 2. Establish tunnel.
 3. Enter S0 standby (close lid).
 4. Wake repeatedly under varying load.
-5. Monitor for crash dumps and service recovery.
-6. Repeat 1~5 for 20 times</t>
+5. Monitor for crash dumps and service recovery.</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
@@ -3334,8 +3316,7 @@
           <t>1. Enable watchdog FF via tenant config push.
 2. Verify stWatchdog service is running.
 3. Disable watchdog FF via tenant config push.
-4. Verify stWatchdog service is stopped and removed from SCM.
-5. Repeat 1~4 for 20 times</t>
+4. Verify stWatchdog service is stopped and removed from SCM.</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -3402,8 +3383,7 @@
           <t>1. Enable watchdog FF.
 2. Suspend stAgentSvc process immediately after SCM marks it START_PENDING.
 3. Wait &gt;5 minutes.
-4. Observe whether watchdog takes corrective action or remains dormant.
-5. Repeat 1~4 for 20 times</t>
+4. Observe whether watchdog takes corrective action or remains dormant.</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -3471,8 +3451,7 @@
 2. Generate heavy SMB traffic (file shares, DFS)
 3. Monitor domain controller CPU utilization
 4. Verify NSClient does not amplify SMB connections
-5. Monitor client crash under massive connection load
-6. Repeat 1~5 for 20 times</t>
+5. Monitor client crash under massive connection load</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
@@ -3539,8 +3518,7 @@
           <t>1. Deploy NSClient on multi-session Citrix/AVD with FailClose enabled
 2. Login first user and verify tunnel
 3. Login second user whose AppData is not yet initialized
-4. Verify first user session is not disrupted
-5. Repeat 1~4 for 20 times</t>
+4. Verify first user session is not disrupted</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -3607,8 +3585,7 @@
           <t>1. Install NSClient in IDP+peruserconfig mode on multi-session AVD
 2. First user logs in and completes IDP enrollment
 3. Second user logs in
-4. Verify second user gets IDP authentication prompt (not silent UPN enrollment)
-5. Repeat 1~4 for 20 times</t>
+4. Verify second user gets IDP authentication prompt (not silent UPN enrollment)</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -3676,8 +3653,7 @@
 2. Trigger auto-upgrade.
 3. Force reboot/power-off during MSI installation phase.
 4. Boot and trigger another auto-upgrade.
-5. Verify binary version matches registered version.
-6. Repeat 1~5 for 5 times</t>
+5. Verify binary version matches registered version.</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -3745,8 +3721,7 @@
 2. Enable secure enrollment + fail-close.
 3. Have 5+ users log in simultaneously.
 4. Introduce tunnel delay (17+ seconds).
-5. Verify traffic steering.
-6. Repeat 1~5 for 20 times</t>
+5. Verify traffic steering.</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -3814,8 +3789,7 @@
 2. Do admin disable then enable.
 3. Change network.
 4. Attempt to access blocked sites via IPv6 (configure hosts file with IPv6 addresses).
-5. Verify traffic blocked.
-6. Repeat 1~5 for 20 times</t>
+5. Verify traffic blocked.</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
@@ -3882,8 +3856,7 @@
           <t>1. Enable fail-close and reset_with_overlapped_io FF.
 2. Run client under continuous traffic.
 3. Perform network switches repeatedly for hours.
-4. Monitor for crash dumps.
-5. Repeat 1~4 for 20 times</t>
+4. Monitor for crash dumps.</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -3949,8 +3922,7 @@
         <is>
           <t>1. Install 32-bit NSClient with secure enrollment (tokens in WOW6432Node).
 2. Trigger auto-upgrade to 64-bit MSI.
-3. After upgrade verify enrollment tokens exist under HKLM\Software\Netskope\SecureToken.
-4. Repeat 1~3 for 5 times</t>
+3. After upgrade verify enrollment tokens exist under HKLM\Software\Netskope\SecureToken.</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
@@ -4018,8 +3990,7 @@
 2. Verify IPv6 traffic correctly steered through tunnel
 3. Add IPv6 local-link exception
 4. Verify local-link IPv6 traffic bypassed
-5. Run throughput test over IPv6 and compare with IPv4 baseline
-6. Repeat 1~5 for 20 times</t>
+5. Run throughput test over IPv6 and compare with IPv4 baseline</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -4086,8 +4057,7 @@
           <t>1. Enable AOAC, self-protection, fail-close on Windows device.
 2. Put device into hibernate/S0 sleep.
 3. Trigger auto-upgrade immediately after wake.
-4. Monitor SCM callback timing and MSI completion.
-5. Repeat 1~4 for 20 times</t>
+4. Monitor SCM callback timing and MSI completion.</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
@@ -4154,8 +4124,7 @@
           <t>1. Enable AOAC + fail-close on Windows.
 2. Run under system stress (many apps, high memory).
 3. Cycle sleep/wake repeatedly (20+ times).
-4. Monitor for error 1453 and tunnel disconnection.
-5. Repeat 1~4 for 20 times</t>
+4. Monitor for error 1453 and tunnel disconnection.</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
@@ -4222,8 +4191,7 @@
           <t>1. Configure cloud steering mode with domain exceptions.
 2. Switch steering config to web mode (different exception list).
 3. Verify exception list downloads successfully before tunnel disconnects.
-4. Confirm bypassed domains remain accessible.
-5. Repeat 1~4 for 20 times</t>
+4. Confirm bypassed domains remain accessible.</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
@@ -4290,8 +4258,7 @@
           <t>1. Enable secure config encryption on tenant.
 2. Enable watchdog FF.
 3. Reboot machine.
-4. Verify stWatchdog service starts within 90 seconds of boot.
-5. Repeat 1~4 for 20 times</t>
+4. Verify stWatchdog service starts within 90 seconds of boot.</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
@@ -4489,8 +4456,7 @@
         <is>
           <t>1. Configure scheduled upgrade with daily frequency and specific time
 2. Install client and wait for scheduled upgrade window to pass
-3. Verify client remains functional and does not enter hung/disabled state
-4. Repeat 1~3 for 5 times</t>
+3. Verify client remains functional and does not enter hung/disabled state</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr">
@@ -4557,8 +4523,7 @@
           <t>1. Configure FailClose with dynamic steering disabled
 2. Reboot Windows device
 3. At login screen, attempt Self-Service Password Reset (SSPR)
-4. Verify SSPR traffic (passwordreset.microsoftonline.com) is not blocked
-5. Repeat 1~4 for 20 times</t>
+4. Verify SSPR traffic (passwordreset.microsoftonline.com) is not blocked</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr">
@@ -4625,8 +4590,7 @@
           <t>1. Enable Secure Config validation on tenant
 2. Deploy NSClient and verify initial config download
 3. Trigger feature flag update from admin
-4. Verify subsequent steering config downloads succeed (no 405 error)
-5. Repeat 1~4 for 20 times</t>
+4. Verify subsequent steering config downloads succeed (no 405 error)</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr">
@@ -4693,8 +4657,7 @@
           <t>1. Install NSClient older version
 2. Delete Logs folder under %appdata%\Netskope\stagent
 3. Trigger auto-upgrade via config push
-4. Verify upgrade completes
-5. Repeat 1~4 for 5 times</t>
+4. Verify upgrade completes</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr">
@@ -5085,8 +5048,7 @@
 3. Launch sustained network traffic in parallel: 1000+ concurrent HTTP/HTTPS flows per second, plus 500 DNS queries per second (mix TCP DNS and UDP DNS), for 30 mins
 4. In parallel with the traffic, push a steering policy update from the tenant every 30 seconds so nsdiag -u forces readCustomDnsSettings and on-prem label re-evaluation on the endpoint
 5. In parallel, toggle the endpoint on-prem/off-prem state every 60 seconds (e.g., by flipping the on-prem detection egress IP or on-prem test URL reachability) so CDetectOnprem::OnpremdetectThread fires repeatedly with push_back into onpremStatusInfoListPtr
-6. Monitor throughout: stAgentSvc.exe PID (must not change), stAgentSvc memory (lower than 200 MB), tunnel status, no dump generated during this period
-7. Repeat for n times (by the --iterations option)</t>
+6. Monitor throughout: stAgentSvc.exe PID (must not change), stAgentSvc memory (lower than 200 MB), tunnel status, no dump generated during this period</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -2094,7 +2094,7 @@
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>DNS traffic steered correctly after FailClose recovery; steering mode change during FailClose does not leave inconsistent state; consistent results across all 20 repetitions with no degradation</t>
+          <t>DNS traffic steered correctly after FailClose recovery; steering mode change during FailClose does not leave inconsistent state</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
@@ -2162,7 +2162,7 @@
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>Client throttles status updates to &lt;1 per 60s; config downloads succeed within 30s during storm; no cascading failure; consistent results across all 20 repetitions with no degradation</t>
+          <t>Client throttles status updates to &lt;1 per 60s; config downloads succeed within 30s during storm; no cascading failure</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>Client remains enabled with correct status after AOAC wake; upgrade completes without enrollment loss on AOAC device; consistent results across all 20 repetitions with no degradation</t>
+          <t>Client remains enabled with correct status after AOAC wake; upgrade completes without enrollment loss on AOAC device</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>All non-exempt traffic blocked immediately after boot even when gateway is unreachable; tunnel recovers when gateway accessible again; consistent results across all 20 repetitions with no degradation</t>
+          <t>All non-exempt traffic blocked immediately after boot even when gateway is unreachable; tunnel recovers when gateway accessible again</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
@@ -2367,7 +2367,7 @@
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>All third-party uninstall attempts blocked; unauthorized IOCTL commands rejected; client remains enabled and protected; consistent results across all 20 repetitions with no degradation</t>
+          <t>All third-party uninstall attempts blocked; unauthorized IOCTL commands rejected; client remains enabled and protected</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
@@ -2435,7 +2435,7 @@
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>No packet drops for large DNS TCP; no BSOD; DNS latency &lt;100ms under 50-session load on VDI; consistent results across all 20 repetitions with no degradation</t>
+          <t>No packet drops for large DNS TCP; no BSOD; DNS latency &lt;100ms under 50-session load on VDI</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>No packet drops for large DNS TCP; no BSOD; DNS latency &lt;100ms under 50-session load on VDI; consistent results across all 20 repetitions with no degradation</t>
+          <t>No packet drops for large DNS TCP; no BSOD; DNS latency &lt;100ms under 50-session load on VDI</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
@@ -2572,7 +2572,7 @@
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>After reboot, UpgradeMonitorThread detects aborted upgrade, retries MSI, and clears UpgradeInProgress within 3 hours; consistent results across all 20 repetitions with no degradation</t>
+          <t>After reboot, UpgradeMonitorThread detects aborted upgrade, retries MSI, and clears UpgradeInProgress within 3 hours</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
@@ -2640,7 +2640,7 @@
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>Client selects optimal DP via GSLB; DTLS-to-TLS failover completes within 30s; client returns to DTLS when available; consistent results across all 20 repetitions with no degradation</t>
+          <t>Client selects optimal DP via GSLB; DTLS-to-TLS failover completes within 30s; client returns to DTLS when available</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>Client recovers from corrupted config via backup mechanism; cert deletion does not crash service; client re-enrolls automatically; consistent results across all 20 repetitions with no degradation</t>
+          <t>Client recovers from corrupted config via backup mechanism; cert deletion does not crash service; client re-enrolls automatically</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
@@ -2777,7 +2777,7 @@
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>Upgrade triggers on scheduled day; interrupted upgrade recovered by Legacy Monitor; client never left in removed state; consistent results across all 5 repetitions with no degradation</t>
+          <t>Upgrade triggers on scheduled day; interrupted upgrade recovered by Legacy Monitor; client never left in removed state</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>No traffic disruption for existing sessions during concurrent logon; each user gets correct steering; logout does not break other sessions; consistent results across all 20 repetitions with no degradation</t>
+          <t>No traffic disruption for existing sessions during concurrent logon; each user gets correct steering; logout does not break other sessions</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
@@ -2915,7 +2915,7 @@
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>IDP enrollment succeeds on Citrix first login; Autopilot enrollment completes; no blank webview2 windows; consistent results across all 20 repetitions with no degradation</t>
+          <t>IDP enrollment succeeds on Citrix first login; Autopilot enrollment completes; no blank webview2 windows</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
@@ -2983,7 +2983,7 @@
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Only cert-pinned app traffic bypasses; all other traffic remains steered; config change does not broaden exception scope; consistent results across all 20 repetitions with no degradation</t>
+          <t>Only cert-pinned app traffic bypasses; all other traffic remains steered; config change does not broaden exception scope</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>No stAgentSvc crash dumps generated across 50 service stop/start cycles with concurrent network events; consistent results across all 20 repetitions with no degradation</t>
+          <t>No stAgentSvc crash dumps generated across 50 service stop/start cycles with concurrent network events</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
@@ -3119,7 +3119,7 @@
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>On-prem correctly detected via egress IP; off-prem transition triggers tunnel reconnect within 30s; steering resumes; consistent results across all 20 repetitions with no degradation</t>
+          <t>On-prem correctly detected via egress IP; off-prem transition triggers tunnel reconnect within 30s; steering resumes</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>After reboot, installation monitor service detects incomplete upgrade and retries. Client is present and functional; consistent results across all 5 repetitions with no degradation</t>
+          <t>After reboot, installation monitor service detects incomplete upgrade and retries. Client is present and functional</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>Service never crashes on wake. Write-packet thread waits for driver initialization. No null pointer access; consistent results across all 20 repetitions with no degradation</t>
+          <t>Service never crashes on wake. Write-packet thread waits for driver initialization. No null pointer access</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>stWatchdog service no longer appears in services.msc; UpgradeInProgress registry absent; no orphan stAgentSvcMon.exe on disk; consistent results across all 20 repetitions with no degradation</t>
+          <t>stWatchdog service no longer appears in services.msc; UpgradeInProgress registry absent; no orphan stAgentSvcMon.exe on disk</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>Watchdog eventually force-kills and restarts the hung service, or escalates via log error after N cycles; consistent results across all 20 repetitions with no degradation</t>
+          <t>Watchdog eventually force-kills and restarts the hung service, or escalates via log error after N cycles</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>DC CPU stays below 80% during SMB operations with NSClient; no connection amplification; no client crash; consistent results across all 20 repetitions with no degradation</t>
+          <t>DC CPU stays below 80% during SMB operations with NSClient; no connection amplification; no client crash</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
@@ -3523,7 +3523,7 @@
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>New user session failure to read nsuser.conf does not trigger FailClose for existing active sessions; consistent results across all 20 repetitions with no degradation</t>
+          <t>New user session failure to read nsuser.conf does not trigger FailClose for existing active sessions</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>Second and subsequent users must complete IDP authentication before enrollment; no silent UPN bypass; consistent results across all 20 repetitions with no degradation</t>
+          <t>Second and subsequent users must complete IDP authentication before enrollment; no silent UPN bypass</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
@@ -3658,7 +3658,7 @@
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>After recovery, stAgentSvc runs the new version. No version mismatch between appinfo.log and running binary; consistent results across all 5 repetitions with no degradation</t>
+          <t>After recovery, stAgentSvc runs the new version. No version mismatch between appinfo.log and running binary</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
@@ -3726,7 +3726,7 @@
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>nsFilterDevice config reloads correctly regardless of multi-user logon timing. All traffic steered through inner tunnel; consistent results across all 20 repetitions with no degradation</t>
+          <t>nsFilterDevice config reloads correctly regardless of multi-user logon timing. All traffic steered through inner tunnel</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>IPv6 traffic without hostname is blocked (not bypassed). m_forceTearDown resets correctly after admin enable; consistent results across all 20 repetitions with no degradation</t>
+          <t>IPv6 traffic without hostname is blocked (not bypassed). m_forceTearDown resets correctly after admin enable</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>No service crash during extended network switching. Overlapped IO prevents indefinite DeviceIoControl blocking; consistent results across all 20 repetitions with no degradation</t>
+          <t>No service crash during extended network switching. Overlapped IO prevents indefinite DeviceIoControl blocking</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
@@ -3927,7 +3927,7 @@
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>AuthenticationToken and EncryptionToken data values exist and match pre-upgrade values; device does not require re-enrollment; consistent results across all 5 repetitions with no degradation</t>
+          <t>AuthenticationToken and EncryptionToken data values exist and match pre-upgrade values; device does not require re-enrollment</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>IPv6 traffic correctly steered; local-link exceptions honored; IPv6 throughput within 20% of IPv4 baseline; consistent results across all 20 repetitions with no degradation</t>
+          <t>IPv6 traffic correctly steered; local-link exceptions honored; IPv6 throughput within 20% of IPv4 baseline</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
@@ -4062,7 +4062,7 @@
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>Upgrade completes within SCM timeout. Service stop token is accepted. No MSI rollback occurs; consistent results across all 20 repetitions with no degradation</t>
+          <t>Upgrade completes within SCM timeout. Service stop token is accepted. No MSI rollback occurs</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>On quota error, stadrv restarts automatically. Tunnel reconnects without manual intervention. No persistent fail-close state; consistent results across all 20 repetitions with no degradation</t>
+          <t>On quota error, stadrv restarts automatically. Tunnel reconnects without manual intervention. No persistent fail-close state</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>All mandatory config downloads complete before tunnel teardown. No traffic mode enforcement without valid exception list; consistent results across all 20 repetitions with no degradation</t>
+          <t>All mandatory config downloads complete before tunnel teardown. No traffic mode enforcement without valid exception list</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
@@ -4263,7 +4263,7 @@
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>stWatchdog service state is SERVICE_RUNNING; nswatchdog_log shows successful startup entry; consistent results across all 20 repetitions with no degradation</t>
+          <t>stWatchdog service state is SERVICE_RUNNING; nswatchdog_log shows successful startup entry</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="F60" s="7" t="inlineStr">
         <is>
-          <t>Client remains enabled and functional; scheduled upgrade triggers correctly without hanging; consistent results across all 5 repetitions with no degradation</t>
+          <t>Client remains enabled and functional; scheduled upgrade triggers correctly without hanging</t>
         </is>
       </c>
       <c r="G60" s="6" t="inlineStr">
@@ -4528,7 +4528,7 @@
       </c>
       <c r="F61" s="7" t="inlineStr">
         <is>
-          <t>SSPR workflow completes at Windows login screen despite FailClose being configured; consistent results across all 20 repetitions with no degradation</t>
+          <t>SSPR workflow completes at Windows login screen despite FailClose being configured</t>
         </is>
       </c>
       <c r="G61" s="6" t="inlineStr">
@@ -4595,7 +4595,7 @@
       </c>
       <c r="F62" s="7" t="inlineStr">
         <is>
-          <t>Steering config downloads successfully after feature flag changes; no 405 errors in client logs; consistent results across all 20 repetitions with no degradation</t>
+          <t>Steering config downloads successfully after feature flag changes; no 405 errors in client logs</t>
         </is>
       </c>
       <c r="G62" s="6" t="inlineStr">
@@ -4662,7 +4662,7 @@
       </c>
       <c r="F63" s="7" t="inlineStr">
         <is>
-          <t>Upgrade completes successfully; installer creates missing Logs folder before launching msiexec; consistent results across all 5 repetitions with no degradation</t>
+          <t>Upgrade completes successfully; installer creates missing Logs folder before launching msiexec</t>
         </is>
       </c>
       <c r="G63" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -672,19 +672,18 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>1. Verify stAgentSvc and stAgentSvcWD are both running
-2. taskkill /F /IM stAgentSvc.exe (force kill — simulates crash)
-3. Wait up to 60 seconds (watchdog check interval)
-4. Verify stAgentSvcWD detects abnormal stop (Win32ExitCode != ERROR_SUCCESS)
-5. Verify stAgentSvc is restarted automatically
-6. Verify tunnel re-establishes after restart
-7. Repeat: kill during active traffic — verify no permanent state corruption
-8. Test edge case: kill stAgentSvc during upgrade (UpgradeInProgress=1 in registry) — watchdog should NOT restart</t>
+          <t>1. Verify stAgentSvc and stAgentSvcMon are both running
+2. Verify tunnel is established
+3. Generate HTTPS flooding by 600 conn in 30 threads
+4. taskkill /F /IM stAgentSvc.exe (force kill — simulates crash)
+5. Verify stAgentSvc is restarted automatically and tunnel re-establishes within 60s
+6. Generate HTTPS flooding by 600 conn in 30 threads
+7. restart stAgentSvc (sc stop stagentsvc and sc start stagentsvc)</t>
         </is>
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Watchdog restarts service within 60-90s. Tunnel recovers. No restart during upgrade. No permanent state corruption after crash+restart.</t>
+          <t>Watchdog restarts service within 61s. Tunnel recovers. No restart during upgrade. No permanent state corruption after crash+restart.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -672,7 +672,7 @@
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>1. Verify stAgentSvc and stAgentSvcMon are both running
+          <t>1. Verify stAgentSvc and stWatchdog are both running
 2. Verify tunnel is established
 3. Generate HTTPS flooding by 600 conn in 30 threads
 4. taskkill /F /IM stAgentSvc.exe (force kill — simulates crash)

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Watchdog restarts service within 61s. Tunnel recovers. No restart during upgrade. No permanent state corruption after crash+restart.</t>
+          <t>Watchdog restarts service within 61s. Tunnel recovers. No permanent state corruption after crash+restart.</t>
         </is>
       </c>
       <c r="G5" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -2063,7 +2063,7 @@
     <row r="25" ht="15.75" customHeight="1" s="5">
       <c r="A25" s="6" t="inlineStr">
         <is>
-          <t>STRESS-09</t>
+          <t>FC-04</t>
         </is>
       </c>
       <c r="B25" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -742,19 +742,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>1. Enable FailClose in client configuration
+          <t xml:space="preserve">1. Enable FailClose in client configuration
 2. Establish tunnel — verify normal traffic flows
-3. Simulate gateway unreachable (block gateway IP at firewall/hosts)
-4. Verify: all user traffic is blocked (cannot browse, cannot reach any external site)
-5. Verify: captive portal detection triggers if connecting to new WiFi with portal
-6. Restore gateway access — verify tunnel reconnects AND traffic unblocks
-7. Test edge case: service crash with FailClose ON — verify traffic blocks during crash window, unblocks after watchdog restart
-8. Test edge case: FailClose + NPA-only tunnel (ENG-1012026 pattern) — verify cert-pinned apps are also blocked</t>
+3. Simulate gateway unreachable (block gateway IP/hostname at firewall + hosts; block BOTH primary and backup gateway, and chase GSLB POP switches after the client restart, or the client reconnects to an unblocked POP and never fail-closes)
+4. Verify: all user traffic is blocked (cannot browse, cannot reach any external site) — measure the block latency from tunnel drop
+5. (OPTIONAL — SKIPPED: needs a captive-portal-capable WiFi environment, which no current lane VM has; the client-side WiFi toggle helper does not exist either. Track separately, do not gate this case on it.) Verify: captive portal detection triggers if connecting to new WiFi with portal
+6. Restore gateway access — verify tunnel reconnects AND traffic unblocks; measure the restore latency
+7. Test edge case: service crash with FailClose ON — verify traffic blocks during the crash window, unblocks after watchdog restart
+8. (OPTIONAL — NPA-licensed tenants only. Auto-detect with nsdiag -n and skip when it reports NPA status Disabled or gateway IP N/A, same pattern as STRESS-03.) Test edge case: FailClose + NPA-only tunnel (ENG-1012026 pattern) — verify cert-pinned apps are also blocked</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Traffic blocked within 5s of tunnel drop. Traffic restored within 30s of tunnel recovery. No permanent block state. Captive portal detection works.</t>
+          <t xml:space="preserve">Traffic blocked within 5s of tunnel drop. Traffic restored within 30s of tunnel recovery. No permanent block state (traffic must recover WITHOUT restarting the client — a restart-only recovery is a fail, since it hides the stuck-blocking bug). Crash window: traffic blocked while the service is down, unblocked after the watchdog restart. Captive portal detection works (only when step 5 is exercised; skipped runs must not report it as passed).</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -745,16 +745,16 @@
           <t xml:space="preserve">1. Enable FailClose in client configuration
 2. Establish tunnel — verify normal traffic flows
 3. Simulate gateway unreachable (block gateway IP/hostname at firewall + hosts; block BOTH primary and backup gateway, and chase GSLB POP switches after the client restart, or the client reconnects to an unblocked POP and never fail-closes)
-4. Verify: all user traffic is blocked (cannot browse, cannot reach any external site) — measure the block latency from tunnel drop
+4. Verify: all user traffic is blocked (cannot browse, cannot reach any external site)
 5. (OPTIONAL — SKIPPED: needs a captive-portal-capable WiFi environment, which no current lane VM has; the client-side WiFi toggle helper does not exist either. Track separately, do not gate this case on it.) Verify: captive portal detection triggers if connecting to new WiFi with portal
-6. Restore gateway access — verify tunnel reconnects AND traffic unblocks; measure the restore latency
+6. Restore gateway access — verify tunnel reconnects AND traffic unblocks
 7. Test edge case: service crash with FailClose ON — verify traffic blocks during the crash window, unblocks after watchdog restart
 8. (OPTIONAL — NPA-licensed tenants only. Auto-detect with nsdiag -n and skip when it reports NPA status Disabled or gateway IP N/A, same pattern as STRESS-03.) Test edge case: FailClose + NPA-only tunnel (ENG-1012026 pattern) — verify cert-pinned apps are also blocked</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Traffic blocked within 5s of tunnel drop. Traffic restored within 30s of tunnel recovery. No permanent block state (traffic must recover WITHOUT restarting the client — a restart-only recovery is a fail, since it hides the stuck-blocking bug). Crash window: traffic blocked while the service is down, unblocked after the watchdog restart. Captive portal detection works (only when step 5 is exercised; skipped runs must not report it as passed).</t>
+          <t xml:space="preserve">All non-exempt traffic blocked while the gateway is unreachable; tunnel and traffic both recover when the gateway is accessible again, WITHOUT restarting the client (a restart-only recovery is a fail — it hides the stuck-blocking bug). No permanent block state. During the crash window: traffic blocked while the service is down, unblocked after the watchdog restart. Captive portal detection works (only when step 5 is exercised; a skipped run must not report it as passed).</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -742,19 +742,19 @@
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1. Enable FailClose in client configuration
+          <t>1. Enable FailClose in client configuration
 2. Establish tunnel — verify normal traffic flows
-3. Simulate gateway unreachable (block gateway IP/hostname at firewall + hosts; block BOTH primary and backup gateway, and chase GSLB POP switches after the client restart, or the client reconnects to an unblocked POP and never fail-closes)
+3. Simulate gateway unreachable (block gateway IP at firewall/hosts)
 4. Verify: all user traffic is blocked (cannot browse, cannot reach any external site)
-5. (OPTIONAL — SKIPPED: needs a captive-portal-capable WiFi environment, which no current lane VM has; the client-side WiFi toggle helper does not exist either. Track separately, do not gate this case on it.) Verify: captive portal detection triggers if connecting to new WiFi with portal
-6. Restore gateway access — verify tunnel reconnects AND traffic unblocks
-7. Test edge case: service crash with FailClose ON — verify traffic blocks during the crash window, unblocks after watchdog restart
-8. (OPTIONAL — NPA-licensed tenants only. Auto-detect with nsdiag -n and skip when it reports NPA status Disabled or gateway IP N/A, same pattern as STRESS-03.) Test edge case: FailClose + NPA-only tunnel (ENG-1012026 pattern) — verify cert-pinned apps are also blocked</t>
+5. (OPTIONAL — requires a captive-portal-capable WiFi environment, not available on current lane VMs; non-blocking) Verify: captive portal detection triggers if connecting to new WiFi with portal
+6. Restore gateway access — verify tunnel reconnects AND traffic unblocks WITHOUT a client restart (a recovery needing a restart hides the stuck-blocking bug)
+7. Test edge case: service crash with FailClose ON. EXPECTED fail-open: killing stAgentSvc tears down the WFP blocking (driver auto-teardown on device-handle close — availability over security for the agent's own crash), so traffic FLOWS during the crash window. The hard assertion is AFTER the watchdog restart: with the gateway still blocked, FailClose must RE-ENGAGE (traffic blocked again); then restore gateway access — traffic unblocks
+8. (OPTIONAL — NPA-licensed tenants only; auto-detect via nsdiag -n, skip when NPA status is N/A, mirroring STRESS-03's NPA pattern) Test edge case: FailClose + NPA-only tunnel (ENG-1012026 pattern) — verify cert-pinned apps are also blocked</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">All non-exempt traffic blocked while the gateway is unreachable; tunnel and traffic both recover when the gateway is accessible again, WITHOUT restarting the client (a restart-only recovery is a fail — it hides the stuck-blocking bug). No permanent block state. During the crash window: traffic blocked while the service is down, unblocked after the watchdog restart. Captive portal detection works (only when step 5 is exercised; a skipped run must not report it as passed).</t>
+          <t>All non-exempt traffic blocked while FailClose is engaged (gateway unreachable). Traffic restored after gateway recovery WITHOUT a client restart. No permanent block state. Service crash is a deliberate FAIL-OPEN (driver auto-teardown): traffic flows during the crash window — this is expected, NOT a failure. After the watchdog restarts the service with the gateway still blocked, FailClose must re-engage and block again. Captive portal detection works (OPTIONAL — non-blocking until a captive-portal-capable environment exists). Cert-pinned apps blocked under FailClose + NPA-only tunnel (OPTIONAL — verified only on NPA-licensed tenants, auto-detected via nsdiag -n; skipped when N/A).</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -747,14 +747,14 @@
 3. Simulate gateway unreachable (block gateway IP at firewall/hosts)
 4. Verify: all user traffic is blocked (cannot browse, cannot reach any external site)
 5. (OPTIONAL — requires a captive-portal-capable WiFi environment, not available on current lane VMs; non-blocking) Verify: captive portal detection triggers if connecting to new WiFi with portal
-6. Restore gateway access — verify tunnel reconnects AND traffic unblocks WITHOUT a client restart (a recovery needing a restart hides the stuck-blocking bug)
-7. Test edge case: service crash with FailClose ON. EXPECTED fail-open: killing stAgentSvc tears down the WFP blocking (driver auto-teardown on device-handle close — availability over security for the agent's own crash), so traffic FLOWS during the crash window. The hard assertion is AFTER the watchdog restart: with the gateway still blocked, FailClose must RE-ENGAGE (traffic blocked again); then restore gateway access — traffic unblocks
+6. Restore gateway access — verify tunnel reconnects AND traffic unblocks WITHOUT a client restart
+7. Service crash edge case: crash is a deliberate fail-open (driver auto-teardown drops WFP blocking) — traffic flowing in the crash window is expected, NOT a failure. After watchdog restart with gateway still blocked, FailClose must re-engage (traffic blocked again); restore gateway — traffic unblocks
 8. (OPTIONAL — NPA-licensed tenants only; auto-detect via nsdiag -n, skip when NPA status is N/A, mirroring STRESS-03's NPA pattern) Test edge case: FailClose + NPA-only tunnel (ENG-1012026 pattern) — verify cert-pinned apps are also blocked</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>All non-exempt traffic blocked while FailClose is engaged (gateway unreachable). Traffic restored after gateway recovery WITHOUT a client restart. No permanent block state. Service crash is a deliberate FAIL-OPEN (driver auto-teardown): traffic flows during the crash window — this is expected, NOT a failure. After the watchdog restarts the service with the gateway still blocked, FailClose must re-engage and block again. Captive portal detection works (OPTIONAL — non-blocking until a captive-portal-capable environment exists). Cert-pinned apps blocked under FailClose + NPA-only tunnel (OPTIONAL — verified only on NPA-licensed tenants, auto-detected via nsdiag -n; skipped when N/A).</t>
+          <t>Traffic blocked while FailClose engaged. Traffic restored after gateway recovery WITHOUT a client restart. No permanent block. Crash-window fail-open is by design (expected, not a failure); FailClose must re-engage after watchdog restart while still fenced. (OPTIONAL, non-blocking) Captive portal detection. (OPTIONAL, NPA tenants only, auto-detect via nsdiag -n) Cert-pinned apps blocked under NPA-only tunnel.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -2425,16 +2425,17 @@
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>1. Enable DNS security
-2. Generate large DNS TCP responses (&gt;512 bytes, fragmented)
-3. Verify packets not dropped or corrupted
-4. Monitor for BSOD/crash
-5. Verify DNS resolution latency stays under threshold</t>
+          <t>1. Enable Flexible Dynamic Steering; measure baseline DNS-over-TCP latency with DNS Security OFF
+2. Enable DNS Security and verify the DNS fields actually reached the client
+3. Generate large DNS-over-TCP responses under concurrent load, in two size tiers: single-segment (&gt;512 bytes, forces TCP fallback) and multi-segment (&gt;1460 bytes / TCP MSS, forces segmentation and reassembly)
+4. Verify packets not dropped or corrupted (full length-prefixed response read; a short read or length mismatch counts as a drop)
+5. Monitor for BSOD / user-mode crash and for CPU / memory / handle regression
+6. Verify DNS resolution latency stays under threshold and not grossly worse than the DNS-Security-OFF baseline</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>No packet drops for large DNS TCP; no BSOD; DNS latency &lt;100ms under 50-session load on VDI</t>
+          <t>No drops or corruption of large DNS-over-TCP responses in either size tier, and both tiers provably exercised (at least one response over 512 bytes AND at least one over 1460 bytes per cycle -- a run that only saw small responses proves nothing); no BSOD and no user-mode crash; DNS p95 latency under threshold and not grossly worse than the same-host DNS-Security-OFF baseline; stAgentSvc CPU / memory / handles within the SystemTest health gate. Multi-session (50+ concurrent sessions) is covered by VDI-07; this row covers the single-host path.</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z70"/>
+  <dimension ref="A1:Z71"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="11.63" customWidth="1" style="5" min="1" max="1"/>
@@ -5074,7 +5074,61 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="15.75" customHeight="1" s="5"/>
+    <row r="71" ht="15.75" customHeight="1" s="5">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>AOAC-02</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Hibernate (S4) &amp; Resume</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Power Management / Service Lifecycle</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Tests NSClient behavior across full hibernate (S4 — memory saved to disk, full power off) and resume. Unlike Modern Standby, S4 means ALL state is lost — network adapters reset, services see a cold-start-like event but with preserved process memory. Tests whether the service correctly re-detects network, re-establishes tunnel, and whether any in-memory state (tunnel state machine, config cache, GSLB selection) becomes stale or corrupt after resume.</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>1. Establish tunnel, verify traffic flowing
+2. Trigger hibernate (shutdown /h)
+3. Resume from hibernate
+4. Verify: stAgentSvc is running (should survive hibernate as service)
+5. Verify: tunnel reconnects — network detection fires on resume
+6. Verify: config is still valid (not expired during hibernate period)
+7. Verify: GSLB cache is refreshed (POP might have changed while hibernated)
+8. Test: hibernate for extended period (2+ hours) then resume — verify cert hasn't expired, config re-downloads
+9. Verify: FailClose handles the transition correctly (doesn't block during reconnect window)</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Service survives hibernate. Tunnel reconnects within 30s of resume. Config re-validated. No stale GSLB state.</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>After hibernate: tunnel never reconnects, user has no security coverage. Or FailClose activates permanently because tunnel state is stale from pre-hibernate.</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Service lifecycle gaps (45% test gap rate in ch.03). Power event handling in stAgentSvc.cpp.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Confluence Page - Windows System Test Plan</t>
+        </is>
+      </c>
+    </row>
     <row r="72" ht="15.75" customHeight="1" s="5"/>
     <row r="73" ht="15.75" customHeight="1" s="5"/>
     <row r="74" ht="15.75" customHeight="1" s="5"/>

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -749,12 +749,12 @@
 5. (OPTIONAL — requires a captive-portal-capable WiFi environment, not available on current lane VMs; non-blocking) Verify: captive portal detection triggers if connecting to new WiFi with portal
 6. Restore gateway access — verify tunnel reconnects AND traffic unblocks WITHOUT a client restart
 7. Service crash edge case: crash is a deliberate fail-open (driver auto-teardown drops WFP blocking) — traffic flowing in the crash window is expected, NOT a failure. After watchdog restart with gateway still blocked, FailClose must re-engage (traffic blocked again); restore gateway — traffic unblocks
-8. (OPTIONAL — NPA-licensed tenants only; auto-detect via nsdiag -n, skip when NPA status is N/A, mirroring STRESS-03's NPA pattern) Test edge case: FailClose + NPA-only tunnel (ENG-1012026 pattern) — verify cert-pinned apps are also blocked</t>
+8. (OPTIONAL — NPA-licensed tenants only; auto-detect via nsdiag -n, skip when NPA is not Connected) FailClose + NPA User Tunnel (ENG-1012026): with FailClose armed, block BOTH the CASB gateway and the NPA gateway -&gt; restart -&gt; FAIL_CLOSED. Verify: non-CPA traffic is blocked AND cert-pinned app flows (decrypt-action CPA, e.g. [tlstest]) are also blocked — expected evidence 'FailClosed flow dropped:: ... process: &lt;cpa proc&gt;' in nsdebuglog. Note: the ticket's claimed mechanism (NPA in m_tunnelIds) is source-disputed, but live repro on tenant 1347 (2026-07-30) shows the decrypt-action CPA bypasses FailClose via bypassAppMgr 'Bypassing connection ... to be decrypted' — the assertion documents the CORRECT behavior; a bypass is the bug signature</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Traffic blocked while FailClose engaged. Traffic restored after gateway recovery WITHOUT a client restart. No permanent block. Crash-window fail-open is by design (expected, not a failure); FailClose must re-engage after watchdog restart while still fenced. (OPTIONAL, non-blocking) Captive portal detection. (OPTIONAL, NPA tenants only, auto-detect via nsdiag -n) Cert-pinned apps blocked under NPA-only tunnel.</t>
+          <t>Traffic blocked while FailClose engaged. Traffic restored after gateway recovery WITHOUT a client restart. No permanent block. Crash-window fail-open is by design (expected, not a failure); FailClose must re-engage after watchdog restart while still fenced. (OPTIONAL, non-blocking) Captive portal detection. (OPTIONAL, NPA tenants only, auto-detect via nsdiag -n) Under FailClose + NPA User Tunnel with both gateways blocked: non-CPA traffic blocked AND cert-pinned apps blocked ('FailClosed flow dropped::' + process in log); a cert-pinned 'Bypassing connection' line while fenced = FAIL.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">
@@ -5075,27 +5075,27 @@
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" s="5">
-      <c r="A71" t="inlineStr">
+      <c r="A71" s="0" t="inlineStr">
         <is>
           <t>AOAC-02</t>
         </is>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="0" t="inlineStr">
         <is>
           <t>Hibernate (S4) &amp; Resume</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
+      <c r="C71" s="0" t="inlineStr">
         <is>
           <t>Power Management / Service Lifecycle</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
+      <c r="D71" s="0" t="inlineStr">
         <is>
           <t>Tests NSClient behavior across full hibernate (S4 — memory saved to disk, full power off) and resume. Unlike Modern Standby, S4 means ALL state is lost — network adapters reset, services see a cold-start-like event but with preserved process memory. Tests whether the service correctly re-detects network, re-establishes tunnel, and whether any in-memory state (tunnel state machine, config cache, GSLB selection) becomes stale or corrupt after resume.</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
+      <c r="E71" s="0" t="inlineStr">
         <is>
           <t>1. Establish tunnel, verify traffic flowing
 2. Trigger hibernate (shutdown /h)
@@ -5108,22 +5108,22 @@
 9. Verify: FailClose handles the transition correctly (doesn't block during reconnect window)</t>
         </is>
       </c>
-      <c r="F71" t="inlineStr">
+      <c r="F71" s="0" t="inlineStr">
         <is>
           <t>Service survives hibernate. Tunnel reconnects within 30s of resume. Config re-validated. No stale GSLB state.</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="G71" s="0" t="inlineStr">
         <is>
           <t>After hibernate: tunnel never reconnects, user has no security coverage. Or FailClose activates permanently because tunnel state is stale from pre-hibernate.</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
+      <c r="H71" s="0" t="inlineStr">
         <is>
           <t>Service lifecycle gaps (45% test gap rate in ch.03). Power event handling in stAgentSvc.cpp.</t>
         </is>
       </c>
-      <c r="I71" t="inlineStr">
+      <c r="I71" s="0" t="inlineStr">
         <is>
           <t>Confluence Page - Windows System Test Plan</t>
         </is>

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -744,17 +744,17 @@
         <is>
           <t>1. Enable FailClose in client configuration
 2. Establish tunnel — verify normal traffic flows
-3. Simulate gateway unreachable (block gateway IP at firewall/hosts)
-4. Verify: all user traffic is blocked (cannot browse, cannot reach any external site)
-5. (OPTIONAL — requires a captive-portal-capable WiFi environment, not available on current lane VMs; non-blocking) Verify: captive portal detection triggers if connecting to new WiFi with portal
+3. Simulate gateway unreachable (block gateway IP at firewall)
+4. Verify: all user traffic is blocked
+5. (OPTIONAL, non-blocking — no captive-portal-capable env) Captive portal detection on new WiFi
 6. Restore gateway access — verify tunnel reconnects AND traffic unblocks WITHOUT a client restart
-7. Service crash edge case: crash is a deliberate fail-open (driver auto-teardown drops WFP blocking) — traffic flowing in the crash window is expected, NOT a failure. After watchdog restart with gateway still blocked, FailClose must re-engage (traffic blocked again); restore gateway — traffic unblocks
-8. (OPTIONAL — NPA-licensed tenants only; auto-detect via nsdiag -n, skip when NPA is not Connected) FailClose + NPA User Tunnel (ENG-1012026): with FailClose armed, block BOTH the CASB gateway and the NPA gateway -&gt; restart -&gt; FAIL_CLOSED. Verify: non-CPA traffic is blocked AND cert-pinned app flows (decrypt-action CPA, e.g. [tlstest]) are also blocked — expected evidence 'FailClosed flow dropped:: ... process: &lt;cpa proc&gt;' in nsdebuglog. Note: the ticket's claimed mechanism (NPA in m_tunnelIds) is source-disputed, but live repro on tenant 1347 (2026-07-30) shows the decrypt-action CPA bypasses FailClose via bypassAppMgr 'Bypassing connection ... to be decrypted' — the assertion documents the CORRECT behavior; a bypass is the bug signature</t>
+7. Service crash edge case: deliberate fail-open — traffic flowing in the crash window is expected, NOT a failure. After watchdog restart with gateway still blocked, FailClose must re-engage; restore gateway — traffic unblocks
+8. (OPTIONAL — NPA tenants only; auto-skip) FailClose + NPA-only tunnel: cert-pinned apps must also be blocked</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>Traffic blocked while FailClose engaged. Traffic restored after gateway recovery WITHOUT a client restart. No permanent block. Crash-window fail-open is by design (expected, not a failure); FailClose must re-engage after watchdog restart while still fenced. (OPTIONAL, non-blocking) Captive portal detection. (OPTIONAL, NPA tenants only, auto-detect via nsdiag -n) Under FailClose + NPA User Tunnel with both gateways blocked: non-CPA traffic blocked AND cert-pinned apps blocked ('FailClosed flow dropped::' + process in log); a cert-pinned 'Bypassing connection' line while fenced = FAIL.</t>
+          <t>Traffic blocked while FailClose engaged. Traffic restored after gateway recovery WITHOUT a client restart. No permanent block. Crash-window fail-open is by design; FailClose must re-engage after watchdog restart while still fenced. (OPTIONAL, non-blocking) Captive portal detection. (OPTIONAL, NPA only) Cert-pinned apps blocked under FailClose + NPA-only tunnel.</t>
         </is>
       </c>
       <c r="G6" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -2974,16 +2974,16 @@
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>1. Configure cert-pinned exception for a specific app (e.g., Teams)
-2. Verify only that app's traffic bypasses tunnel
-3. Generate traffic from other apps
-4. Verify other apps still steered through tunnel
-5. Change steering config and verify cert-pinned exception still scoped correctly</t>
+          <t>1. Register tlstest.exe as a cert-pinned app with bypass action
+2. Generate traffic from tlstest.exe, another app, and a non-CPA control app to the same destinations — verify only tlstest bypasses the tunnel; the others stay steered
+3. Verify the exception does not broaden: no other app's traffic bypasses, to any destination
+4. Switch tlstest's action to decrypt
+5. Verify decryption takes effect for tlstest traffic; other apps stay steered</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>Only cert-pinned app traffic bypasses; all other traffic remains steered; config change does not broaden exception scope</t>
+          <t>Only the cert-pinned app's traffic bypasses; all other traffic stays steered — no broadening of exception scope to other apps or domains. Switching the app action to decrypt takes effect, with decryption evidenced for the app's flows.</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z71"/>
+  <dimension ref="A1:Z72"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="11.63" customWidth="1" style="5" min="1" max="1"/>
@@ -5129,7 +5129,57 @@
         </is>
       </c>
     </row>
-    <row r="72" ht="15.75" customHeight="1" s="5"/>
+    <row r="72" ht="15.75" customHeight="1" s="5">
+      <c r="A72" s="0" t="inlineStr">
+        <is>
+          <t>STEER-05</t>
+        </is>
+      </c>
+      <c r="B72" s="0" t="inlineStr">
+        <is>
+          <t>Steering Rule Update Fast Verification (subset of STEER-01)</t>
+        </is>
+      </c>
+      <c r="C72" s="0" t="inlineStr">
+        <is>
+          <t>Steering / Traffic Interception</t>
+        </is>
+      </c>
+      <c r="D72" s="0" t="inlineStr">
+        <is>
+          <t>Fast, isolated subset of STEER-01 (test_steer_05_fast.py, PR #412, merged 2026-08-26): validates only step 1 (client healthy, Cloud Apps traffic mode), step 5 (new connection steered after a rule change), and step 6 (still steered after the leak-grace period). Skips STEER-01's slow steps 2-4 (long-lived download through a rule change). Uses a dedicated HTTPS verify domain instead of an HTTP long-lived-download host: a TLS cert re-signed by the Netskope CA is authoritative proof the connection was steered -- more reliable than the 'Tunneling flow' debug-log marker alone, which is racy for short connections. Runs as separate Windows and Mac test functions (test_steer_05_fast_new_conn_steered / _mac), sharing one pyrobin.case ID with STEER-01 (same spec item, two automations).</t>
+        </is>
+      </c>
+      <c r="E72" s="0" t="inlineStr">
+        <is>
+          <t>1. Ensure client healthy: enrolled, tunnel CONNECTED; force traffic mode to Cloud Apps Only via the bound steering config if not already set (restored in teardown).
+2. Add a dedicated HTTPS verify domain to the steering (managed cloud apps) list; push and content-verify the domain actually landed in the client's nssteering.json (not just that the push API returned success).
+3. Flush DNS, then start a NEW connection (curl) to the verify domain.
+4. Verify the new connection is steered: check the debug-log 'Tunneling flow' marker first, then fall back to TLS cert issuer = Netskope CA. Retry up to 4 times with short backoff.
+5. Wait the leak-grace period, flush DNS, start another new connection, and re-verify it is still steered (no permanent bypass leak after the grace window).</t>
+        </is>
+      </c>
+      <c r="F72" s="0" t="inlineStr">
+        <is>
+          <t>New connection to the just-steered domain is steered promptly (debug-log marker or Netskope-CA cert issuer) within the retry window. After the leak-grace period, a fresh connection to the same domain is still steered -- no reversion to bypass.</t>
+        </is>
+      </c>
+      <c r="G72" s="0" t="inlineStr">
+        <is>
+          <t>Same class of gap as STEER-01 but caught faster: a newly steering-added domain is not promptly enforced for new connections, or reverts to bypass after the grace window -- a security policy gap on always-on/frequently-reconnecting apps.</t>
+        </is>
+      </c>
+      <c r="H72" s="0" t="inlineStr">
+        <is>
+          <t>Same as STEER-01: Ch. 09 (Traffic Interception), Ch. 05 (Steering Configuration). Fast subset isolating STEER-01's flaky steps 5/6 from its slow long-lived-download steps 2-4.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>New - formal test case as of PR #412 (2026-08-26), split into windows/mac wrappers; subset of STEER-01 (test_steer_05_fast.py), intended to be merged back into test_steer_p0.py's full 7-step case once stable.</t>
+        </is>
+      </c>
+    </row>
     <row r="73" ht="15.75" customHeight="1" s="5"/>
     <row r="74" ht="15.75" customHeight="1" s="5"/>
     <row r="75" ht="15.75" customHeight="1" s="5"/>

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -361,7 +361,7 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:Z72"/>
+  <dimension ref="A1:Z73"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col width="11.63" customWidth="1" style="5" min="1" max="1"/>
@@ -5174,13 +5174,63 @@
           <t>Same as STEER-01: Ch. 09 (Traffic Interception), Ch. 05 (Steering Configuration). Fast subset isolating STEER-01's flaky steps 5/6 from its slow long-lived-download steps 2-4.</t>
         </is>
       </c>
-      <c r="I72" t="inlineStr">
+      <c r="I72" s="0" t="inlineStr">
         <is>
           <t>New - formal test case as of PR #412 (2026-08-26), split into windows/mac wrappers; subset of STEER-01 (test_steer_05_fast.py), intended to be merged back into test_steer_p0.py's full 7-step case once stable.</t>
         </is>
       </c>
     </row>
-    <row r="73" ht="15.75" customHeight="1" s="5"/>
+    <row r="73" ht="15.75" customHeight="1" s="5">
+      <c r="A73" s="0" t="inlineStr">
+        <is>
+          <t>STRESS-02-MAC</t>
+        </is>
+      </c>
+      <c r="B73" s="0" t="inlineStr">
+        <is>
+          <t>Per-Protocol Traffic Flood (DNS/UDP/FTP/SFTP) - mac</t>
+        </is>
+      </c>
+      <c r="C73" s="0" t="inlineStr">
+        <is>
+          <t>Tunneling / Stress</t>
+        </is>
+      </c>
+      <c r="D73" s="0" t="inlineStr">
+        <is>
+          <t>Per-protocol face of STRESS-02: drives DNS, UDP, FTP and SFTP volume SIMULTANEOUSLY, instead of the sustained-HTTPS-bandwidth face the STRESS-02 row already covers, and gates client survival under it (tunnel stays connected, steering binding unchanged, client processes alive, bounded memory growth). This is the automation of what QA runs by hand on Macs every release with the local stress_test tool. Mac automation = test_stress_02_protocol_flood_mac, driving a stdlib-only VM-side generator (stock mac python3, no pip packages; the SFTP leg shells out to the stock /usr/bin/sftp client). Shares the SYS-STRESS-02 case ID with the bandwidth face - same spec item, two automations. Deliberately NOT covered: MTU 1300-vs-9000 variation and packet-loss injection (needs a network conditioner; only the UDP payload size is configurable), and GRE/IPsec flooding (cannot be emitted from userland python).</t>
+        </is>
+      </c>
+      <c r="E73" s="0" t="inlineStr">
+        <is>
+          <t>1. Client daemon running and tunnel CONNECTED; capture the bound steering config name and the client memory baseline
+2. Start a simultaneous per-protocol flood from the mac for &gt;=4 min: DNS random-subdomain queries, UDP datagrams, FTP uploads, SFTP uploads
+3. Poll the tunnel for the whole load window - it must never disconnect
+4. Read the per-protocol counters: every enabled protocol must show real volume (missing counters = harness failure, not a product result; all file transfers failing = environment failure)
+5. Verify the bound steering config is unchanged, the tunnel is still connected, client health processes are alive, and client memory growth is under the ceiling</t>
+        </is>
+      </c>
+      <c r="F73" s="0" t="inlineStr">
+        <is>
+          <t>Zero tunnel disconnects across the flood window; every enabled protocol records non-zero volume (FTP/SFTP additionally record non-zero SUCCESSFUL uploads); bound steering config unchanged; client health processes alive; client memory growth &lt;50MB over the window. Consistent across all repetitions (--iterations).</t>
+        </is>
+      </c>
+      <c r="G73" s="0" t="inlineStr">
+        <is>
+          <t>Non-HTTP protocol volume destabilises the client: the tunnel drops or the steering binding changes under load, or memory grows unbounded - leaving traffic unprotected on exactly the protocols customers saturate in production, and on the platform where this load is currently only ever checked by hand.</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Per-release manual mac protocol-flood runs: ENG-914348~352 (R136), ENG-950122 series (R137). Same spec-row family as STRESS-02 (EIMF-237/EIMF-344 slow downloads, IMF-1325 HAProxy CPU).</t>
+        </is>
+      </c>
+      <c r="I73" s="0" t="inlineStr">
+        <is>
+          <t>NSClient Reliability Test Plan - STRESS-02 per-protocol face (the STRESS-02 row keeps the sustained-bandwidth face). Mac automation added 2026-09-04 (PR 442, ns-klin); ported from the per-protocol half of the local stress_test tool.</t>
+        </is>
+      </c>
+    </row>
     <row r="74" ht="15.75" customHeight="1" s="5"/>
     <row r="75" ht="15.75" customHeight="1" s="5"/>
     <row r="76" ht="15.75" customHeight="1" s="5"/>

--- a/systemtest-plan/system_test_new.xlsx
+++ b/systemtest-plan/system_test_new.xlsx
@@ -5183,7 +5183,7 @@
     <row r="73" ht="15.75" customHeight="1" s="5">
       <c r="A73" s="0" t="inlineStr">
         <is>
-          <t>STRESS-02-MAC</t>
+          <t>STRESS-27</t>
         </is>
       </c>
       <c r="B73" s="0" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="D73" s="0" t="inlineStr">
         <is>
-          <t>Per-protocol face of STRESS-02: drives DNS, UDP, FTP and SFTP volume SIMULTANEOUSLY, instead of the sustained-HTTPS-bandwidth face the STRESS-02 row already covers, and gates client survival under it (tunnel stays connected, steering binding unchanged, client processes alive, bounded memory growth). This is the automation of what QA runs by hand on Macs every release with the local stress_test tool. Mac automation = test_stress_02_protocol_flood_mac, driving a stdlib-only VM-side generator (stock mac python3, no pip packages; the SFTP leg shells out to the stock /usr/bin/sftp client). Shares the SYS-STRESS-02 case ID with the bandwidth face - same spec item, two automations. Deliberately NOT covered: MTU 1300-vs-9000 variation and packet-loss injection (needs a network conditioner; only the UDP payload size is configurable), and GRE/IPsec flooding (cannot be emitted from userland python).</t>
+          <t>Per-protocol face of the mac stress family: drives DNS, UDP, FTP and SFTP volume SIMULTANEOUSLY, instead of the sustained-HTTPS-bandwidth face STRESS-02 covers, and gates client survival under it (tunnel stays connected, steering binding unchanged, client processes alive, bounded memory growth). This is the automation of what QA runs by hand on Macs every release with the local stress_test tool. Mac automation = test_stress_02_protocol_flood_mac, driving a stdlib-only VM-side generator (stock mac python3, no pip packages; the SFTP leg shells out to the stock /usr/bin/sftp client). Independent case ID SYS-STRESS-27 (previously staged under a shared STRESS-02 ID; split out to avoid colliding with STRESS-09, which is unrelated). Deliberately NOT covered: MTU 1300-vs-9000 variation and packet-loss injection (needs a network conditioner; only the UDP payload size is configurable), and GRE/IPsec flooding (cannot be emitted from userland python).</t>
         </is>
       </c>
       <c r="E73" s="0" t="inlineStr">
@@ -5220,14 +5220,14 @@
           <t>Non-HTTP protocol volume destabilises the client: the tunnel drops or the steering binding changes under load, or memory grows unbounded - leaving traffic unprotected on exactly the protocols customers saturate in production, and on the platform where this load is currently only ever checked by hand.</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr">
+      <c r="H73" s="0" t="inlineStr">
         <is>
           <t>Per-release manual mac protocol-flood runs: ENG-914348~352 (R136), ENG-950122 series (R137). Same spec-row family as STRESS-02 (EIMF-237/EIMF-344 slow downloads, IMF-1325 HAProxy CPU).</t>
         </is>
       </c>
       <c r="I73" s="0" t="inlineStr">
         <is>
-          <t>NSClient Reliability Test Plan - STRESS-02 per-protocol face (the STRESS-02 row keeps the sustained-bandwidth face). Mac automation added 2026-09-04 (PR 442, ns-klin); ported from the per-protocol half of the local stress_test tool.</t>
+          <t>NSClient Reliability Test Plan - mac per-protocol flood face, independent case ID SYS-STRESS-27 (STRESS-02 keeps the sustained-bandwidth face). Mac automation added 2026-09-04 (PR 442, ns-klin); ported from the per-protocol half of the local stress_test tool.</t>
         </is>
       </c>
     </row>
